--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU41"/>
+  <dimension ref="A1:AU44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Asyut Petroleum</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-08-26 12:00:00</t>
+          <t>2026-08-26 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1892,27 +1892,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-08-26 13:00:00</t>
+          <t>2026-08-26 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2060,22 +2060,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G11">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G12">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-08-26 14:00:00</t>
+          <t>2026-08-26 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2549,22 +2549,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14">
@@ -2712,22 +2712,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G18">
@@ -3359,27 +3359,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G19">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-08-26 14:30:00</t>
+          <t>2026-08-26 14:00:00</t>
         </is>
       </c>
     </row>
@@ -3522,27 +3522,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G20">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-08-26 14:30:00</t>
+          <t>2026-08-26 14:00:00</t>
         </is>
       </c>
     </row>
@@ -3685,27 +3685,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G21">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-08-26 14:30:00</t>
+          <t>2026-08-26 14:00:00</t>
         </is>
       </c>
     </row>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G22">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G23">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-08-26 15:00:00</t>
+          <t>2026-08-26 14:30:00</t>
         </is>
       </c>
     </row>
@@ -4174,27 +4174,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G24">
@@ -4217,68 +4217,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N24">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X24">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y24">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z24">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC24">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AD24">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG24">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK24">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-08-26 15:00:00</t>
+          <t>2026-08-26 14:30:00</t>
         </is>
       </c>
     </row>
@@ -4337,27 +4337,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G25">
@@ -4380,68 +4380,68 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N25">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="V25">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X25">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y25">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z25">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AA25">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC25">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD25">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE25">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG25">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK25">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-08-26 15:00:00</t>
+          <t>2026-08-26 14:30:00</t>
         </is>
       </c>
     </row>
@@ -4505,22 +4505,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X26">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y26">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC26">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="AD26">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE26">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK26">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="O27">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="P27">
+        <v>3.45</v>
+      </c>
+      <c r="Q27">
         <v>3.2</v>
       </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y27">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Z27">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AA27">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="AB27">
+        <v>1.33</v>
+      </c>
+      <c r="AC27">
+        <v>5.7</v>
+      </c>
+      <c r="AD27">
+        <v>1.08</v>
+      </c>
+      <c r="AE27">
+        <v>1.03</v>
+      </c>
+      <c r="AF27">
+        <v>2.38</v>
+      </c>
+      <c r="AG27">
+        <v>1.53</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
         <v>1.36</v>
       </c>
-      <c r="AC27">
-        <v>0</v>
-      </c>
-      <c r="AD27">
-        <v>0</v>
-      </c>
-      <c r="AE27">
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <v>0</v>
-      </c>
-      <c r="AG27">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>0</v>
-      </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,52 +4873,52 @@
         </is>
       </c>
       <c r="N28">
+        <v>2.3</v>
+      </c>
+      <c r="O28">
         <v>2.62</v>
       </c>
-      <c r="O28">
-        <v>2.8</v>
-      </c>
       <c r="P28">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="Q28">
-        <v>3.8</v>
+        <v>3.14</v>
       </c>
       <c r="R28">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="S28">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="T28">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U28">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="V28">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W28">
         <v>1.03</v>
       </c>
       <c r="X28">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y28">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z28">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AA28">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AB28">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC28">
-        <v>6.62</v>
+        <v>7</v>
       </c>
       <c r="AD28">
         <v>1.11</v>
@@ -4930,7 +4930,7 @@
         <v>2.28</v>
       </c>
       <c r="AG28">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK28">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:00</t>
+          <t>2026-08-26 15:00:00</t>
         </is>
       </c>
     </row>
@@ -4989,27 +4989,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-08-26 16:00:00</t>
+          <t>2026-08-26 15:00:00</t>
         </is>
       </c>
     </row>
@@ -5152,27 +5152,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G30">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5232,16 +5232,16 @@
         <v>0</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-08-26 16:00:00</t>
+          <t>2026-08-26 15:00:00</t>
         </is>
       </c>
     </row>
@@ -5315,27 +5315,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G31">
@@ -5358,68 +5358,68 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>6.62</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-08-26 16:00:00</t>
+          <t>2026-08-26 15:30:00</t>
         </is>
       </c>
     </row>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G32">
@@ -5646,22 +5646,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G33">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G34">
@@ -5967,27 +5967,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G35">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-08-26 19:00:00</t>
+          <t>2026-08-26 16:00:00</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G36">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-08-26 19:30:00</t>
+          <t>2026-08-26 16:00:00</t>
         </is>
       </c>
     </row>
@@ -6293,27 +6293,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G37">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-08-26 21:00:00</t>
+          <t>2026-08-26 16:00:00</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G38">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-08-26 21:30:00</t>
+          <t>2026-08-26 19:00:00</t>
         </is>
       </c>
     </row>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,17 +6662,17 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P39">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6699,16 +6699,16 @@
         <v>0</v>
       </c>
       <c r="Y39">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-08-26 21:30:00</t>
+          <t>2026-08-26 19:30:00</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G40">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-08-26 22:00:00</t>
+          <t>2026-08-26 21:00:00</t>
         </is>
       </c>
     </row>
@@ -6945,156 +6945,645 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Blooming</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+      <c r="AA41">
+        <v>0</v>
+      </c>
+      <c r="AB41">
+        <v>0</v>
+      </c>
+      <c r="AC41">
+        <v>0</v>
+      </c>
+      <c r="AD41">
+        <v>0</v>
+      </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>0</v>
+      </c>
+      <c r="AG41">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>0</v>
+      </c>
+      <c r="AK41">
+        <v>0</v>
+      </c>
+      <c r="AL41">
+        <v>0</v>
+      </c>
+      <c r="AM41">
+        <v>-1</v>
+      </c>
+      <c r="AN41">
+        <v>-1</v>
+      </c>
+      <c r="AO41">
+        <v>-1</v>
+      </c>
+      <c r="AP41">
+        <v>-1</v>
+      </c>
+      <c r="AQ41">
+        <v>0</v>
+      </c>
+      <c r="AR41">
+        <v>0</v>
+      </c>
+      <c r="AS41">
+        <v>0</v>
+      </c>
+      <c r="AT41">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>2026-08-26 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Central Norte</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Deportivo Morón</t>
+        </is>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N42">
+        <v>3</v>
+      </c>
+      <c r="O42">
+        <v>2.68</v>
+      </c>
+      <c r="P42">
+        <v>2.5</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>1.71</v>
+      </c>
+      <c r="Z42">
+        <v>2</v>
+      </c>
+      <c r="AA42">
+        <v>3.4</v>
+      </c>
+      <c r="AB42">
+        <v>1.33</v>
+      </c>
+      <c r="AC42">
+        <v>0</v>
+      </c>
+      <c r="AD42">
+        <v>0</v>
+      </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>0</v>
+      </c>
+      <c r="AG42">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
+        <v>0</v>
+      </c>
+      <c r="AK42">
+        <v>0</v>
+      </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>-1</v>
+      </c>
+      <c r="AN42">
+        <v>-1</v>
+      </c>
+      <c r="AO42">
+        <v>-1</v>
+      </c>
+      <c r="AP42">
+        <v>-1</v>
+      </c>
+      <c r="AQ42">
+        <v>0</v>
+      </c>
+      <c r="AR42">
+        <v>0</v>
+      </c>
+      <c r="AS42">
+        <v>0</v>
+      </c>
+      <c r="AT42">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>2026-08-26 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Pittsburgh Riverhounds</t>
+        </is>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+      <c r="AA43">
+        <v>0</v>
+      </c>
+      <c r="AB43">
+        <v>0</v>
+      </c>
+      <c r="AC43">
+        <v>0</v>
+      </c>
+      <c r="AD43">
+        <v>0</v>
+      </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
+        <v>0</v>
+      </c>
+      <c r="AG43">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
+        <v>0</v>
+      </c>
+      <c r="AK43">
+        <v>0</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>-1</v>
+      </c>
+      <c r="AN43">
+        <v>-1</v>
+      </c>
+      <c r="AO43">
+        <v>-1</v>
+      </c>
+      <c r="AP43">
+        <v>-1</v>
+      </c>
+      <c r="AQ43">
+        <v>0</v>
+      </c>
+      <c r="AR43">
+        <v>0</v>
+      </c>
+      <c r="AS43">
+        <v>0</v>
+      </c>
+      <c r="AT43">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>2026-08-26 22:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>New Mexico United</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Lexington</t>
         </is>
       </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41" t="inlineStr">
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41">
-        <v>0</v>
-      </c>
-      <c r="P41">
-        <v>0</v>
-      </c>
-      <c r="Q41">
-        <v>0</v>
-      </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
-      <c r="S41">
-        <v>0</v>
-      </c>
-      <c r="T41">
-        <v>0</v>
-      </c>
-      <c r="U41">
-        <v>0</v>
-      </c>
-      <c r="V41">
-        <v>0</v>
-      </c>
-      <c r="W41">
-        <v>0</v>
-      </c>
-      <c r="X41">
-        <v>0</v>
-      </c>
-      <c r="Y41">
-        <v>0</v>
-      </c>
-      <c r="Z41">
-        <v>0</v>
-      </c>
-      <c r="AA41">
-        <v>0</v>
-      </c>
-      <c r="AB41">
-        <v>0</v>
-      </c>
-      <c r="AC41">
-        <v>0</v>
-      </c>
-      <c r="AD41">
-        <v>0</v>
-      </c>
-      <c r="AE41">
-        <v>0</v>
-      </c>
-      <c r="AF41">
-        <v>0</v>
-      </c>
-      <c r="AG41">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>0</v>
-      </c>
-      <c r="AK41">
-        <v>0</v>
-      </c>
-      <c r="AL41">
-        <v>0</v>
-      </c>
-      <c r="AM41">
-        <v>-1</v>
-      </c>
-      <c r="AN41">
-        <v>-1</v>
-      </c>
-      <c r="AO41">
-        <v>-1</v>
-      </c>
-      <c r="AP41">
-        <v>-1</v>
-      </c>
-      <c r="AQ41">
-        <v>0</v>
-      </c>
-      <c r="AR41">
-        <v>0</v>
-      </c>
-      <c r="AS41">
-        <v>0</v>
-      </c>
-      <c r="AT41">
-        <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+      <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+      <c r="AA44">
+        <v>0</v>
+      </c>
+      <c r="AB44">
+        <v>0</v>
+      </c>
+      <c r="AC44">
+        <v>0</v>
+      </c>
+      <c r="AD44">
+        <v>0</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>0</v>
+      </c>
+      <c r="AG44">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
+        <v>0</v>
+      </c>
+      <c r="AK44">
+        <v>0</v>
+      </c>
+      <c r="AL44">
+        <v>0</v>
+      </c>
+      <c r="AM44">
+        <v>-1</v>
+      </c>
+      <c r="AN44">
+        <v>-1</v>
+      </c>
+      <c r="AO44">
+        <v>-1</v>
+      </c>
+      <c r="AP44">
+        <v>-1</v>
+      </c>
+      <c r="AQ44">
+        <v>0</v>
+      </c>
+      <c r="AR44">
+        <v>0</v>
+      </c>
+      <c r="AS44">
+        <v>0</v>
+      </c>
+      <c r="AT44">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
         <is>
           <t>2026-08-26 22:30:00</t>
         </is>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G25">

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G21">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N27">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N31">

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G16">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G21">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G25">

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G20">

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G25">

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G21">

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="O29">
+        <v>2.65</v>
+      </c>
+      <c r="P29">
+        <v>3.2</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>1.63</v>
+      </c>
+      <c r="Z29">
+        <v>2.1</v>
+      </c>
+      <c r="AA29">
         <v>3.1</v>
       </c>
-      <c r="P29">
-        <v>5.5</v>
-      </c>
-      <c r="Q29">
-        <v>2.51</v>
-      </c>
-      <c r="R29">
-        <v>1.93</v>
-      </c>
-      <c r="S29">
-        <v>1.59</v>
-      </c>
-      <c r="T29">
-        <v>2.2</v>
-      </c>
-      <c r="U29">
-        <v>3.6</v>
-      </c>
-      <c r="V29">
-        <v>1.25</v>
-      </c>
-      <c r="W29">
-        <v>1</v>
-      </c>
-      <c r="X29">
-        <v>1.07</v>
-      </c>
-      <c r="Y29">
-        <v>1.6</v>
-      </c>
-      <c r="Z29">
-        <v>2.24</v>
-      </c>
-      <c r="AA29">
-        <v>2.63</v>
-      </c>
       <c r="AB29">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC29">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="O30">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="P30">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y30">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z30">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AA30">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="AB30">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL30">
         <v>0</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G2">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G4">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,80 +3569,80 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.95</v>
+        <v>1.58</v>
       </c>
       <c r="O20">
-        <v>3.95</v>
+        <v>4.55</v>
       </c>
       <c r="P20">
-        <v>2.14</v>
+        <v>4.15</v>
       </c>
       <c r="Q20">
-        <v>3.28</v>
+        <v>1.95</v>
       </c>
       <c r="R20">
-        <v>2.47</v>
+        <v>2.9</v>
       </c>
       <c r="S20">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T20">
-        <v>4.15</v>
+        <v>5.5</v>
       </c>
       <c r="U20">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="V20">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="W20">
+        <v>1.26</v>
+      </c>
+      <c r="X20">
+        <v>1</v>
+      </c>
+      <c r="Y20">
+        <v>1.06</v>
+      </c>
+      <c r="Z20">
+        <v>6.75</v>
+      </c>
+      <c r="AA20">
+        <v>1.26</v>
+      </c>
+      <c r="AB20">
+        <v>3.35</v>
+      </c>
+      <c r="AC20">
+        <v>1.68</v>
+      </c>
+      <c r="AD20">
+        <v>2.12</v>
+      </c>
+      <c r="AE20">
+        <v>1.5</v>
+      </c>
+      <c r="AF20">
+        <v>1.3</v>
+      </c>
+      <c r="AG20">
+        <v>3.2</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
         <v>1.16</v>
       </c>
-      <c r="X20">
-        <v>1.01</v>
-      </c>
-      <c r="Y20">
-        <v>1.11</v>
-      </c>
-      <c r="Z20">
-        <v>4.9</v>
-      </c>
-      <c r="AA20">
-        <v>1.33</v>
-      </c>
-      <c r="AB20">
-        <v>2.83</v>
-      </c>
-      <c r="AC20">
-        <v>2.04</v>
-      </c>
-      <c r="AD20">
-        <v>1.81</v>
-      </c>
-      <c r="AE20">
-        <v>1.3</v>
-      </c>
-      <c r="AF20">
-        <v>1.38</v>
-      </c>
-      <c r="AG20">
-        <v>2.8</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.25</v>
-      </c>
       <c r="AK20">
-        <v>1.36</v>
+        <v>1.98</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.58</v>
+        <v>2.95</v>
       </c>
       <c r="O21">
-        <v>4.55</v>
+        <v>3.95</v>
       </c>
       <c r="P21">
+        <v>2.14</v>
+      </c>
+      <c r="Q21">
+        <v>3.28</v>
+      </c>
+      <c r="R21">
+        <v>2.47</v>
+      </c>
+      <c r="S21">
+        <v>1.17</v>
+      </c>
+      <c r="T21">
         <v>4.15</v>
       </c>
-      <c r="Q21">
-        <v>1.95</v>
-      </c>
-      <c r="R21">
-        <v>2.9</v>
-      </c>
-      <c r="S21">
-        <v>1.13</v>
-      </c>
-      <c r="T21">
-        <v>5.5</v>
-      </c>
       <c r="U21">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="V21">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="W21">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="X21">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z21">
-        <v>6.75</v>
+        <v>4.9</v>
       </c>
       <c r="AA21">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AB21">
-        <v>3.35</v>
+        <v>2.83</v>
       </c>
       <c r="AC21">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="AD21">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="AE21">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AF21">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AG21">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.98</v>
+        <v>1.36</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G28">
@@ -4869,68 +4869,68 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N28">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O28">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P28">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q28">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Z28">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AA28">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB28">
         <v>1.36</v>
       </c>
       <c r="AC28">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK28">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="O29">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="P29">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y29">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z29">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AA29">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="AB29">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G30">
@@ -5195,65 +5195,65 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="O30">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="P30">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q30">
-        <v>2.51</v>
+        <v>3.14</v>
       </c>
       <c r="R30">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="S30">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="T30">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="U30">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="V30">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="W30">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X30">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Y30">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Z30">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AA30">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AB30">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC30">
-        <v>5.58</v>
+        <v>7</v>
       </c>
       <c r="AD30">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AE30">
         <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AG30">
         <v>1.55</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK30">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="AL30">
         <v>0</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.58</v>
+        <v>2.95</v>
       </c>
       <c r="O20">
-        <v>4.55</v>
+        <v>3.95</v>
       </c>
       <c r="P20">
+        <v>2.14</v>
+      </c>
+      <c r="Q20">
+        <v>3.28</v>
+      </c>
+      <c r="R20">
+        <v>2.47</v>
+      </c>
+      <c r="S20">
+        <v>1.17</v>
+      </c>
+      <c r="T20">
         <v>4.15</v>
       </c>
-      <c r="Q20">
-        <v>1.95</v>
-      </c>
-      <c r="R20">
-        <v>2.9</v>
-      </c>
-      <c r="S20">
-        <v>1.13</v>
-      </c>
-      <c r="T20">
-        <v>5.5</v>
-      </c>
       <c r="U20">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="V20">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="W20">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z20">
-        <v>6.75</v>
+        <v>4.9</v>
       </c>
       <c r="AA20">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AB20">
-        <v>3.35</v>
+        <v>2.83</v>
       </c>
       <c r="AC20">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="AD20">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="AE20">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AF20">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AG20">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.98</v>
+        <v>1.36</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,80 +3732,80 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.95</v>
+        <v>1.58</v>
       </c>
       <c r="O21">
-        <v>3.95</v>
+        <v>4.55</v>
       </c>
       <c r="P21">
-        <v>2.14</v>
+        <v>4.15</v>
       </c>
       <c r="Q21">
-        <v>3.28</v>
+        <v>1.95</v>
       </c>
       <c r="R21">
-        <v>2.47</v>
+        <v>2.9</v>
       </c>
       <c r="S21">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T21">
-        <v>4.15</v>
+        <v>5.5</v>
       </c>
       <c r="U21">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="V21">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="W21">
+        <v>1.26</v>
+      </c>
+      <c r="X21">
+        <v>1</v>
+      </c>
+      <c r="Y21">
+        <v>1.06</v>
+      </c>
+      <c r="Z21">
+        <v>6.75</v>
+      </c>
+      <c r="AA21">
+        <v>1.26</v>
+      </c>
+      <c r="AB21">
+        <v>3.35</v>
+      </c>
+      <c r="AC21">
+        <v>1.68</v>
+      </c>
+      <c r="AD21">
+        <v>2.12</v>
+      </c>
+      <c r="AE21">
+        <v>1.5</v>
+      </c>
+      <c r="AF21">
+        <v>1.3</v>
+      </c>
+      <c r="AG21">
+        <v>3.2</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
         <v>1.16</v>
       </c>
-      <c r="X21">
-        <v>1.01</v>
-      </c>
-      <c r="Y21">
-        <v>1.11</v>
-      </c>
-      <c r="Z21">
-        <v>4.9</v>
-      </c>
-      <c r="AA21">
-        <v>1.33</v>
-      </c>
-      <c r="AB21">
-        <v>2.83</v>
-      </c>
-      <c r="AC21">
-        <v>2.04</v>
-      </c>
-      <c r="AD21">
-        <v>1.81</v>
-      </c>
-      <c r="AE21">
-        <v>1.3</v>
-      </c>
-      <c r="AF21">
-        <v>1.38</v>
-      </c>
-      <c r="AG21">
-        <v>2.8</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.25</v>
-      </c>
       <c r="AK21">
-        <v>1.36</v>
+        <v>1.98</v>
       </c>
       <c r="AL21">
         <v>0</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -2274,10 +2274,10 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -2286,10 +2286,10 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W12">
         <v>0</v>
@@ -2298,31 +2298,31 @@
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G15">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>7.05</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL37">
         <v>0</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.52</v>
+        <v>1.96</v>
       </c>
       <c r="O33">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>6.55</v>
+        <v>3.74</v>
       </c>
       <c r="Q33">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="R33">
         <v>2.2</v>
       </c>
       <c r="S33">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="U33">
-        <v>2.97</v>
+        <v>2.6</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W33">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>2.86</v>
+        <v>3.65</v>
       </c>
       <c r="AA33">
+        <v>1.83</v>
+      </c>
+      <c r="AB33">
         <v>2.01</v>
       </c>
-      <c r="AB33">
-        <v>1.69</v>
-      </c>
       <c r="AC33">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="AD33">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE33">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF33">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AG33">
-        <v>1.64</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK33">
-        <v>2.32</v>
+        <v>1.85</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.38</v>
+        <v>1.52</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P34">
-        <v>2.75</v>
+        <v>6.55</v>
       </c>
       <c r="Q34">
+        <v>2</v>
+      </c>
+      <c r="R34">
+        <v>2.2</v>
+      </c>
+      <c r="S34">
+        <v>1.41</v>
+      </c>
+      <c r="T34">
         <v>2.88</v>
       </c>
-      <c r="R34">
-        <v>2.47</v>
-      </c>
-      <c r="S34">
-        <v>1.3</v>
-      </c>
-      <c r="T34">
-        <v>3.1</v>
-      </c>
       <c r="U34">
-        <v>2.27</v>
+        <v>2.97</v>
       </c>
       <c r="V34">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X34">
         <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="Z34">
-        <v>4</v>
+        <v>2.86</v>
       </c>
       <c r="AA34">
-        <v>1.7</v>
+        <v>2.01</v>
       </c>
       <c r="AB34">
-        <v>2.21</v>
+        <v>1.69</v>
       </c>
       <c r="AC34">
-        <v>2.48</v>
+        <v>3.9</v>
       </c>
       <c r="AD34">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AE34">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AF34">
-        <v>1.51</v>
+        <v>2.1</v>
       </c>
       <c r="AG34">
-        <v>2.25</v>
+        <v>1.64</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK34">
-        <v>1.53</v>
+        <v>2.32</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.96</v>
+        <v>2.38</v>
       </c>
       <c r="O35">
         <v>3.6</v>
       </c>
       <c r="P35">
-        <v>3.74</v>
+        <v>2.75</v>
       </c>
       <c r="Q35">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="R35">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="S35">
         <v>1.3</v>
       </c>
       <c r="T35">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="U35">
-        <v>2.6</v>
+        <v>2.27</v>
       </c>
       <c r="V35">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X35">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
         <v>1.22</v>
       </c>
       <c r="Z35">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="AA35">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AB35">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="AC35">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="AD35">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE35">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF35">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="AG35">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK35">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL38">
         <v>0</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G25">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.44</v>
+        <v>1.96</v>
       </c>
       <c r="O32">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="P32">
-        <v>2.7</v>
+        <v>3.74</v>
       </c>
       <c r="Q32">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="R32">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="U32">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="V32">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
         <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>3.49</v>
+        <v>3.65</v>
       </c>
       <c r="AA32">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB32">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AC32">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="AD32">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE32">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF32">
         <v>1.67</v>
       </c>
       <c r="AG32">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK32">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.96</v>
+        <v>2.38</v>
       </c>
       <c r="O33">
         <v>3.6</v>
       </c>
       <c r="P33">
-        <v>3.74</v>
+        <v>2.75</v>
       </c>
       <c r="Q33">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="R33">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="S33">
         <v>1.3</v>
       </c>
       <c r="T33">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="U33">
-        <v>2.6</v>
+        <v>2.27</v>
       </c>
       <c r="V33">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
         <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="AA33">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AB33">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="AC33">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="AD33">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE33">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF33">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="O35">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="P35">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q35">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R35">
-        <v>2.47</v>
+        <v>2.07</v>
       </c>
       <c r="S35">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T35">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U35">
-        <v>2.27</v>
+        <v>2.78</v>
       </c>
       <c r="V35">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="W35">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y35">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z35">
-        <v>4</v>
+        <v>3.49</v>
       </c>
       <c r="AA35">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB35">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="AC35">
-        <v>2.48</v>
+        <v>3.24</v>
       </c>
       <c r="AD35">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AE35">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AF35">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="AG35">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AK35">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AL35">
         <v>0</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="O28">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="P28">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y28">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z28">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AA28">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="AB28">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="O29">
+        <v>2.65</v>
+      </c>
+      <c r="P29">
+        <v>3.2</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>1.63</v>
+      </c>
+      <c r="Z29">
+        <v>2.1</v>
+      </c>
+      <c r="AA29">
         <v>3.1</v>
       </c>
-      <c r="P29">
-        <v>5.5</v>
-      </c>
-      <c r="Q29">
-        <v>2.51</v>
-      </c>
-      <c r="R29">
-        <v>1.93</v>
-      </c>
-      <c r="S29">
-        <v>1.59</v>
-      </c>
-      <c r="T29">
-        <v>2.2</v>
-      </c>
-      <c r="U29">
-        <v>3.6</v>
-      </c>
-      <c r="V29">
-        <v>1.25</v>
-      </c>
-      <c r="W29">
-        <v>1</v>
-      </c>
-      <c r="X29">
-        <v>1.07</v>
-      </c>
-      <c r="Y29">
-        <v>1.6</v>
-      </c>
-      <c r="Z29">
-        <v>2.24</v>
-      </c>
-      <c r="AA29">
-        <v>2.63</v>
-      </c>
       <c r="AB29">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC29">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,65 +5851,65 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.52</v>
+        <v>2.44</v>
       </c>
       <c r="O34">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="P34">
-        <v>6.55</v>
+        <v>2.7</v>
       </c>
       <c r="Q34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S34">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U34">
-        <v>2.97</v>
+        <v>2.78</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W34">
+        <v>1.06</v>
+      </c>
+      <c r="X34">
+        <v>1</v>
+      </c>
+      <c r="Y34">
+        <v>1.28</v>
+      </c>
+      <c r="Z34">
+        <v>3.49</v>
+      </c>
+      <c r="AA34">
+        <v>1.95</v>
+      </c>
+      <c r="AB34">
+        <v>1.83</v>
+      </c>
+      <c r="AC34">
+        <v>3.24</v>
+      </c>
+      <c r="AD34">
+        <v>1.29</v>
+      </c>
+      <c r="AE34">
         <v>1.05</v>
       </c>
-      <c r="X34">
-        <v>1.04</v>
-      </c>
-      <c r="Y34">
-        <v>1.34</v>
-      </c>
-      <c r="Z34">
-        <v>2.86</v>
-      </c>
-      <c r="AA34">
-        <v>2.01</v>
-      </c>
-      <c r="AB34">
-        <v>1.69</v>
-      </c>
-      <c r="AC34">
-        <v>3.9</v>
-      </c>
-      <c r="AD34">
-        <v>1.28</v>
-      </c>
-      <c r="AE34">
-        <v>1.09</v>
-      </c>
       <c r="AF34">
+        <v>1.67</v>
+      </c>
+      <c r="AG34">
         <v>2.1</v>
       </c>
-      <c r="AG34">
-        <v>1.64</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AK34">
-        <v>2.32</v>
+        <v>1.58</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.44</v>
+        <v>1.52</v>
       </c>
       <c r="O35">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="P35">
-        <v>2.7</v>
+        <v>6.55</v>
       </c>
       <c r="Q35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R35">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="S35">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T35">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U35">
-        <v>2.78</v>
+        <v>2.97</v>
       </c>
       <c r="V35">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X35">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
+        <v>1.34</v>
+      </c>
+      <c r="Z35">
+        <v>2.86</v>
+      </c>
+      <c r="AA35">
+        <v>2.01</v>
+      </c>
+      <c r="AB35">
+        <v>1.69</v>
+      </c>
+      <c r="AC35">
+        <v>3.9</v>
+      </c>
+      <c r="AD35">
         <v>1.28</v>
       </c>
-      <c r="Z35">
-        <v>3.49</v>
-      </c>
-      <c r="AA35">
-        <v>1.95</v>
-      </c>
-      <c r="AB35">
-        <v>1.83</v>
-      </c>
-      <c r="AC35">
-        <v>3.24</v>
-      </c>
-      <c r="AD35">
-        <v>1.29</v>
-      </c>
       <c r="AE35">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF35">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AG35">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AK35">
-        <v>1.58</v>
+        <v>2.32</v>
       </c>
       <c r="AL35">
         <v>0</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="AK12">
         <v>1.21</v>
@@ -2434,10 +2434,10 @@
         <v>3.92</v>
       </c>
       <c r="P13">
-        <v>3.63</v>
+        <v>3.05</v>
       </c>
       <c r="Q13">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="R13">
         <v>2.39</v>
@@ -2446,13 +2446,13 @@
         <v>1.25</v>
       </c>
       <c r="T13">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U13">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V13">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W13">
         <v>1.15</v>
@@ -2464,28 +2464,28 @@
         <v>1.1</v>
       </c>
       <c r="Z13">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AA13">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AB13">
         <v>2.4</v>
       </c>
       <c r="AC13">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AD13">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE13">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF13">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG13">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,34 +2591,34 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="O14">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="P14">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="Q14">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="R14">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="S14">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T14">
         <v>2.6</v>
       </c>
       <c r="U14">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="V14">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
         <v>1.05</v>
@@ -2627,16 +2627,16 @@
         <v>1.39</v>
       </c>
       <c r="Z14">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="AA14">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="AB14">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC14">
-        <v>3.96</v>
+        <v>4.23</v>
       </c>
       <c r="AD14">
         <v>1.17</v>
@@ -2645,10 +2645,10 @@
         <v>1.03</v>
       </c>
       <c r="AF14">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG14">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="AK14">
         <v>1.28</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="O16">
         <v>6.05</v>
@@ -2926,31 +2926,31 @@
         <v>8.25</v>
       </c>
       <c r="Q16">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="R16">
         <v>3.1</v>
       </c>
       <c r="S16">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T16">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U16">
         <v>1.8</v>
       </c>
       <c r="V16">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="W16">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X16">
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z16">
         <v>8.5</v>
@@ -2959,16 +2959,16 @@
         <v>1.25</v>
       </c>
       <c r="AB16">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AC16">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AD16">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AE16">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AF16">
         <v>1.5</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK16">
         <v>3.6</v>
@@ -3083,31 +3083,31 @@
         <v>1.4</v>
       </c>
       <c r="O17">
-        <v>5.15</v>
+        <v>5.35</v>
       </c>
       <c r="P17">
-        <v>5.15</v>
+        <v>5.65</v>
       </c>
       <c r="Q17">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R17">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="S17">
         <v>1.12</v>
       </c>
       <c r="T17">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="U17">
         <v>1.72</v>
       </c>
       <c r="V17">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="W17">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X17">
         <v>1</v>
@@ -3116,22 +3116,22 @@
         <v>1.02</v>
       </c>
       <c r="Z17">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="AA17">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AB17">
-        <v>4.03</v>
+        <v>4.11</v>
       </c>
       <c r="AC17">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AD17">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="AE17">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AF17">
         <v>1.27</v>
@@ -3153,7 +3153,7 @@
         <v>1.11</v>
       </c>
       <c r="AK17">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,40 +3243,40 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="O18">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P18">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q18">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="R18">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="S18">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T18">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="U18">
         <v>1.73</v>
       </c>
       <c r="V18">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="W18">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z18">
         <v>8</v>
@@ -3285,22 +3285,22 @@
         <v>1.29</v>
       </c>
       <c r="AB18">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AC18">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AD18">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AE18">
         <v>1.44</v>
       </c>
       <c r="AF18">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AG18">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="O19">
         <v>4.05</v>
       </c>
       <c r="P19">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="Q19">
         <v>2.75</v>
@@ -3421,13 +3421,13 @@
         <v>2.7</v>
       </c>
       <c r="S19">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T19">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="U19">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="V19">
         <v>1.91</v>
@@ -3439,28 +3439,28 @@
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z19">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AA19">
         <v>1.3</v>
       </c>
       <c r="AB19">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="AC19">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AD19">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AE19">
         <v>1.46</v>
       </c>
       <c r="AF19">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AG19">
         <v>3.2</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
         <v>1.44</v>
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="O20">
         <v>3.95</v>
       </c>
       <c r="P20">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="Q20">
-        <v>3.28</v>
+        <v>3.37</v>
       </c>
       <c r="R20">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="S20">
         <v>1.17</v>
       </c>
       <c r="T20">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="U20">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="V20">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="W20">
         <v>1.16</v>
@@ -3602,28 +3602,28 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z20">
         <v>4.9</v>
       </c>
       <c r="AA20">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB20">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AC20">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AD20">
         <v>1.81</v>
       </c>
       <c r="AE20">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AF20">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AG20">
         <v>2.8</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK20">
         <v>1.36</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="O21">
         <v>4.55</v>
@@ -3741,10 +3741,10 @@
         <v>4.15</v>
       </c>
       <c r="Q21">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R21">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="S21">
         <v>1.13</v>
@@ -3753,28 +3753,28 @@
         <v>5.5</v>
       </c>
       <c r="U21">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="V21">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="W21">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="X21">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z21">
-        <v>6.75</v>
+        <v>7.4</v>
       </c>
       <c r="AA21">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AB21">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="AC21">
         <v>1.68</v>
@@ -3783,13 +3783,13 @@
         <v>2.12</v>
       </c>
       <c r="AE21">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AF21">
         <v>1.3</v>
       </c>
       <c r="AG21">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.16</v>
       </c>
       <c r="AK21">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4713,10 +4713,10 @@
         <v>2.28</v>
       </c>
       <c r="O27">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="P27">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="Q27">
         <v>3.2</v>
@@ -4725,13 +4725,13 @@
         <v>1.73</v>
       </c>
       <c r="S27">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="T27">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="U27">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="V27">
         <v>1.2</v>
@@ -4743,19 +4743,19 @@
         <v>1.1</v>
       </c>
       <c r="Y27">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="Z27">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="AA27">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="AB27">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC27">
-        <v>5.7</v>
+        <v>6.35</v>
       </c>
       <c r="AD27">
         <v>1.08</v>
@@ -4767,7 +4767,7 @@
         <v>2.38</v>
       </c>
       <c r="AG27">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.36</v>
       </c>
       <c r="AK27">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,28 +4873,28 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.67</v>
+        <v>1.19</v>
       </c>
       <c r="O28">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P28">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q28">
-        <v>2.51</v>
+        <v>2.31</v>
       </c>
       <c r="R28">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="S28">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="T28">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="U28">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="V28">
         <v>1.25</v>
@@ -4903,31 +4903,31 @@
         <v>1</v>
       </c>
       <c r="X28">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y28">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Z28">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AA28">
         <v>2.63</v>
       </c>
       <c r="AB28">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC28">
-        <v>5.58</v>
+        <v>5.5</v>
       </c>
       <c r="AD28">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AE28">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF28">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AG28">
         <v>1.55</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK28">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G29">
@@ -5032,68 +5032,68 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O29">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="P29">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y29">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Z29">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AA29">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="AB29">
         <v>1.36</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G30">
@@ -5195,68 +5195,68 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="O30">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="P30">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="Q30">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="V30">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W30">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X30">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Z30">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AA30">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB30">
         <v>1.36</v>
       </c>
       <c r="AC30">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK30">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="O31">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="P31">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q31">
         <v>3.8</v>
@@ -5380,7 +5380,7 @@
         <v>1.65</v>
       </c>
       <c r="T31">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U31">
         <v>4</v>
@@ -5395,25 +5395,25 @@
         <v>1.1</v>
       </c>
       <c r="Y31">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Z31">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="AA31">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AB31">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC31">
-        <v>6.62</v>
+        <v>6.5</v>
       </c>
       <c r="AD31">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF31">
         <v>2.28</v>
@@ -5435,7 +5435,7 @@
         <v>1.35</v>
       </c>
       <c r="AK31">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O32">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P32">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="Q32">
         <v>2.45</v>
@@ -5540,10 +5540,10 @@
         <v>2.2</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T32">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="U32">
         <v>2.6</v>
@@ -5552,7 +5552,7 @@
         <v>1.46</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
         <v>1</v>
@@ -5567,13 +5567,13 @@
         <v>1.83</v>
       </c>
       <c r="AB32">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AC32">
         <v>3</v>
       </c>
       <c r="AD32">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE32">
         <v>1.14</v>
@@ -5598,7 +5598,7 @@
         <v>1.3</v>
       </c>
       <c r="AK32">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5700,19 +5700,19 @@
         <v>2.88</v>
       </c>
       <c r="R33">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T33">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U33">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="V33">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="W33">
         <v>1.11</v>
@@ -5721,19 +5721,19 @@
         <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z33">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="AA33">
         <v>1.7</v>
       </c>
       <c r="AB33">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AC33">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="AD33">
         <v>1.42</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.46</v>
       </c>
       <c r="AK33">
         <v>1.53</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="O34">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="P34">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q34">
         <v>3</v>
@@ -5875,7 +5875,7 @@
         <v>2.78</v>
       </c>
       <c r="V34">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
         <v>1.06</v>
@@ -5884,7 +5884,7 @@
         <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z34">
         <v>3.49</v>
@@ -5893,22 +5893,22 @@
         <v>1.95</v>
       </c>
       <c r="AB34">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC34">
         <v>3.24</v>
       </c>
       <c r="AD34">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE34">
         <v>1.05</v>
       </c>
       <c r="AF34">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG34">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6014,28 +6014,28 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="O35">
         <v>4</v>
       </c>
       <c r="P35">
-        <v>6.55</v>
+        <v>6</v>
       </c>
       <c r="Q35">
         <v>2</v>
       </c>
       <c r="R35">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S35">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T35">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U35">
-        <v>2.97</v>
+        <v>2.89</v>
       </c>
       <c r="V35">
         <v>1.36</v>
@@ -6047,31 +6047,31 @@
         <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z35">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="AA35">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AB35">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AC35">
-        <v>3.9</v>
+        <v>3.52</v>
       </c>
       <c r="AD35">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE35">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF35">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AG35">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="O37">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="P37">
-        <v>7.05</v>
+        <v>6.5</v>
       </c>
       <c r="Q37">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="R37">
         <v>2.5</v>
@@ -6358,7 +6358,7 @@
         <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="U37">
         <v>2.2</v>
@@ -6367,7 +6367,7 @@
         <v>1.6</v>
       </c>
       <c r="W37">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X37">
         <v>1.02</v>
@@ -6376,28 +6376,28 @@
         <v>1.11</v>
       </c>
       <c r="Z37">
-        <v>4.85</v>
+        <v>4.95</v>
       </c>
       <c r="AA37">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB37">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AC37">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AD37">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AE37">
         <v>1.2</v>
       </c>
       <c r="AF37">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AG37">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK37">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6518,16 +6518,16 @@
         <v>2.05</v>
       </c>
       <c r="S38">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T38">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="U38">
         <v>2.65</v>
       </c>
       <c r="V38">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W38">
         <v>1.08</v>
@@ -6545,7 +6545,7 @@
         <v>1.85</v>
       </c>
       <c r="AB38">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC38">
         <v>3.1</v>
@@ -6554,10 +6554,10 @@
         <v>1.3</v>
       </c>
       <c r="AE38">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF38">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AG38">
         <v>2.1</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK38">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="O42">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="P42">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,55 +7490,55 @@
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL44">
         <v>0</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="O13">
-        <v>3.92</v>
+        <v>3.48</v>
       </c>
       <c r="P13">
         <v>3.05</v>
       </c>
       <c r="Q13">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="R13">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="S13">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T13">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U13">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="V13">
         <v>1.63</v>
       </c>
       <c r="W13">
+        <v>1.13</v>
+      </c>
+      <c r="X13">
+        <v>1.01</v>
+      </c>
+      <c r="Y13">
         <v>1.15</v>
       </c>
-      <c r="X13">
-        <v>1.03</v>
-      </c>
-      <c r="Y13">
-        <v>1.1</v>
-      </c>
       <c r="Z13">
-        <v>4.7</v>
+        <v>5.05</v>
       </c>
       <c r="AA13">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB13">
         <v>2.4</v>
       </c>
       <c r="AC13">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AD13">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AE13">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AF13">
         <v>1.44</v>
       </c>
       <c r="AG13">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK13">
         <v>1.85</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O14">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P14">
         <v>2.25</v>
@@ -2603,22 +2603,22 @@
         <v>3.8</v>
       </c>
       <c r="R14">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="S14">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T14">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="U14">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="V14">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
         <v>1.05</v>
@@ -2636,16 +2636,16 @@
         <v>1.53</v>
       </c>
       <c r="AC14">
-        <v>4.23</v>
+        <v>4.33</v>
       </c>
       <c r="AD14">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE14">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF14">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG14">
         <v>1.75</v>
@@ -2760,49 +2760,49 @@
         <v>2.3</v>
       </c>
       <c r="P15">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="Q15">
         <v>3.6</v>
       </c>
       <c r="R15">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="S15">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="T15">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="U15">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="V15">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X15">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Y15">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="Z15">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="AA15">
-        <v>2.69</v>
+        <v>2.35</v>
       </c>
       <c r="AB15">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AC15">
         <v>4.93</v>
       </c>
       <c r="AD15">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE15">
         <v>1.02</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AK15">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="O16">
         <v>6.05</v>
       </c>
       <c r="P16">
-        <v>8.25</v>
+        <v>6.9</v>
       </c>
       <c r="Q16">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="R16">
         <v>3.1</v>
@@ -2938,28 +2938,28 @@
         <v>5</v>
       </c>
       <c r="U16">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="V16">
         <v>1.98</v>
       </c>
       <c r="W16">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X16">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z16">
         <v>8.5</v>
       </c>
       <c r="AA16">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB16">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AC16">
         <v>1.63</v>
@@ -2968,13 +2968,13 @@
         <v>2.03</v>
       </c>
       <c r="AE16">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AF16">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG16">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.08</v>
       </c>
       <c r="AK16">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,34 +3080,34 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="O17">
-        <v>5.35</v>
+        <v>4.8</v>
       </c>
       <c r="P17">
-        <v>5.65</v>
+        <v>4.65</v>
       </c>
       <c r="Q17">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="R17">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="S17">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="T17">
         <v>4.95</v>
       </c>
       <c r="U17">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="V17">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="W17">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X17">
         <v>1</v>
@@ -3116,22 +3116,22 @@
         <v>1.02</v>
       </c>
       <c r="Z17">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
       <c r="AA17">
         <v>1.22</v>
       </c>
       <c r="AB17">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="AC17">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AD17">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="AE17">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AF17">
         <v>1.27</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK17">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,28 +3243,28 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O18">
-        <v>4.1</v>
+        <v>3.83</v>
       </c>
       <c r="P18">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="Q18">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="R18">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="S18">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T18">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="U18">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="V18">
         <v>1.95</v>
@@ -3276,31 +3276,31 @@
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z18">
         <v>8</v>
       </c>
       <c r="AA18">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB18">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="AC18">
         <v>1.7</v>
       </c>
       <c r="AD18">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AE18">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AF18">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AG18">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK18">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,19 +3406,19 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="O19">
-        <v>4.05</v>
+        <v>3.78</v>
       </c>
       <c r="P19">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="Q19">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="R19">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="S19">
         <v>1.15</v>
@@ -3427,37 +3427,37 @@
         <v>5</v>
       </c>
       <c r="U19">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="V19">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="W19">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Z19">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AA19">
         <v>1.3</v>
       </c>
       <c r="AB19">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AC19">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AD19">
         <v>1.97</v>
       </c>
       <c r="AE19">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AF19">
         <v>1.3</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AK19">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.83</v>
+        <v>2.45</v>
       </c>
       <c r="O20">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="P20">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="Q20">
-        <v>3.37</v>
+        <v>3.15</v>
       </c>
       <c r="R20">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="S20">
         <v>1.17</v>
       </c>
       <c r="T20">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="U20">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="V20">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="W20">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Z20">
-        <v>4.9</v>
+        <v>6.25</v>
       </c>
       <c r="AA20">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB20">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="AC20">
         <v>1.98</v>
       </c>
       <c r="AD20">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="AE20">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AF20">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AG20">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
         <v>1.36</v>
@@ -3732,31 +3732,31 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="O21">
-        <v>4.55</v>
+        <v>4.3</v>
       </c>
       <c r="P21">
-        <v>4.15</v>
+        <v>3.65</v>
       </c>
       <c r="Q21">
         <v>1.93</v>
       </c>
       <c r="R21">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="S21">
         <v>1.13</v>
       </c>
       <c r="T21">
-        <v>5.5</v>
+        <v>4.65</v>
       </c>
       <c r="U21">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="V21">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="W21">
         <v>1.29</v>
@@ -3765,31 +3765,31 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z21">
-        <v>7.4</v>
+        <v>6.75</v>
       </c>
       <c r="AA21">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AB21">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AC21">
         <v>1.68</v>
       </c>
       <c r="AD21">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AE21">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AF21">
         <v>1.3</v>
       </c>
       <c r="AG21">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK21">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="O37">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="P37">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="Q37">
         <v>1.8</v>
@@ -6355,13 +6355,13 @@
         <v>2.5</v>
       </c>
       <c r="S37">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T37">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="U37">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V37">
         <v>1.6</v>
@@ -6370,34 +6370,34 @@
         <v>1.18</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z37">
         <v>4.95</v>
       </c>
       <c r="AA37">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB37">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AC37">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="AD37">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AE37">
         <v>1.2</v>
       </c>
       <c r="AF37">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AG37">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -7327,10 +7327,10 @@
         <v>3.3</v>
       </c>
       <c r="Q43">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="R43">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="S43">
         <v>1.46</v>
@@ -7351,31 +7351,31 @@
         <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="Z43">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AA43">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AB43">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AC43">
-        <v>4.22</v>
+        <v>3.15</v>
       </c>
       <c r="AD43">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AE43">
         <v>1.01</v>
       </c>
       <c r="AF43">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AG43">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK43">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7508,37 +7508,37 @@
         <v>1.43</v>
       </c>
       <c r="W44">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z44">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA44">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AB44">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="AC44">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="AD44">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AE44">
         <v>1.13</v>
       </c>
       <c r="AF44">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AG44">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK44">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AL44">
         <v>0</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.48</v>
+        <v>3.1</v>
       </c>
       <c r="O2">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="P2">
-        <v>6</v>
+        <v>2.15</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.25</v>
+        <v>1.49</v>
       </c>
       <c r="O3">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="P3">
-        <v>2.62</v>
+        <v>5.6</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="O4">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="O17">
-        <v>4.8</v>
+        <v>3.83</v>
       </c>
       <c r="P17">
-        <v>4.65</v>
+        <v>2.18</v>
       </c>
       <c r="Q17">
-        <v>1.78</v>
+        <v>2.56</v>
       </c>
       <c r="R17">
-        <v>3.1</v>
+        <v>2.61</v>
       </c>
       <c r="S17">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T17">
-        <v>4.95</v>
+        <v>4.6</v>
       </c>
       <c r="U17">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="V17">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="W17">
+        <v>1.24</v>
+      </c>
+      <c r="X17">
+        <v>1.01</v>
+      </c>
+      <c r="Y17">
+        <v>1.05</v>
+      </c>
+      <c r="Z17">
+        <v>8</v>
+      </c>
+      <c r="AA17">
         <v>1.3</v>
       </c>
-      <c r="X17">
-        <v>1</v>
-      </c>
-      <c r="Y17">
-        <v>1.02</v>
-      </c>
-      <c r="Z17">
-        <v>8.9</v>
-      </c>
-      <c r="AA17">
-        <v>1.22</v>
-      </c>
       <c r="AB17">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AC17">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AD17">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="AE17">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="AF17">
         <v>1.27</v>
       </c>
       <c r="AG17">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AK17">
-        <v>2.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="O18">
-        <v>3.83</v>
+        <v>3.78</v>
       </c>
       <c r="P18">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="Q18">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="R18">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="S18">
         <v>1.15</v>
       </c>
       <c r="T18">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="U18">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="V18">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="W18">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z18">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AA18">
         <v>1.3</v>
       </c>
       <c r="AB18">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AC18">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AD18">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="AE18">
+        <v>1.4</v>
+      </c>
+      <c r="AF18">
+        <v>1.3</v>
+      </c>
+      <c r="AG18">
+        <v>3.2</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.57</v>
+      </c>
+      <c r="AK18">
         <v>1.43</v>
-      </c>
-      <c r="AF18">
-        <v>1.27</v>
-      </c>
-      <c r="AG18">
-        <v>3.48</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.19</v>
-      </c>
-      <c r="AK18">
-        <v>1.53</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="O19">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="P19">
         <v>2.02</v>
       </c>
       <c r="Q19">
-        <v>2.67</v>
+        <v>3.15</v>
       </c>
       <c r="R19">
-        <v>2.58</v>
+        <v>2.43</v>
       </c>
       <c r="S19">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>4.15</v>
       </c>
       <c r="U19">
-        <v>1.82</v>
+        <v>2.01</v>
       </c>
       <c r="V19">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="W19">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z19">
-        <v>7.2</v>
+        <v>6.25</v>
       </c>
       <c r="AA19">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AB19">
-        <v>3.28</v>
+        <v>2.87</v>
       </c>
       <c r="AC19">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="AD19">
-        <v>1.97</v>
+        <v>1.61</v>
       </c>
       <c r="AE19">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AF19">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AG19">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,34 +3569,34 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.45</v>
+        <v>1.48</v>
       </c>
       <c r="O20">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="P20">
-        <v>2.02</v>
+        <v>3.65</v>
       </c>
       <c r="Q20">
-        <v>3.15</v>
+        <v>1.93</v>
       </c>
       <c r="R20">
-        <v>2.43</v>
+        <v>2.8</v>
       </c>
       <c r="S20">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T20">
-        <v>4.15</v>
+        <v>4.65</v>
       </c>
       <c r="U20">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="V20">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="W20">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3605,44 +3605,44 @@
         <v>1.06</v>
       </c>
       <c r="Z20">
-        <v>6.25</v>
+        <v>6.75</v>
       </c>
       <c r="AA20">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AB20">
-        <v>2.87</v>
+        <v>4</v>
       </c>
       <c r="AC20">
+        <v>1.68</v>
+      </c>
+      <c r="AD20">
+        <v>2.06</v>
+      </c>
+      <c r="AE20">
+        <v>1.43</v>
+      </c>
+      <c r="AF20">
+        <v>1.3</v>
+      </c>
+      <c r="AG20">
+        <v>3.14</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>1.18</v>
+      </c>
+      <c r="AK20">
         <v>1.98</v>
-      </c>
-      <c r="AD20">
-        <v>1.61</v>
-      </c>
-      <c r="AE20">
-        <v>1.28</v>
-      </c>
-      <c r="AF20">
-        <v>1.38</v>
-      </c>
-      <c r="AG20">
-        <v>2.93</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.25</v>
-      </c>
-      <c r="AK20">
-        <v>1.36</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="O21">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="P21">
-        <v>3.65</v>
+        <v>4.65</v>
       </c>
       <c r="Q21">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="R21">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="S21">
         <v>1.13</v>
       </c>
       <c r="T21">
-        <v>4.65</v>
+        <v>4.95</v>
       </c>
       <c r="U21">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="V21">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="W21">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Z21">
-        <v>6.75</v>
+        <v>8.9</v>
       </c>
       <c r="AA21">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AB21">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AC21">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AD21">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="AE21">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AF21">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AG21">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK21">
-        <v>1.98</v>
+        <v>2.55</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="O27">
         <v>2.85</v>
       </c>
       <c r="P27">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="Q27">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="R27">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="S27">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="T27">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="U27">
-        <v>3.96</v>
+        <v>3.75</v>
       </c>
       <c r="V27">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W27">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X27">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y27">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="Z27">
-        <v>2.26</v>
+        <v>2.39</v>
       </c>
       <c r="AA27">
-        <v>3.1</v>
+        <v>2.49</v>
       </c>
       <c r="AB27">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AC27">
-        <v>6.35</v>
+        <v>4.2</v>
       </c>
       <c r="AD27">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE27">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF27">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AG27">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G28">
@@ -4869,65 +4869,65 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N28">
-        <v>1.19</v>
+        <v>2.35</v>
       </c>
       <c r="O28">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="P28">
-        <v>5.75</v>
+        <v>3.25</v>
       </c>
       <c r="Q28">
-        <v>2.31</v>
+        <v>3.14</v>
       </c>
       <c r="R28">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="S28">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="T28">
-        <v>2.37</v>
+        <v>2.08</v>
       </c>
       <c r="U28">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="V28">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="W28">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X28">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y28">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Z28">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AA28">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="AB28">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC28">
         <v>5.5</v>
       </c>
       <c r="AD28">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AE28">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF28">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="AG28">
         <v>1.55</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AK28">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G29">
@@ -5032,68 +5032,68 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="O29">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="P29">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="Q29">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V29">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W29">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X29">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Z29">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="AA29">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="AB29">
         <v>1.36</v>
       </c>
       <c r="AC29">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.23</v>
+        <v>1.19</v>
       </c>
       <c r="O30">
-        <v>2.48</v>
+        <v>5.35</v>
       </c>
       <c r="P30">
-        <v>3.38</v>
+        <v>5.75</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y30">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="Z30">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AA30">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="AB30">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="O31">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="P31">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="Q31">
         <v>3.8</v>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="O32">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P32">
         <v>3.7</v>
@@ -5537,7 +5537,7 @@
         <v>2.45</v>
       </c>
       <c r="R32">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S32">
         <v>1.35</v>
@@ -5546,40 +5546,40 @@
         <v>2.94</v>
       </c>
       <c r="U32">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="V32">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
         <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z32">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AA32">
         <v>1.83</v>
       </c>
       <c r="AB32">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC32">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD32">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE32">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF32">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG32">
         <v>2.05</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,19 +5688,19 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="O33">
         <v>3.6</v>
       </c>
       <c r="P33">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q33">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="R33">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
         <v>1.29</v>
@@ -5709,16 +5709,16 @@
         <v>3.25</v>
       </c>
       <c r="U33">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="V33">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W33">
         <v>1.11</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
         <v>1.16</v>
@@ -5727,25 +5727,25 @@
         <v>4.25</v>
       </c>
       <c r="AA33">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB33">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AC33">
         <v>2.63</v>
       </c>
       <c r="AD33">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE33">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF33">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG33">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AK33">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="O34">
-        <v>3.36</v>
+        <v>3.22</v>
       </c>
       <c r="P34">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="Q34">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="R34">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T34">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="U34">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W34">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z34">
-        <v>3.49</v>
+        <v>3.24</v>
       </c>
       <c r="AA34">
         <v>1.95</v>
       </c>
       <c r="AB34">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC34">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AD34">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AE34">
         <v>1.05</v>
       </c>
       <c r="AF34">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AK34">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,61 +6014,61 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="O35">
         <v>4</v>
       </c>
       <c r="P35">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="Q35">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R35">
         <v>2.15</v>
       </c>
       <c r="S35">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T35">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="U35">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="V35">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W35">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X35">
         <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z35">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="AA35">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AB35">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC35">
-        <v>3.52</v>
+        <v>3.73</v>
       </c>
       <c r="AD35">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE35">
         <v>1.04</v>
       </c>
       <c r="AF35">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AG35">
         <v>1.67</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK35">
         <v>2.38</v>
@@ -6340,37 +6340,37 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="O37">
-        <v>4.85</v>
+        <v>4.98</v>
       </c>
       <c r="P37">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="Q37">
         <v>1.8</v>
       </c>
       <c r="R37">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="S37">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T37">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="U37">
         <v>2.26</v>
       </c>
       <c r="V37">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W37">
         <v>1.18</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
         <v>1.15</v>
@@ -6379,25 +6379,25 @@
         <v>4.95</v>
       </c>
       <c r="AA37">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB37">
         <v>2.46</v>
       </c>
       <c r="AC37">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AD37">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AE37">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AF37">
         <v>1.74</v>
       </c>
       <c r="AG37">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AK37">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="O38">
         <v>3.1</v>
       </c>
       <c r="P38">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="Q38">
-        <v>2.63</v>
+        <v>2.77</v>
       </c>
       <c r="R38">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S38">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T38">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="U38">
         <v>2.65</v>
       </c>
       <c r="V38">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z38">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA38">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB38">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AC38">
         <v>3.1</v>
       </c>
       <c r="AD38">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE38">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF38">
         <v>1.69</v>
       </c>
       <c r="AG38">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK38">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7158,7 +7158,7 @@
         <v>2.91</v>
       </c>
       <c r="O42">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="P42">
         <v>2.65</v>
@@ -7327,25 +7327,25 @@
         <v>3.3</v>
       </c>
       <c r="Q43">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="R43">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="S43">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T43">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="U43">
         <v>3.18</v>
       </c>
       <c r="V43">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W43">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X43">
         <v>1.03</v>
@@ -7366,7 +7366,7 @@
         <v>3.15</v>
       </c>
       <c r="AD43">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AE43">
         <v>1.01</v>
@@ -7391,7 +7391,7 @@
         <v>1.26</v>
       </c>
       <c r="AK43">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7496,7 +7496,7 @@
         <v>2.08</v>
       </c>
       <c r="S44">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T44">
         <v>3.15</v>
@@ -7508,25 +7508,25 @@
         <v>1.43</v>
       </c>
       <c r="W44">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X44">
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z44">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AA44">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AB44">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AC44">
-        <v>2.81</v>
+        <v>2.97</v>
       </c>
       <c r="AD44">
         <v>1.37</v>
@@ -7535,7 +7535,7 @@
         <v>1.13</v>
       </c>
       <c r="AF44">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AG44">
         <v>2.12</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK44">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AL44">
         <v>0</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -641,58 +641,58 @@
         <v>3.1</v>
       </c>
       <c r="P2">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q2">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="R2">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S2">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="U2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W2">
+        <v>1.05</v>
+      </c>
+      <c r="X2">
         <v>1.01</v>
       </c>
-      <c r="X2">
-        <v>1.05</v>
-      </c>
       <c r="Y2">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z2">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="AA2">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AB2">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AC2">
         <v>3.84</v>
       </c>
       <c r="AD2">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE2">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF2">
         <v>1.85</v>
       </c>
       <c r="AG2">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK2">
         <v>1.3</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="O3">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q3">
-        <v>2.07</v>
+        <v>2.78</v>
       </c>
       <c r="R3">
         <v>2.3</v>
       </c>
       <c r="S3">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="U3">
-        <v>2.99</v>
+        <v>2.51</v>
       </c>
       <c r="V3">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="W3">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="Z3">
-        <v>2.94</v>
+        <v>4.44</v>
       </c>
       <c r="AA3">
-        <v>2.07</v>
+        <v>1.69</v>
       </c>
       <c r="AB3">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AC3">
-        <v>3.54</v>
+        <v>2.75</v>
       </c>
       <c r="AD3">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AE3">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="AG3">
-        <v>1.63</v>
+        <v>2.38</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AK3">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G4">
@@ -961,65 +961,65 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.25</v>
+        <v>1.52</v>
       </c>
       <c r="O4">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="P4">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="R4">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="S4">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="T4">
-        <v>3.28</v>
+        <v>2.55</v>
       </c>
       <c r="U4">
-        <v>2.51</v>
+        <v>3.12</v>
       </c>
       <c r="V4">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="Z4">
-        <v>4.15</v>
+        <v>3.14</v>
       </c>
       <c r="AA4">
-        <v>1.68</v>
+        <v>2.07</v>
       </c>
       <c r="AB4">
-        <v>2.14</v>
+        <v>1.73</v>
       </c>
       <c r="AC4">
-        <v>2.73</v>
+        <v>3.85</v>
       </c>
       <c r="AD4">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AE4">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF4">
+        <v>2.15</v>
+      </c>
+      <c r="AG4">
         <v>1.54</v>
       </c>
-      <c r="AG4">
-        <v>2.32</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK4">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="O13">
         <v>3.48</v>
       </c>
       <c r="P13">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="Q13">
         <v>2.31</v>
       </c>
       <c r="R13">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="S13">
         <v>1.22</v>
       </c>
       <c r="T13">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U13">
         <v>2.17</v>
@@ -2458,34 +2458,34 @@
         <v>1.13</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z13">
-        <v>5.05</v>
+        <v>4.7</v>
       </c>
       <c r="AA13">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AB13">
         <v>2.4</v>
       </c>
       <c r="AC13">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AD13">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AE13">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF13">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG13">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK13">
         <v>1.85</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="O14">
-        <v>2.87</v>
+        <v>2.35</v>
       </c>
       <c r="P14">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q14">
-        <v>3.8</v>
+        <v>4.04</v>
       </c>
       <c r="R14">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="S14">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="T14">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="U14">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="V14">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="W14">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X14">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Y14">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="Z14">
-        <v>2.9</v>
+        <v>2.39</v>
       </c>
       <c r="AA14">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AB14">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AC14">
-        <v>4.33</v>
+        <v>4.91</v>
       </c>
       <c r="AD14">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE14">
         <v>1.02</v>
       </c>
       <c r="AF14">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AG14">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AK14">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="O15">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="P15">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="Q15">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="R15">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="S15">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T15">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="U15">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="V15">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W15">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="Z15">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="AA15">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AB15">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AC15">
-        <v>4.93</v>
+        <v>4.33</v>
       </c>
       <c r="AD15">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE15">
         <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AG15">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AK15">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2932,16 +2932,16 @@
         <v>3.1</v>
       </c>
       <c r="S16">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T16">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="U16">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V16">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="W16">
         <v>1.25</v>
@@ -2950,16 +2950,16 @@
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z16">
         <v>8.5</v>
       </c>
       <c r="AA16">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AB16">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AC16">
         <v>1.63</v>
@@ -2968,13 +2968,13 @@
         <v>2.03</v>
       </c>
       <c r="AE16">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AF16">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG16">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3095,13 +3095,13 @@
         <v>2.61</v>
       </c>
       <c r="S17">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T17">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="U17">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="V17">
         <v>1.95</v>
@@ -3113,25 +3113,25 @@
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z17">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AA17">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AB17">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AC17">
         <v>1.7</v>
       </c>
       <c r="AD17">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AE17">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AF17">
         <v>1.27</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK17">
         <v>1.53</v>
@@ -3243,16 +3243,16 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="O18">
-        <v>3.78</v>
+        <v>4.05</v>
       </c>
       <c r="P18">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="Q18">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="R18">
         <v>2.58</v>
@@ -3264,13 +3264,13 @@
         <v>5</v>
       </c>
       <c r="U18">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="V18">
         <v>1.88</v>
       </c>
       <c r="W18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3282,10 +3282,10 @@
         <v>7.2</v>
       </c>
       <c r="AA18">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AB18">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="AC18">
         <v>1.76</v>
@@ -3294,10 +3294,10 @@
         <v>1.97</v>
       </c>
       <c r="AE18">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AF18">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AG18">
         <v>3.2</v>
@@ -3316,7 +3316,7 @@
         <v>1.57</v>
       </c>
       <c r="AK18">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,16 +3409,16 @@
         <v>2.45</v>
       </c>
       <c r="O19">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="P19">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="Q19">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="R19">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="S19">
         <v>1.17</v>
@@ -3427,13 +3427,13 @@
         <v>4.15</v>
       </c>
       <c r="U19">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="V19">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W19">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X19">
         <v>1.01</v>
@@ -3445,7 +3445,7 @@
         <v>6.25</v>
       </c>
       <c r="AA19">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB19">
         <v>2.87</v>
@@ -3460,10 +3460,10 @@
         <v>1.28</v>
       </c>
       <c r="AF19">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AG19">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AK19">
         <v>1.36</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="O20">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P20">
-        <v>3.65</v>
+        <v>4.15</v>
       </c>
       <c r="Q20">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R20">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="S20">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T20">
         <v>4.65</v>
       </c>
       <c r="U20">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="V20">
         <v>2.1</v>
       </c>
       <c r="W20">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z20">
         <v>6.75</v>
       </c>
       <c r="AA20">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AB20">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AC20">
         <v>1.68</v>
       </c>
       <c r="AD20">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AE20">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AF20">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AG20">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK20">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,37 +3732,37 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="O21">
         <v>4.8</v>
       </c>
       <c r="P21">
-        <v>4.65</v>
+        <v>5.82</v>
       </c>
       <c r="Q21">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="R21">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="S21">
         <v>1.13</v>
       </c>
       <c r="T21">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="U21">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="V21">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="W21">
         <v>1.3</v>
       </c>
       <c r="X21">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
         <v>1.02</v>
@@ -3771,16 +3771,16 @@
         <v>8.9</v>
       </c>
       <c r="AA21">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AB21">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AC21">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AD21">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AE21">
         <v>1.63</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK21">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4713,37 +4713,37 @@
         <v>2.14</v>
       </c>
       <c r="O27">
-        <v>2.85</v>
+        <v>2.67</v>
       </c>
       <c r="P27">
         <v>3.6</v>
       </c>
       <c r="Q27">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="R27">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="S27">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T27">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="U27">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="V27">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W27">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="Y27">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="Z27">
         <v>2.39</v>
@@ -4752,13 +4752,13 @@
         <v>2.49</v>
       </c>
       <c r="AB27">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AC27">
-        <v>4.2</v>
+        <v>5.33</v>
       </c>
       <c r="AD27">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE27">
         <v>1.01</v>
@@ -4767,7 +4767,7 @@
         <v>2.15</v>
       </c>
       <c r="AG27">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O28">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="P28">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="Q28">
         <v>3.14</v>
@@ -5042,7 +5042,7 @@
         <v>2.48</v>
       </c>
       <c r="P29">
-        <v>3.38</v>
+        <v>3.65</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="O30">
-        <v>5.35</v>
+        <v>2.8</v>
       </c>
       <c r="P30">
         <v>5.75</v>
@@ -5368,31 +5368,31 @@
         <v>2.8</v>
       </c>
       <c r="P31">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q31">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="R31">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="S31">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="T31">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="U31">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="V31">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W31">
         <v>1.03</v>
       </c>
       <c r="X31">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y31">
         <v>1.64</v>
@@ -5416,10 +5416,10 @@
         <v>1.01</v>
       </c>
       <c r="AF31">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AG31">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AK31">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,28 +5525,28 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="O32">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P32">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q32">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="R32">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S32">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="U32">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="V32">
         <v>1.44</v>
@@ -5555,31 +5555,31 @@
         <v>1.07</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y32">
         <v>1.27</v>
       </c>
       <c r="Z32">
-        <v>3.6</v>
+        <v>3.87</v>
       </c>
       <c r="AA32">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB32">
         <v>1.91</v>
       </c>
       <c r="AC32">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AD32">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE32">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF32">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG32">
         <v>2.05</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="O33">
         <v>3.6</v>
@@ -5697,7 +5697,7 @@
         <v>2.8</v>
       </c>
       <c r="Q33">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="R33">
         <v>2.3</v>
@@ -5709,43 +5709,43 @@
         <v>3.25</v>
       </c>
       <c r="U33">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="V33">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W33">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z33">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AA33">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB33">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AC33">
         <v>2.63</v>
       </c>
       <c r="AD33">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE33">
         <v>1.14</v>
       </c>
       <c r="AF33">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG33">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AK33">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O34">
         <v>3.22</v>
@@ -5860,7 +5860,7 @@
         <v>2.68</v>
       </c>
       <c r="Q34">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="R34">
         <v>2.18</v>
@@ -5869,34 +5869,34 @@
         <v>1.38</v>
       </c>
       <c r="T34">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="U34">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="V34">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
         <v>1.26</v>
       </c>
       <c r="Z34">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="AA34">
         <v>1.95</v>
       </c>
       <c r="AB34">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC34">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AD34">
         <v>1.25</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AK34">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,31 +6014,31 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="O35">
         <v>4</v>
       </c>
       <c r="P35">
-        <v>6.25</v>
+        <v>6.35</v>
       </c>
       <c r="Q35">
         <v>2.05</v>
       </c>
       <c r="R35">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S35">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="U35">
         <v>2.94</v>
       </c>
       <c r="V35">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W35">
         <v>1.03</v>
@@ -6047,28 +6047,28 @@
         <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z35">
         <v>2.99</v>
       </c>
       <c r="AA35">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AB35">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC35">
-        <v>3.73</v>
+        <v>3.55</v>
       </c>
       <c r="AD35">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE35">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG35">
         <v>1.67</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AK35">
         <v>2.38</v>
@@ -6340,22 +6340,22 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="O37">
-        <v>4.98</v>
+        <v>5.3</v>
       </c>
       <c r="P37">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="Q37">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R37">
         <v>2.65</v>
       </c>
       <c r="S37">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T37">
         <v>3.6</v>
@@ -6376,28 +6376,28 @@
         <v>1.15</v>
       </c>
       <c r="Z37">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA37">
         <v>1.5</v>
       </c>
       <c r="AB37">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AC37">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AD37">
+        <v>1.65</v>
+      </c>
+      <c r="AE37">
+        <v>1.25</v>
+      </c>
+      <c r="AF37">
         <v>1.7</v>
       </c>
-      <c r="AE37">
-        <v>1.23</v>
-      </c>
-      <c r="AF37">
-        <v>1.74</v>
-      </c>
       <c r="AG37">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.18</v>
       </c>
       <c r="AK37">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,28 +6503,28 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O38">
         <v>3.1</v>
       </c>
       <c r="P38">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q38">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="R38">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S38">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T38">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U38">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="V38">
         <v>1.42</v>
@@ -6533,34 +6533,34 @@
         <v>1.07</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y38">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z38">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA38">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AB38">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC38">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="AD38">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE38">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF38">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AG38">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.28</v>
       </c>
       <c r="AK38">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6838,55 +6838,55 @@
         <v>0</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7327,13 +7327,13 @@
         <v>3.3</v>
       </c>
       <c r="Q43">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="R43">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="S43">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T43">
         <v>2.63</v>
@@ -7363,7 +7363,7 @@
         <v>1.57</v>
       </c>
       <c r="AC43">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="AD43">
         <v>1.16</v>
@@ -7375,7 +7375,7 @@
         <v>1.92</v>
       </c>
       <c r="AG43">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK43">
         <v>1.62</v>
@@ -7493,52 +7493,52 @@
         <v>3.26</v>
       </c>
       <c r="R44">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="S44">
         <v>1.35</v>
       </c>
       <c r="T44">
-        <v>3.15</v>
+        <v>2.82</v>
       </c>
       <c r="U44">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="V44">
         <v>1.43</v>
       </c>
       <c r="W44">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z44">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA44">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AB44">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="AC44">
         <v>2.97</v>
       </c>
       <c r="AD44">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE44">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF44">
         <v>1.62</v>
       </c>
       <c r="AG44">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="AK44">
         <v>1.39</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -2265,37 +2265,37 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q12">
-        <v>3.8</v>
+        <v>4.19</v>
       </c>
       <c r="R12">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U12">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="V12">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12">
         <v>1.09</v>
@@ -2307,22 +2307,22 @@
         <v>1.4</v>
       </c>
       <c r="AB12">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AC12">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AD12">
         <v>1.64</v>
       </c>
       <c r="AE12">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF12">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG12">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK12">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="O14">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="P14">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q14">
-        <v>4.04</v>
+        <v>4.33</v>
       </c>
       <c r="R14">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="S14">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="T14">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="U14">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="V14">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W14">
         <v>1.01</v>
       </c>
       <c r="X14">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Y14">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="Z14">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="AA14">
         <v>2.35</v>
       </c>
       <c r="AB14">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AC14">
-        <v>4.91</v>
+        <v>4.5</v>
       </c>
       <c r="AD14">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE14">
         <v>1.02</v>
       </c>
       <c r="AF14">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AG14">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AK14">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2757,16 +2757,16 @@
         <v>3.25</v>
       </c>
       <c r="O15">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P15">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q15">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="R15">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="S15">
         <v>1.44</v>
@@ -2775,43 +2775,43 @@
         <v>2.62</v>
       </c>
       <c r="U15">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V15">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
         <v>1.06</v>
       </c>
       <c r="X15">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y15">
         <v>1.39</v>
       </c>
       <c r="Z15">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AA15">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AB15">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC15">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AD15">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF15">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AG15">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AK15">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="O37">
-        <v>5.3</v>
+        <v>4.75</v>
       </c>
       <c r="P37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q37">
         <v>1.75</v>
       </c>
       <c r="R37">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="S37">
         <v>1.24</v>
       </c>
       <c r="T37">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="U37">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V37">
         <v>1.64</v>
       </c>
       <c r="W37">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Z37">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA37">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB37">
-        <v>2.49</v>
+        <v>2.58</v>
       </c>
       <c r="AC37">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AD37">
         <v>1.65</v>
       </c>
       <c r="AE37">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF37">
         <v>1.7</v>
       </c>
       <c r="AG37">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK37">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AL37">
         <v>0</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>7.6</v>
+        <v>9.35</v>
       </c>
       <c r="O8">
-        <v>4.2</v>
+        <v>5.05</v>
       </c>
       <c r="P8">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="O13">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="P13">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="Q13">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="R13">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S13">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T13">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U13">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="V13">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W13">
         <v>1.13</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z13">
-        <v>4.7</v>
+        <v>5.25</v>
       </c>
       <c r="AA13">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AB13">
         <v>2.4</v>
       </c>
       <c r="AC13">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="AD13">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE13">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF13">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG13">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK13">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2917,25 +2917,25 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="O16">
-        <v>6.05</v>
+        <v>5.75</v>
       </c>
       <c r="P16">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="R16">
         <v>3.1</v>
       </c>
       <c r="S16">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="T16">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="U16">
         <v>1.8</v>
@@ -2950,31 +2950,31 @@
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z16">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA16">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB16">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AC16">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AD16">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AE16">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AF16">
         <v>1.5</v>
       </c>
       <c r="AG16">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3080,28 +3080,28 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O17">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="P17">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="Q17">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="R17">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="S17">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T17">
         <v>4.7</v>
       </c>
       <c r="U17">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V17">
         <v>1.95</v>
@@ -3113,31 +3113,31 @@
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z17">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AA17">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AB17">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AC17">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AD17">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AE17">
         <v>1.44</v>
       </c>
       <c r="AF17">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AG17">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK17">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="O18">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="P18">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q18">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="R18">
         <v>2.58</v>
       </c>
       <c r="S18">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T18">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="U18">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="V18">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="W18">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z18">
-        <v>7.2</v>
+        <v>8.5</v>
       </c>
       <c r="AA18">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB18">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="AC18">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AD18">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AE18">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AF18">
         <v>1.25</v>
       </c>
       <c r="AG18">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.57</v>
+        <v>1.19</v>
       </c>
       <c r="AK18">
         <v>1.44</v>
@@ -3406,46 +3406,46 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="O19">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="Q19">
         <v>3.36</v>
       </c>
       <c r="R19">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="S19">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T19">
         <v>4.15</v>
       </c>
       <c r="U19">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="V19">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="W19">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z19">
-        <v>6.25</v>
+        <v>6.17</v>
       </c>
       <c r="AA19">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB19">
         <v>2.87</v>
@@ -3454,16 +3454,16 @@
         <v>1.98</v>
       </c>
       <c r="AD19">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="AE19">
         <v>1.28</v>
       </c>
       <c r="AF19">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AG19">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AK19">
         <v>1.36</v>
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O20">
         <v>4.2</v>
       </c>
       <c r="P20">
-        <v>4.15</v>
+        <v>3.65</v>
       </c>
       <c r="Q20">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="R20">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="S20">
         <v>1.15</v>
       </c>
       <c r="T20">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="U20">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V20">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="W20">
         <v>1.25</v>
@@ -3605,28 +3605,28 @@
         <v>1.03</v>
       </c>
       <c r="Z20">
-        <v>6.75</v>
+        <v>8.5</v>
       </c>
       <c r="AA20">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AB20">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AC20">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AD20">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AE20">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AF20">
         <v>1.31</v>
       </c>
       <c r="AG20">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK20">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="O21">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="P21">
-        <v>5.82</v>
+        <v>4.6</v>
       </c>
       <c r="Q21">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="R21">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="S21">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T21">
         <v>5</v>
       </c>
       <c r="U21">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="V21">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="W21">
         <v>1.3</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z21">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="AA21">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AB21">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AC21">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AD21">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AE21">
         <v>1.63</v>
       </c>
       <c r="AF21">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AG21">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AK21">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G24">
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="O32">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="P32">
-        <v>3.75</v>
+        <v>2.84</v>
       </c>
       <c r="Q32">
-        <v>2.42</v>
+        <v>2.65</v>
       </c>
       <c r="R32">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="U32">
-        <v>2.56</v>
+        <v>2.29</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X32">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="Z32">
-        <v>3.87</v>
+        <v>4.55</v>
       </c>
       <c r="AA32">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="AB32">
-        <v>1.91</v>
+        <v>2.41</v>
       </c>
       <c r="AC32">
-        <v>2.97</v>
+        <v>2.45</v>
       </c>
       <c r="AD32">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="AE32">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF32">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AG32">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK32">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="P33">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="Q33">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="R33">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="S33">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="T33">
-        <v>3.25</v>
+        <v>2.59</v>
       </c>
       <c r="U33">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="V33">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="W33">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="Z33">
-        <v>4.3</v>
+        <v>3.22</v>
       </c>
       <c r="AA33">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AB33">
-        <v>2.31</v>
+        <v>1.66</v>
       </c>
       <c r="AC33">
-        <v>2.63</v>
+        <v>3.64</v>
       </c>
       <c r="AD33">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AE33">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AF33">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AG33">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AK33">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="O34">
-        <v>3.22</v>
+        <v>3.95</v>
       </c>
       <c r="P34">
-        <v>2.68</v>
+        <v>6.5</v>
       </c>
       <c r="Q34">
+        <v>2.05</v>
+      </c>
+      <c r="R34">
+        <v>2.1</v>
+      </c>
+      <c r="S34">
+        <v>1.36</v>
+      </c>
+      <c r="T34">
         <v>2.8</v>
       </c>
-      <c r="R34">
-        <v>2.18</v>
-      </c>
-      <c r="S34">
-        <v>1.38</v>
-      </c>
-      <c r="T34">
-        <v>3</v>
-      </c>
       <c r="U34">
-        <v>2.63</v>
+        <v>2.94</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X34">
+        <v>1.01</v>
+      </c>
+      <c r="Y34">
+        <v>1.35</v>
+      </c>
+      <c r="Z34">
+        <v>2.99</v>
+      </c>
+      <c r="AA34">
+        <v>2.05</v>
+      </c>
+      <c r="AB34">
+        <v>1.7</v>
+      </c>
+      <c r="AC34">
+        <v>3.75</v>
+      </c>
+      <c r="AD34">
+        <v>1.22</v>
+      </c>
+      <c r="AE34">
         <v>1.04</v>
       </c>
-      <c r="Y34">
-        <v>1.26</v>
-      </c>
-      <c r="Z34">
-        <v>3.25</v>
-      </c>
-      <c r="AA34">
-        <v>1.95</v>
-      </c>
-      <c r="AB34">
-        <v>1.87</v>
-      </c>
-      <c r="AC34">
-        <v>3.25</v>
-      </c>
-      <c r="AD34">
-        <v>1.25</v>
-      </c>
-      <c r="AE34">
-        <v>1.05</v>
-      </c>
       <c r="AF34">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AG34">
-        <v>1.96</v>
+        <v>1.64</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="AK34">
-        <v>1.55</v>
+        <v>2.38</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,65 +6014,65 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.54</v>
+        <v>1.9</v>
       </c>
       <c r="O35">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="P35">
-        <v>6.35</v>
+        <v>3.75</v>
       </c>
       <c r="Q35">
+        <v>2.41</v>
+      </c>
+      <c r="R35">
+        <v>2.2</v>
+      </c>
+      <c r="S35">
+        <v>1.3</v>
+      </c>
+      <c r="T35">
+        <v>3.26</v>
+      </c>
+      <c r="U35">
+        <v>2.56</v>
+      </c>
+      <c r="V35">
+        <v>1.44</v>
+      </c>
+      <c r="W35">
+        <v>1.07</v>
+      </c>
+      <c r="X35">
+        <v>1.03</v>
+      </c>
+      <c r="Y35">
+        <v>1.24</v>
+      </c>
+      <c r="Z35">
+        <v>3.7</v>
+      </c>
+      <c r="AA35">
+        <v>1.85</v>
+      </c>
+      <c r="AB35">
+        <v>1.95</v>
+      </c>
+      <c r="AC35">
+        <v>2.97</v>
+      </c>
+      <c r="AD35">
+        <v>1.38</v>
+      </c>
+      <c r="AE35">
+        <v>1.1</v>
+      </c>
+      <c r="AF35">
+        <v>1.7</v>
+      </c>
+      <c r="AG35">
         <v>2.05</v>
       </c>
-      <c r="R35">
-        <v>2.1</v>
-      </c>
-      <c r="S35">
-        <v>1.36</v>
-      </c>
-      <c r="T35">
-        <v>2.65</v>
-      </c>
-      <c r="U35">
-        <v>2.94</v>
-      </c>
-      <c r="V35">
-        <v>1.37</v>
-      </c>
-      <c r="W35">
-        <v>1.03</v>
-      </c>
-      <c r="X35">
-        <v>1.04</v>
-      </c>
-      <c r="Y35">
-        <v>1.33</v>
-      </c>
-      <c r="Z35">
-        <v>2.99</v>
-      </c>
-      <c r="AA35">
-        <v>2.08</v>
-      </c>
-      <c r="AB35">
-        <v>1.73</v>
-      </c>
-      <c r="AC35">
-        <v>3.55</v>
-      </c>
-      <c r="AD35">
-        <v>1.24</v>
-      </c>
-      <c r="AE35">
-        <v>1.08</v>
-      </c>
-      <c r="AF35">
-        <v>2.05</v>
-      </c>
-      <c r="AG35">
-        <v>1.67</v>
-      </c>
       <c r="AH35" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AK35">
-        <v>2.38</v>
+        <v>1.86</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6503,28 +6503,28 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="O38">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P38">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q38">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="R38">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S38">
         <v>1.33</v>
       </c>
       <c r="T38">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="U38">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V38">
         <v>1.42</v>
@@ -6533,34 +6533,34 @@
         <v>1.07</v>
       </c>
       <c r="X38">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z38">
         <v>3.5</v>
       </c>
       <c r="AA38">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AB38">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC38">
-        <v>3.11</v>
+        <v>3.25</v>
       </c>
       <c r="AD38">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE38">
         <v>1.09</v>
       </c>
       <c r="AF38">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG38">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AL39">
         <v>0</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -635,49 +635,49 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O2">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
         <v>2.25</v>
       </c>
       <c r="Q2">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="R2">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T2">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V2">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z2">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AA2">
         <v>2.14</v>
       </c>
       <c r="AB2">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AC2">
         <v>3.84</v>
@@ -692,7 +692,7 @@
         <v>1.85</v>
       </c>
       <c r="AG2">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.31</v>
       </c>
       <c r="AK2">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -801,61 +801,61 @@
         <v>2.2</v>
       </c>
       <c r="O3">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P3">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="Q3">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R3">
         <v>2.3</v>
       </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
         <v>3.3</v>
       </c>
       <c r="U3">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="V3">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W3">
         <v>1.11</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
         <v>1.21</v>
       </c>
       <c r="Z3">
-        <v>4.44</v>
+        <v>4.43</v>
       </c>
       <c r="AA3">
         <v>1.69</v>
       </c>
       <c r="AB3">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC3">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="AD3">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AE3">
         <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG3">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AK3">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,28 +961,28 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="O4">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P4">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="Q4">
+        <v>1.96</v>
+      </c>
+      <c r="R4">
         <v>2.06</v>
       </c>
-      <c r="R4">
-        <v>2.16</v>
-      </c>
       <c r="S4">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T4">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="U4">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="V4">
         <v>1.35</v>
@@ -994,31 +994,31 @@
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z4">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="AA4">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AB4">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC4">
-        <v>3.85</v>
+        <v>3.44</v>
       </c>
       <c r="AD4">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE4">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
         <v>2.15</v>
       </c>
       <c r="AG4">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.2</v>
       </c>
       <c r="AK4">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="O11">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="P11">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="O20">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P20">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="Q20">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="R20">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="S20">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T20">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="V20">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="W20">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z20">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AA20">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AB20">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AC20">
         <v>1.67</v>
       </c>
       <c r="AD20">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AE20">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AF20">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AG20">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AK20">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="O21">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="P21">
+        <v>3.65</v>
+      </c>
+      <c r="Q21">
+        <v>2.01</v>
+      </c>
+      <c r="R21">
+        <v>2.7</v>
+      </c>
+      <c r="S21">
+        <v>1.15</v>
+      </c>
+      <c r="T21">
         <v>4.6</v>
       </c>
-      <c r="Q21">
-        <v>1.75</v>
-      </c>
-      <c r="R21">
-        <v>2.88</v>
-      </c>
-      <c r="S21">
-        <v>1.14</v>
-      </c>
-      <c r="T21">
-        <v>5</v>
-      </c>
       <c r="U21">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="V21">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="W21">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X21">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z21">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AA21">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AB21">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AC21">
         <v>1.67</v>
       </c>
       <c r="AD21">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AE21">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AF21">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AG21">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AK21">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O26">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P26">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q26">
         <v>2.3</v>
@@ -4577,19 +4577,19 @@
         <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="AA26">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AB26">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC26">
         <v>3.1</v>
@@ -4598,7 +4598,7 @@
         <v>1.36</v>
       </c>
       <c r="AE26">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF26">
         <v>1.8</v>
@@ -4710,31 +4710,31 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="O27">
-        <v>2.67</v>
+        <v>2.95</v>
       </c>
       <c r="P27">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="Q27">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="R27">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="S27">
         <v>1.5</v>
       </c>
       <c r="T27">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U27">
         <v>3.5</v>
       </c>
       <c r="V27">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W27">
         <v>1.04</v>
@@ -4743,13 +4743,13 @@
         <v>1.06</v>
       </c>
       <c r="Y27">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="Z27">
         <v>2.39</v>
       </c>
       <c r="AA27">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AB27">
         <v>1.44</v>
@@ -4758,13 +4758,13 @@
         <v>5.33</v>
       </c>
       <c r="AD27">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE27">
         <v>1.01</v>
       </c>
       <c r="AF27">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AG27">
         <v>1.62</v>
@@ -4783,7 +4783,7 @@
         <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="O29">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="P29">
-        <v>3.65</v>
+        <v>3.03</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="O30">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="P30">
-        <v>5.75</v>
+        <v>22</v>
       </c>
       <c r="Q30">
         <v>2.31</v>
@@ -5365,7 +5365,7 @@
         <v>2.18</v>
       </c>
       <c r="O31">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="P31">
         <v>3.3</v>
@@ -5374,16 +5374,16 @@
         <v>3.1</v>
       </c>
       <c r="R31">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="S31">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="T31">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="U31">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="V31">
         <v>1.22</v>
@@ -5392,34 +5392,34 @@
         <v>1.03</v>
       </c>
       <c r="X31">
+        <v>1.12</v>
+      </c>
+      <c r="Y31">
+        <v>1.62</v>
+      </c>
+      <c r="Z31">
+        <v>2.2</v>
+      </c>
+      <c r="AA31">
+        <v>2.85</v>
+      </c>
+      <c r="AB31">
+        <v>1.38</v>
+      </c>
+      <c r="AC31">
+        <v>5.7</v>
+      </c>
+      <c r="AD31">
         <v>1.08</v>
       </c>
-      <c r="Y31">
-        <v>1.64</v>
-      </c>
-      <c r="Z31">
-        <v>2.09</v>
-      </c>
-      <c r="AA31">
-        <v>2.88</v>
-      </c>
-      <c r="AB31">
-        <v>1.4</v>
-      </c>
-      <c r="AC31">
-        <v>6.5</v>
-      </c>
-      <c r="AD31">
-        <v>1.1</v>
-      </c>
       <c r="AE31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AG31">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK31">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,80 +5525,80 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="O32">
-        <v>3.66</v>
+        <v>3.22</v>
       </c>
       <c r="P32">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="Q32">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="R32">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="T32">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="U32">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="V32">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="W32">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="Z32">
-        <v>4.55</v>
+        <v>3.22</v>
       </c>
       <c r="AA32">
-        <v>1.56</v>
+        <v>2.15</v>
       </c>
       <c r="AB32">
-        <v>2.41</v>
+        <v>1.66</v>
       </c>
       <c r="AC32">
-        <v>2.45</v>
+        <v>3.64</v>
       </c>
       <c r="AD32">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="AE32">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AF32">
+        <v>1.73</v>
+      </c>
+      <c r="AG32">
+        <v>2</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <v>1.28</v>
+      </c>
+      <c r="AK32">
         <v>1.5</v>
-      </c>
-      <c r="AG32">
-        <v>2.5</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.4</v>
-      </c>
-      <c r="AK32">
-        <v>1.63</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="O33">
-        <v>3.22</v>
+        <v>3.95</v>
       </c>
       <c r="P33">
-        <v>2.68</v>
+        <v>6.5</v>
       </c>
       <c r="Q33">
-        <v>2.76</v>
+        <v>2.05</v>
       </c>
       <c r="R33">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="U33">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="V33">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X33">
+        <v>1.01</v>
+      </c>
+      <c r="Y33">
+        <v>1.35</v>
+      </c>
+      <c r="Z33">
+        <v>2.99</v>
+      </c>
+      <c r="AA33">
+        <v>2.05</v>
+      </c>
+      <c r="AB33">
+        <v>1.7</v>
+      </c>
+      <c r="AC33">
+        <v>3.75</v>
+      </c>
+      <c r="AD33">
+        <v>1.22</v>
+      </c>
+      <c r="AE33">
         <v>1.04</v>
       </c>
-      <c r="Y33">
-        <v>1.3</v>
-      </c>
-      <c r="Z33">
-        <v>3.22</v>
-      </c>
-      <c r="AA33">
-        <v>2.15</v>
-      </c>
-      <c r="AB33">
-        <v>1.66</v>
-      </c>
-      <c r="AC33">
-        <v>3.64</v>
-      </c>
-      <c r="AD33">
-        <v>1.25</v>
-      </c>
-      <c r="AE33">
-        <v>1.03</v>
-      </c>
       <c r="AF33">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AK33">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,65 +5851,65 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="O34">
-        <v>3.95</v>
+        <v>3.42</v>
       </c>
       <c r="P34">
-        <v>6.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q34">
+        <v>2.41</v>
+      </c>
+      <c r="R34">
+        <v>2.2</v>
+      </c>
+      <c r="S34">
+        <v>1.3</v>
+      </c>
+      <c r="T34">
+        <v>3.26</v>
+      </c>
+      <c r="U34">
+        <v>2.56</v>
+      </c>
+      <c r="V34">
+        <v>1.44</v>
+      </c>
+      <c r="W34">
+        <v>1.07</v>
+      </c>
+      <c r="X34">
+        <v>1.03</v>
+      </c>
+      <c r="Y34">
+        <v>1.24</v>
+      </c>
+      <c r="Z34">
+        <v>3.7</v>
+      </c>
+      <c r="AA34">
+        <v>1.85</v>
+      </c>
+      <c r="AB34">
+        <v>1.95</v>
+      </c>
+      <c r="AC34">
+        <v>2.97</v>
+      </c>
+      <c r="AD34">
+        <v>1.38</v>
+      </c>
+      <c r="AE34">
+        <v>1.1</v>
+      </c>
+      <c r="AF34">
+        <v>1.7</v>
+      </c>
+      <c r="AG34">
         <v>2.05</v>
       </c>
-      <c r="R34">
-        <v>2.1</v>
-      </c>
-      <c r="S34">
-        <v>1.36</v>
-      </c>
-      <c r="T34">
-        <v>2.8</v>
-      </c>
-      <c r="U34">
-        <v>2.94</v>
-      </c>
-      <c r="V34">
-        <v>1.35</v>
-      </c>
-      <c r="W34">
-        <v>1.03</v>
-      </c>
-      <c r="X34">
-        <v>1.01</v>
-      </c>
-      <c r="Y34">
-        <v>1.35</v>
-      </c>
-      <c r="Z34">
-        <v>2.99</v>
-      </c>
-      <c r="AA34">
-        <v>2.05</v>
-      </c>
-      <c r="AB34">
-        <v>1.7</v>
-      </c>
-      <c r="AC34">
-        <v>3.75</v>
-      </c>
-      <c r="AD34">
-        <v>1.22</v>
-      </c>
-      <c r="AE34">
-        <v>1.04</v>
-      </c>
-      <c r="AF34">
-        <v>2.1</v>
-      </c>
-      <c r="AG34">
-        <v>1.64</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AK34">
-        <v>2.38</v>
+        <v>1.86</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="O35">
-        <v>3.42</v>
+        <v>3.66</v>
       </c>
       <c r="P35">
-        <v>3.75</v>
+        <v>2.84</v>
       </c>
       <c r="Q35">
+        <v>2.65</v>
+      </c>
+      <c r="R35">
+        <v>2.23</v>
+      </c>
+      <c r="S35">
+        <v>1.29</v>
+      </c>
+      <c r="T35">
+        <v>3.2</v>
+      </c>
+      <c r="U35">
+        <v>2.29</v>
+      </c>
+      <c r="V35">
+        <v>1.58</v>
+      </c>
+      <c r="W35">
+        <v>1.13</v>
+      </c>
+      <c r="X35">
+        <v>1.01</v>
+      </c>
+      <c r="Y35">
+        <v>1.13</v>
+      </c>
+      <c r="Z35">
+        <v>4.55</v>
+      </c>
+      <c r="AA35">
+        <v>1.56</v>
+      </c>
+      <c r="AB35">
         <v>2.41</v>
       </c>
-      <c r="R35">
-        <v>2.2</v>
-      </c>
-      <c r="S35">
-        <v>1.3</v>
-      </c>
-      <c r="T35">
-        <v>3.26</v>
-      </c>
-      <c r="U35">
-        <v>2.56</v>
-      </c>
-      <c r="V35">
-        <v>1.44</v>
-      </c>
-      <c r="W35">
-        <v>1.07</v>
-      </c>
-      <c r="X35">
-        <v>1.03</v>
-      </c>
-      <c r="Y35">
-        <v>1.24</v>
-      </c>
-      <c r="Z35">
-        <v>3.7</v>
-      </c>
-      <c r="AA35">
-        <v>1.85</v>
-      </c>
-      <c r="AB35">
-        <v>1.95</v>
-      </c>
       <c r="AC35">
-        <v>2.97</v>
+        <v>2.45</v>
       </c>
       <c r="AD35">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="AE35">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AF35">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AG35">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AK35">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,10 +6186,10 @@
         <v>2.11</v>
       </c>
       <c r="Q36">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="R36">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="S36">
         <v>1.22</v>
@@ -6204,7 +6204,7 @@
         <v>1.6</v>
       </c>
       <c r="W36">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X36">
         <v>1.02</v>
@@ -6213,22 +6213,22 @@
         <v>1.12</v>
       </c>
       <c r="Z36">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA36">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AB36">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AC36">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AD36">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AE36">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF36">
         <v>1.43</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O37">
         <v>4.75</v>
@@ -6349,7 +6349,7 @@
         <v>6</v>
       </c>
       <c r="Q37">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R37">
         <v>2.7</v>
@@ -6361,28 +6361,28 @@
         <v>3.84</v>
       </c>
       <c r="U37">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="V37">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="W37">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z37">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AA37">
         <v>1.44</v>
       </c>
       <c r="AB37">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="AC37">
         <v>2.26</v>
@@ -6394,10 +6394,10 @@
         <v>1.3</v>
       </c>
       <c r="AF37">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG37">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK37">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6506,49 +6506,49 @@
         <v>2.17</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P38">
         <v>2.9</v>
       </c>
       <c r="Q38">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="R38">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S38">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T38">
-        <v>2.77</v>
+        <v>3.09</v>
       </c>
       <c r="U38">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V38">
         <v>1.42</v>
       </c>
       <c r="W38">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y38">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z38">
         <v>3.5</v>
       </c>
       <c r="AA38">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB38">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC38">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AD38">
         <v>1.3</v>
@@ -6560,7 +6560,7 @@
         <v>1.67</v>
       </c>
       <c r="AG38">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6675,10 +6675,10 @@
         <v>6.5</v>
       </c>
       <c r="Q39">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R39">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="S39">
         <v>1.2</v>
@@ -6687,22 +6687,22 @@
         <v>4</v>
       </c>
       <c r="U39">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="V39">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W39">
         <v>1.18</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
         <v>1.09</v>
       </c>
       <c r="Z39">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AA39">
         <v>1.44</v>
@@ -6711,10 +6711,10 @@
         <v>2.7</v>
       </c>
       <c r="AC39">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AD39">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE39">
         <v>1.25</v>
@@ -6739,7 +6739,7 @@
         <v>1.12</v>
       </c>
       <c r="AK39">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6838,43 +6838,43 @@
         <v>0</v>
       </c>
       <c r="Q40">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R40">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S40">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T40">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U40">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="V40">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X40">
         <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z40">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AA40">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB40">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AC40">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="AD40">
         <v>1.42</v>
@@ -6883,10 +6883,10 @@
         <v>1.14</v>
       </c>
       <c r="AF40">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG40">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.21</v>
       </c>
       <c r="AK40">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.91</v>
+        <v>2.6</v>
       </c>
       <c r="O42">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="P42">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7194,10 +7194,10 @@
         <v>2</v>
       </c>
       <c r="AA42">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AB42">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC42">
         <v>0</v>
@@ -7318,52 +7318,52 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="O43">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P43">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q43">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="R43">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="S43">
         <v>1.46</v>
       </c>
       <c r="T43">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="U43">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="V43">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W43">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X43">
         <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z43">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AA43">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB43">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC43">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="AD43">
         <v>1.16</v>
@@ -7372,10 +7372,10 @@
         <v>1.01</v>
       </c>
       <c r="AF43">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AG43">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7493,10 +7493,10 @@
         <v>3.26</v>
       </c>
       <c r="R44">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="S44">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T44">
         <v>2.82</v>
@@ -7508,7 +7508,7 @@
         <v>1.43</v>
       </c>
       <c r="W44">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X44">
         <v>1.01</v>
@@ -7517,16 +7517,16 @@
         <v>1.18</v>
       </c>
       <c r="Z44">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AA44">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AB44">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AC44">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AD44">
         <v>1.33</v>
@@ -7535,7 +7535,7 @@
         <v>1.1</v>
       </c>
       <c r="AF44">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG44">
         <v>2.3</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AK44">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL44">
         <v>0</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O14">
+        <v>2.9</v>
+      </c>
+      <c r="P14">
+        <v>2.3</v>
+      </c>
+      <c r="Q14">
+        <v>4.05</v>
+      </c>
+      <c r="R14">
+        <v>1.85</v>
+      </c>
+      <c r="S14">
+        <v>1.44</v>
+      </c>
+      <c r="T14">
         <v>2.62</v>
       </c>
-      <c r="P14">
-        <v>2.37</v>
-      </c>
-      <c r="Q14">
-        <v>4.33</v>
-      </c>
-      <c r="R14">
-        <v>1.97</v>
-      </c>
-      <c r="S14">
-        <v>1.54</v>
-      </c>
-      <c r="T14">
-        <v>2.39</v>
-      </c>
       <c r="U14">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="V14">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="Z14">
-        <v>2.49</v>
+        <v>2.8</v>
       </c>
       <c r="AA14">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB14">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AC14">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AD14">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE14">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF14">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AG14">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AK14">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,80 +2754,80 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O15">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="P15">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q15">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="R15">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="S15">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="T15">
-        <v>2.62</v>
+        <v>2.39</v>
       </c>
       <c r="U15">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="V15">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X15">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y15">
+        <v>1.47</v>
+      </c>
+      <c r="Z15">
+        <v>2.49</v>
+      </c>
+      <c r="AA15">
+        <v>2.35</v>
+      </c>
+      <c r="AB15">
+        <v>1.5</v>
+      </c>
+      <c r="AC15">
+        <v>4.5</v>
+      </c>
+      <c r="AD15">
+        <v>1.17</v>
+      </c>
+      <c r="AE15">
+        <v>1.02</v>
+      </c>
+      <c r="AF15">
+        <v>1.98</v>
+      </c>
+      <c r="AG15">
+        <v>1.64</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
         <v>1.39</v>
       </c>
-      <c r="Z15">
-        <v>2.8</v>
-      </c>
-      <c r="AA15">
-        <v>2.2</v>
-      </c>
-      <c r="AB15">
-        <v>1.58</v>
-      </c>
-      <c r="AC15">
-        <v>3.9</v>
-      </c>
-      <c r="AD15">
-        <v>1.19</v>
-      </c>
-      <c r="AE15">
-        <v>1.03</v>
-      </c>
-      <c r="AF15">
-        <v>1.89</v>
-      </c>
-      <c r="AG15">
-        <v>1.76</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.53</v>
-      </c>
       <c r="AK15">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -6177,34 +6177,34 @@
         </is>
       </c>
       <c r="N36">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O36">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P36">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q36">
-        <v>3.1</v>
+        <v>3.53</v>
       </c>
       <c r="R36">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="S36">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T36">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="U36">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="V36">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W36">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X36">
         <v>1.02</v>
@@ -6216,16 +6216,16 @@
         <v>4.75</v>
       </c>
       <c r="AA36">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AB36">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC36">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AD36">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AE36">
         <v>1.21</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK36">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6503,37 +6503,37 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="O38">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P38">
+        <v>3.1</v>
+      </c>
+      <c r="Q38">
+        <v>2.62</v>
+      </c>
+      <c r="R38">
+        <v>2.1</v>
+      </c>
+      <c r="S38">
+        <v>1.32</v>
+      </c>
+      <c r="T38">
         <v>2.9</v>
       </c>
-      <c r="Q38">
-        <v>2.88</v>
-      </c>
-      <c r="R38">
-        <v>2.12</v>
-      </c>
-      <c r="S38">
-        <v>1.34</v>
-      </c>
-      <c r="T38">
-        <v>3.09</v>
-      </c>
       <c r="U38">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="V38">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W38">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
         <v>1.25</v>
@@ -6542,16 +6542,16 @@
         <v>3.5</v>
       </c>
       <c r="AA38">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AB38">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC38">
         <v>3</v>
       </c>
       <c r="AD38">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE38">
         <v>1.09</v>
@@ -6560,7 +6560,7 @@
         <v>1.67</v>
       </c>
       <c r="AG38">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="O39">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="P39">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q39">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R39">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="S39">
         <v>1.2</v>
@@ -6702,13 +6702,13 @@
         <v>1.09</v>
       </c>
       <c r="Z39">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="AA39">
         <v>1.44</v>
       </c>
       <c r="AB39">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AC39">
         <v>2.04</v>
@@ -6723,7 +6723,7 @@
         <v>1.6</v>
       </c>
       <c r="AG39">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK39">
         <v>2.72</v>
@@ -6847,16 +6847,16 @@
         <v>1.29</v>
       </c>
       <c r="T40">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U40">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V40">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W40">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
         <v>1.03</v>
@@ -6868,7 +6868,7 @@
         <v>4</v>
       </c>
       <c r="AA40">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB40">
         <v>2.12</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7031,10 +7031,10 @@
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC41">
         <v>0</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -2591,16 +2591,16 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O14">
         <v>2.9</v>
       </c>
       <c r="P14">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q14">
-        <v>4.05</v>
+        <v>4.22</v>
       </c>
       <c r="R14">
         <v>1.85</v>
@@ -2621,28 +2621,28 @@
         <v>1.06</v>
       </c>
       <c r="X14">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y14">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z14">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA14">
         <v>2.2</v>
       </c>
       <c r="AB14">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AC14">
         <v>3.9</v>
       </c>
       <c r="AD14">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE14">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
         <v>1.89</v>
@@ -2664,7 +2664,7 @@
         <v>1.53</v>
       </c>
       <c r="AK14">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,52 +2754,52 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O15">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P15">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="Q15">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="R15">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="S15">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="T15">
-        <v>2.39</v>
+        <v>2.22</v>
       </c>
       <c r="U15">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="V15">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W15">
         <v>1.01</v>
       </c>
       <c r="X15">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y15">
         <v>1.47</v>
       </c>
       <c r="Z15">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="AA15">
         <v>2.35</v>
       </c>
       <c r="AB15">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AC15">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AD15">
         <v>1.17</v>
@@ -2808,7 +2808,7 @@
         <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AG15">
         <v>1.64</v>
@@ -2827,7 +2827,7 @@
         <v>1.39</v>
       </c>
       <c r="AK15">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -4719,22 +4719,22 @@
         <v>3.18</v>
       </c>
       <c r="Q27">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="R27">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="S27">
         <v>1.5</v>
       </c>
       <c r="T27">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U27">
         <v>3.5</v>
       </c>
       <c r="V27">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W27">
         <v>1.04</v>
@@ -4746,13 +4746,13 @@
         <v>1.53</v>
       </c>
       <c r="Z27">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="AA27">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AB27">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AC27">
         <v>5.33</v>
@@ -4764,10 +4764,10 @@
         <v>1.01</v>
       </c>
       <c r="AF27">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AG27">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK27">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="O29">
         <v>2.8</v>
       </c>
       <c r="P29">
-        <v>3.03</v>
+        <v>3.85</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5362,37 +5362,37 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="O31">
-        <v>2.71</v>
+        <v>2.87</v>
       </c>
       <c r="P31">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q31">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="R31">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="S31">
         <v>1.57</v>
       </c>
       <c r="T31">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="U31">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="V31">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W31">
         <v>1.03</v>
       </c>
       <c r="X31">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Y31">
         <v>1.62</v>
@@ -5407,19 +5407,19 @@
         <v>1.38</v>
       </c>
       <c r="AC31">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AD31">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE31">
         <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG31">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK31">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,65 +5688,65 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="O33">
-        <v>3.95</v>
+        <v>3.42</v>
       </c>
       <c r="P33">
-        <v>6.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q33">
+        <v>2.41</v>
+      </c>
+      <c r="R33">
+        <v>2.2</v>
+      </c>
+      <c r="S33">
+        <v>1.3</v>
+      </c>
+      <c r="T33">
+        <v>3.26</v>
+      </c>
+      <c r="U33">
+        <v>2.56</v>
+      </c>
+      <c r="V33">
+        <v>1.44</v>
+      </c>
+      <c r="W33">
+        <v>1.07</v>
+      </c>
+      <c r="X33">
+        <v>1.03</v>
+      </c>
+      <c r="Y33">
+        <v>1.24</v>
+      </c>
+      <c r="Z33">
+        <v>3.7</v>
+      </c>
+      <c r="AA33">
+        <v>1.85</v>
+      </c>
+      <c r="AB33">
+        <v>1.95</v>
+      </c>
+      <c r="AC33">
+        <v>2.97</v>
+      </c>
+      <c r="AD33">
+        <v>1.38</v>
+      </c>
+      <c r="AE33">
+        <v>1.1</v>
+      </c>
+      <c r="AF33">
+        <v>1.7</v>
+      </c>
+      <c r="AG33">
         <v>2.05</v>
       </c>
-      <c r="R33">
-        <v>2.1</v>
-      </c>
-      <c r="S33">
-        <v>1.36</v>
-      </c>
-      <c r="T33">
-        <v>2.8</v>
-      </c>
-      <c r="U33">
-        <v>2.94</v>
-      </c>
-      <c r="V33">
-        <v>1.35</v>
-      </c>
-      <c r="W33">
-        <v>1.03</v>
-      </c>
-      <c r="X33">
-        <v>1.01</v>
-      </c>
-      <c r="Y33">
-        <v>1.35</v>
-      </c>
-      <c r="Z33">
-        <v>2.99</v>
-      </c>
-      <c r="AA33">
-        <v>2.05</v>
-      </c>
-      <c r="AB33">
-        <v>1.7</v>
-      </c>
-      <c r="AC33">
-        <v>3.75</v>
-      </c>
-      <c r="AD33">
-        <v>1.22</v>
-      </c>
-      <c r="AE33">
-        <v>1.04</v>
-      </c>
-      <c r="AF33">
-        <v>2.1</v>
-      </c>
-      <c r="AG33">
-        <v>1.64</v>
-      </c>
       <c r="AH33" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AK33">
-        <v>2.38</v>
+        <v>1.86</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="O34">
-        <v>3.42</v>
+        <v>3.95</v>
       </c>
       <c r="P34">
+        <v>6.5</v>
+      </c>
+      <c r="Q34">
+        <v>2.05</v>
+      </c>
+      <c r="R34">
+        <v>2.1</v>
+      </c>
+      <c r="S34">
+        <v>1.36</v>
+      </c>
+      <c r="T34">
+        <v>2.8</v>
+      </c>
+      <c r="U34">
+        <v>2.94</v>
+      </c>
+      <c r="V34">
+        <v>1.35</v>
+      </c>
+      <c r="W34">
+        <v>1.03</v>
+      </c>
+      <c r="X34">
+        <v>1.01</v>
+      </c>
+      <c r="Y34">
+        <v>1.35</v>
+      </c>
+      <c r="Z34">
+        <v>2.99</v>
+      </c>
+      <c r="AA34">
+        <v>2.05</v>
+      </c>
+      <c r="AB34">
+        <v>1.7</v>
+      </c>
+      <c r="AC34">
         <v>3.75</v>
       </c>
-      <c r="Q34">
-        <v>2.41</v>
-      </c>
-      <c r="R34">
-        <v>2.2</v>
-      </c>
-      <c r="S34">
-        <v>1.3</v>
-      </c>
-      <c r="T34">
-        <v>3.26</v>
-      </c>
-      <c r="U34">
-        <v>2.56</v>
-      </c>
-      <c r="V34">
-        <v>1.44</v>
-      </c>
-      <c r="W34">
-        <v>1.07</v>
-      </c>
-      <c r="X34">
-        <v>1.03</v>
-      </c>
-      <c r="Y34">
-        <v>1.24</v>
-      </c>
-      <c r="Z34">
-        <v>3.7</v>
-      </c>
-      <c r="AA34">
-        <v>1.85</v>
-      </c>
-      <c r="AB34">
-        <v>1.95</v>
-      </c>
-      <c r="AC34">
-        <v>2.97</v>
-      </c>
       <c r="AD34">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AE34">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF34">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AG34">
-        <v>2.05</v>
+        <v>1.64</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AK34">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="O42">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="P42">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7327,40 +7327,40 @@
         <v>3.2</v>
       </c>
       <c r="Q43">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="R43">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="S43">
         <v>1.46</v>
       </c>
       <c r="T43">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="U43">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="V43">
         <v>1.28</v>
       </c>
       <c r="W43">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X43">
         <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z43">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AA43">
         <v>2.15</v>
       </c>
       <c r="AB43">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC43">
         <v>4.1</v>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK43">
         <v>1.62</v>
@@ -7496,13 +7496,13 @@
         <v>2.08</v>
       </c>
       <c r="S44">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T44">
         <v>2.82</v>
       </c>
       <c r="U44">
-        <v>2.69</v>
+        <v>2.28</v>
       </c>
       <c r="V44">
         <v>1.43</v>
@@ -7520,10 +7520,10 @@
         <v>3.5</v>
       </c>
       <c r="AA44">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB44">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC44">
         <v>2.83</v>
@@ -7535,10 +7535,10 @@
         <v>1.1</v>
       </c>
       <c r="AF44">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AG44">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.2</v>
+        <v>1.48</v>
       </c>
       <c r="O3">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P3">
-        <v>2.58</v>
+        <v>5.3</v>
       </c>
       <c r="Q3">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="R3">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="S3">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="T3">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="U3">
-        <v>2.59</v>
+        <v>2.94</v>
       </c>
       <c r="V3">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="Z3">
-        <v>4.43</v>
+        <v>3.17</v>
       </c>
       <c r="AA3">
-        <v>1.69</v>
+        <v>2.04</v>
       </c>
       <c r="AB3">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AC3">
-        <v>2.61</v>
+        <v>3.44</v>
       </c>
       <c r="AD3">
-        <v>1.45</v>
+        <v>1.23</v>
       </c>
       <c r="AE3">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF3">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="AG3">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AK3">
-        <v>1.59</v>
+        <v>2.35</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
+        <v>2.2</v>
+      </c>
+      <c r="O4">
+        <v>3.55</v>
+      </c>
+      <c r="P4">
+        <v>2.58</v>
+      </c>
+      <c r="Q4">
+        <v>2.8</v>
+      </c>
+      <c r="R4">
+        <v>2.3</v>
+      </c>
+      <c r="S4">
+        <v>1.33</v>
+      </c>
+      <c r="T4">
+        <v>3.3</v>
+      </c>
+      <c r="U4">
+        <v>2.59</v>
+      </c>
+      <c r="V4">
         <v>1.48</v>
       </c>
-      <c r="O4">
-        <v>3.7</v>
-      </c>
-      <c r="P4">
-        <v>5.3</v>
-      </c>
-      <c r="Q4">
-        <v>1.96</v>
-      </c>
-      <c r="R4">
-        <v>2.06</v>
-      </c>
-      <c r="S4">
-        <v>1.42</v>
-      </c>
-      <c r="T4">
-        <v>2.65</v>
-      </c>
-      <c r="U4">
-        <v>2.94</v>
-      </c>
-      <c r="V4">
-        <v>1.35</v>
-      </c>
       <c r="W4">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="Z4">
-        <v>3.17</v>
+        <v>4.43</v>
       </c>
       <c r="AA4">
-        <v>2.04</v>
+        <v>1.69</v>
       </c>
       <c r="AB4">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AC4">
-        <v>3.44</v>
+        <v>2.61</v>
       </c>
       <c r="AD4">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="AE4">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF4">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="AG4">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AK4">
-        <v>2.35</v>
+        <v>1.59</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="O7">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="P7">
-        <v>5.85</v>
+        <v>5.3</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA7">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB7">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>9.35</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>5.05</v>
+        <v>4.6</v>
       </c>
       <c r="P8">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA8">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB8">
         <v>2.05</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1948,55 +1948,55 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA10">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="AB10">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="O11">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="P11">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2277,10 +2277,10 @@
         <v>4.19</v>
       </c>
       <c r="R12">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S12">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T12">
         <v>3.58</v>
@@ -2298,31 +2298,31 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z12">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="AA12">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB12">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="AC12">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AD12">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AE12">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AF12">
         <v>1.44</v>
       </c>
       <c r="AG12">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.17</v>
+        <v>1.94</v>
       </c>
       <c r="AK12">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="O13">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P13">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q13">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="R13">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="S13">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T13">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U13">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="V13">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W13">
         <v>1.13</v>
@@ -2461,31 +2461,31 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z13">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA13">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AB13">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AC13">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AD13">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE13">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF13">
         <v>1.44</v>
       </c>
       <c r="AG13">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK13">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2917,34 +2917,34 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="O16">
-        <v>5.75</v>
+        <v>6.05</v>
       </c>
       <c r="P16">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="Q16">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R16">
         <v>3.1</v>
       </c>
       <c r="S16">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="T16">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="U16">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="V16">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="W16">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X16">
         <v>1.01</v>
@@ -2953,13 +2953,13 @@
         <v>1.06</v>
       </c>
       <c r="Z16">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AA16">
         <v>1.22</v>
       </c>
       <c r="AB16">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AC16">
         <v>1.62</v>
@@ -2968,13 +2968,13 @@
         <v>2.25</v>
       </c>
       <c r="AE16">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AF16">
         <v>1.5</v>
       </c>
       <c r="AG16">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AK16">
         <v>3.78</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.25</v>
+        <v>2.53</v>
       </c>
       <c r="O17">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="P17">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="Q17">
-        <v>2.71</v>
+        <v>2.85</v>
       </c>
       <c r="R17">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="S17">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T17">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="U17">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="V17">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="W17">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z17">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AA17">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB17">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AC17">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AD17">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AE17">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AF17">
+        <v>1.29</v>
+      </c>
+      <c r="AG17">
+        <v>3.25</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
         <v>1.25</v>
       </c>
-      <c r="AG17">
-        <v>3.5</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.19</v>
-      </c>
       <c r="AK17">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="O18">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="P18">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q18">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="R18">
-        <v>2.58</v>
+        <v>2.43</v>
       </c>
       <c r="S18">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T18">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="U18">
-        <v>1.79</v>
+        <v>2.01</v>
       </c>
       <c r="V18">
-        <v>2.03</v>
+        <v>1.74</v>
       </c>
       <c r="W18">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z18">
-        <v>8.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA18">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB18">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="AC18">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AD18">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AE18">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AF18">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AG18">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>5.35</v>
       </c>
       <c r="P19">
-        <v>2.05</v>
+        <v>5.82</v>
       </c>
       <c r="Q19">
-        <v>3.36</v>
+        <v>1.8</v>
       </c>
       <c r="R19">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="S19">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="T19">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="U19">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="V19">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="W19">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z19">
-        <v>6.17</v>
+        <v>9</v>
       </c>
       <c r="AA19">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AB19">
-        <v>2.87</v>
+        <v>3.77</v>
       </c>
       <c r="AC19">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AD19">
-        <v>1.81</v>
+        <v>2.22</v>
       </c>
       <c r="AE19">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AF19">
         <v>1.33</v>
       </c>
       <c r="AG19">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.65</v>
+        <v>1.13</v>
       </c>
       <c r="AK19">
-        <v>1.36</v>
+        <v>2.55</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="O20">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P20">
-        <v>4.6</v>
+        <v>4.29</v>
       </c>
       <c r="Q20">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="R20">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="S20">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T20">
         <v>5</v>
       </c>
       <c r="U20">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="V20">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="W20">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z20">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AA20">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AB20">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="AC20">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AD20">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AE20">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AF20">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AG20">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK20">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,31 +3732,31 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="O21">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P21">
-        <v>3.65</v>
+        <v>2.4</v>
       </c>
       <c r="Q21">
-        <v>2.01</v>
+        <v>2.63</v>
       </c>
       <c r="R21">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="S21">
         <v>1.15</v>
       </c>
       <c r="T21">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>1.81</v>
       </c>
       <c r="V21">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="W21">
         <v>1.25</v>
@@ -3765,7 +3765,7 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z21">
         <v>8.5</v>
@@ -3774,22 +3774,22 @@
         <v>1.25</v>
       </c>
       <c r="AB21">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AC21">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AD21">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AE21">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AF21">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AG21">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R22">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="S22">
         <v>1.5</v>
       </c>
       <c r="T22">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="U22">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="V22">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W22">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X22">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y22">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Z22">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AA22">
         <v>2.62</v>
       </c>
       <c r="AB22">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AC22">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="AD22">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE22">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF22">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AG22">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AK22">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="O23">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="P23">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="R23">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="S23">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T23">
-        <v>2.78</v>
+        <v>3.02</v>
       </c>
       <c r="U23">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="V23">
         <v>1.44</v>
       </c>
       <c r="W23">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA23">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB23">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC23">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AD23">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE23">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AG23">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK23">
-        <v>2.99</v>
+        <v>3.8</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O25">
         <v>2.87</v>
@@ -4393,52 +4393,52 @@
         <v>2</v>
       </c>
       <c r="Q25">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="R25">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="S25">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="T25">
         <v>2.18</v>
       </c>
       <c r="U25">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="V25">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="W25">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X25">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Y25">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z25">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AA25">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AB25">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC25">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AD25">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AE25">
         <v>1.01</v>
       </c>
       <c r="AF25">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AG25">
         <v>1.53</v>
@@ -4457,7 +4457,7 @@
         <v>1.32</v>
       </c>
       <c r="AK25">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O26">
         <v>3.75</v>
@@ -4559,16 +4559,16 @@
         <v>2.3</v>
       </c>
       <c r="R26">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="S26">
         <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="U26">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V26">
         <v>1.44</v>
@@ -4577,19 +4577,19 @@
         <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y26">
         <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA26">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AB26">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AC26">
         <v>3.1</v>
@@ -4598,10 +4598,10 @@
         <v>1.36</v>
       </c>
       <c r="AE26">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF26">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG26">
         <v>2</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5528,55 +5528,55 @@
         <v>2.4</v>
       </c>
       <c r="O32">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="P32">
         <v>2.68</v>
       </c>
       <c r="Q32">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="R32">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S32">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T32">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="U32">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="V32">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W32">
         <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z32">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="AA32">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AB32">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AC32">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="AD32">
         <v>1.25</v>
       </c>
       <c r="AE32">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF32">
         <v>1.73</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK32">
         <v>1.5</v>
@@ -5688,55 +5688,55 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O33">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="Q33">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="R33">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
         <v>1.3</v>
       </c>
       <c r="T33">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
       <c r="U33">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="V33">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z33">
         <v>3.7</v>
       </c>
       <c r="AA33">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB33">
         <v>1.95</v>
       </c>
       <c r="AC33">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AD33">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE33">
         <v>1.1</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK33">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="O34">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="P34">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Q34">
         <v>2.05</v>
       </c>
       <c r="R34">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S34">
         <v>1.36</v>
@@ -5872,34 +5872,34 @@
         <v>2.8</v>
       </c>
       <c r="U34">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="V34">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
         <v>1.03</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y34">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z34">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="AA34">
         <v>2.05</v>
       </c>
       <c r="AB34">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AC34">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD34">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE34">
         <v>1.04</v>
@@ -5908,7 +5908,7 @@
         <v>2.1</v>
       </c>
       <c r="AG34">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.08</v>
       </c>
       <c r="AK34">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,25 +6014,25 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="O35">
         <v>3.66</v>
       </c>
       <c r="P35">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="Q35">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="R35">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="S35">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U35">
         <v>2.29</v>
@@ -6041,37 +6041,37 @@
         <v>1.58</v>
       </c>
       <c r="W35">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z35">
         <v>4.55</v>
       </c>
       <c r="AA35">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB35">
         <v>2.41</v>
       </c>
       <c r="AC35">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AD35">
         <v>1.49</v>
       </c>
       <c r="AE35">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF35">
         <v>1.5</v>
       </c>
       <c r="AG35">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O36">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
         <v>2.05</v>
@@ -6198,7 +6198,7 @@
         <v>3.7</v>
       </c>
       <c r="U36">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="V36">
         <v>1.62</v>
@@ -6216,7 +6216,7 @@
         <v>4.75</v>
       </c>
       <c r="AA36">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AB36">
         <v>2.35</v>
@@ -6343,31 +6343,31 @@
         <v>1.36</v>
       </c>
       <c r="O37">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="P37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q37">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="R37">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="S37">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.84</v>
+        <v>3.94</v>
       </c>
       <c r="U37">
-        <v>2.19</v>
+        <v>2.03</v>
       </c>
       <c r="V37">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="W37">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X37">
         <v>1.01</v>
@@ -6379,25 +6379,25 @@
         <v>6</v>
       </c>
       <c r="AA37">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB37">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AC37">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="AD37">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AE37">
         <v>1.3</v>
       </c>
       <c r="AF37">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG37">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AK37">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6666,16 +6666,16 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="O39">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="P39">
-        <v>6.25</v>
+        <v>6.88</v>
       </c>
       <c r="Q39">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="R39">
         <v>2.48</v>
@@ -6687,22 +6687,22 @@
         <v>4</v>
       </c>
       <c r="U39">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="V39">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W39">
         <v>1.18</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
         <v>1.09</v>
       </c>
       <c r="Z39">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="AA39">
         <v>1.44</v>
@@ -6711,10 +6711,10 @@
         <v>2.56</v>
       </c>
       <c r="AC39">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AD39">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AE39">
         <v>1.25</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="O41">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P41">
-        <v>6.2</v>
+        <v>5.75</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA41">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB41">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL41">
         <v>0</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -638,58 +638,58 @@
         <v>3.2</v>
       </c>
       <c r="O2">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="P2">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q2">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="R2">
         <v>2</v>
       </c>
       <c r="S2">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T2">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U2">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V2">
         <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z2">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AA2">
         <v>2.14</v>
       </c>
       <c r="AB2">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC2">
         <v>3.84</v>
       </c>
       <c r="AD2">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE2">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF2">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG2">
         <v>1.85</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK2">
         <v>1.33</v>
@@ -798,31 +798,31 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="O3">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P3">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Q3">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="R3">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="S3">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T3">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U3">
-        <v>2.94</v>
+        <v>3.13</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W3">
         <v>1.04</v>
@@ -831,22 +831,22 @@
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z3">
-        <v>3.17</v>
+        <v>2.94</v>
       </c>
       <c r="AA3">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AB3">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC3">
-        <v>3.44</v>
+        <v>3.85</v>
       </c>
       <c r="AD3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE3">
         <v>1.08</v>
@@ -855,7 +855,7 @@
         <v>2.15</v>
       </c>
       <c r="AG3">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AK3">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -964,61 +964,61 @@
         <v>2.2</v>
       </c>
       <c r="O4">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="Q4">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="R4">
         <v>2.3</v>
       </c>
       <c r="S4">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U4">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="V4">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z4">
-        <v>4.43</v>
+        <v>3.5</v>
       </c>
       <c r="AA4">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="AB4">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AC4">
         <v>2.61</v>
       </c>
       <c r="AD4">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AE4">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF4">
         <v>1.55</v>
       </c>
       <c r="AG4">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AK4">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.47</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="P7">
-        <v>5.3</v>
+        <v>1.28</v>
       </c>
       <c r="Q7">
+        <v>7.9</v>
+      </c>
+      <c r="R7">
+        <v>2.31</v>
+      </c>
+      <c r="S7">
+        <v>1.3</v>
+      </c>
+      <c r="T7">
+        <v>3</v>
+      </c>
+      <c r="U7">
+        <v>2.5</v>
+      </c>
+      <c r="V7">
+        <v>1.44</v>
+      </c>
+      <c r="W7">
+        <v>1.1</v>
+      </c>
+      <c r="X7">
+        <v>1.01</v>
+      </c>
+      <c r="Y7">
+        <v>1.19</v>
+      </c>
+      <c r="Z7">
+        <v>3.86</v>
+      </c>
+      <c r="AA7">
+        <v>1.72</v>
+      </c>
+      <c r="AB7">
+        <v>2.05</v>
+      </c>
+      <c r="AC7">
+        <v>2.93</v>
+      </c>
+      <c r="AD7">
+        <v>1.4</v>
+      </c>
+      <c r="AE7">
+        <v>1.14</v>
+      </c>
+      <c r="AF7">
         <v>2</v>
       </c>
-      <c r="R7">
-        <v>2.25</v>
-      </c>
-      <c r="S7">
-        <v>1.29</v>
-      </c>
-      <c r="T7">
-        <v>3.25</v>
-      </c>
-      <c r="U7">
-        <v>2.38</v>
-      </c>
-      <c r="V7">
-        <v>1.5</v>
-      </c>
-      <c r="W7">
-        <v>1.11</v>
-      </c>
-      <c r="X7">
-        <v>1</v>
-      </c>
-      <c r="Y7">
-        <v>1.18</v>
-      </c>
-      <c r="Z7">
-        <v>3.92</v>
-      </c>
-      <c r="AA7">
-        <v>1.7</v>
-      </c>
-      <c r="AB7">
-        <v>2.1</v>
-      </c>
-      <c r="AC7">
-        <v>2.7</v>
-      </c>
-      <c r="AD7">
-        <v>1.43</v>
-      </c>
-      <c r="AE7">
-        <v>1.13</v>
-      </c>
-      <c r="AF7">
-        <v>1.7</v>
-      </c>
       <c r="AG7">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK7">
-        <v>2.45</v>
+        <v>1.05</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>8</v>
+        <v>1.47</v>
       </c>
       <c r="O8">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="P8">
-        <v>1.28</v>
+        <v>5.3</v>
       </c>
       <c r="Q8">
-        <v>7.9</v>
+        <v>2</v>
       </c>
       <c r="R8">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T8">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U8">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V8">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W8">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z8">
-        <v>3.86</v>
+        <v>3.92</v>
       </c>
       <c r="AA8">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB8">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC8">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="AD8">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE8">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AG8">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK8">
-        <v>1.05</v>
+        <v>2.45</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="O17">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="P17">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="Q17">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="R17">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="S17">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T17">
-        <v>4.55</v>
+        <v>4.15</v>
       </c>
       <c r="U17">
-        <v>1.79</v>
+        <v>2.01</v>
       </c>
       <c r="V17">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="W17">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Z17">
-        <v>7.2</v>
+        <v>6.25</v>
       </c>
       <c r="AA17">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB17">
-        <v>3.25</v>
+        <v>2.87</v>
       </c>
       <c r="AC17">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AD17">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AE17">
+        <v>1.36</v>
+      </c>
+      <c r="AF17">
+        <v>1.33</v>
+      </c>
+      <c r="AG17">
+        <v>2.85</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>1.22</v>
+      </c>
+      <c r="AK17">
         <v>1.38</v>
-      </c>
-      <c r="AF17">
-        <v>1.29</v>
-      </c>
-      <c r="AG17">
-        <v>3.25</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.25</v>
-      </c>
-      <c r="AK17">
-        <v>1.46</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="O18">
-        <v>3.95</v>
+        <v>5.35</v>
       </c>
       <c r="P18">
-        <v>2.14</v>
+        <v>5.82</v>
       </c>
       <c r="Q18">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="R18">
-        <v>2.43</v>
+        <v>2.85</v>
       </c>
       <c r="S18">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="T18">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="U18">
-        <v>2.01</v>
+        <v>1.77</v>
       </c>
       <c r="V18">
-        <v>1.74</v>
+        <v>2.15</v>
       </c>
       <c r="W18">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z18">
-        <v>6.25</v>
+        <v>9</v>
       </c>
       <c r="AA18">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AB18">
-        <v>2.87</v>
+        <v>3.77</v>
       </c>
       <c r="AC18">
-        <v>2.04</v>
+        <v>1.65</v>
       </c>
       <c r="AD18">
-        <v>1.78</v>
+        <v>2.22</v>
       </c>
       <c r="AE18">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AF18">
         <v>1.33</v>
       </c>
       <c r="AG18">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK18">
-        <v>1.38</v>
+        <v>2.55</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="O19">
-        <v>5.35</v>
+        <v>4.6</v>
       </c>
       <c r="P19">
-        <v>5.82</v>
+        <v>4.29</v>
       </c>
       <c r="Q19">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="R19">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="S19">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="T19">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U19">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V19">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="W19">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z19">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AA19">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AB19">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="AC19">
         <v>1.65</v>
       </c>
       <c r="AD19">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AE19">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF19">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AG19">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AK19">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,34 +3569,34 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="O20">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="P20">
-        <v>4.29</v>
+        <v>2.4</v>
       </c>
       <c r="Q20">
-        <v>2.08</v>
+        <v>2.63</v>
       </c>
       <c r="R20">
-        <v>2.76</v>
+        <v>2.57</v>
       </c>
       <c r="S20">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T20">
         <v>5</v>
       </c>
       <c r="U20">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="V20">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="W20">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3605,28 +3605,28 @@
         <v>1.06</v>
       </c>
       <c r="Z20">
-        <v>7.4</v>
+        <v>8.5</v>
       </c>
       <c r="AA20">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB20">
-        <v>3.76</v>
+        <v>3.42</v>
       </c>
       <c r="AC20">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AD20">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AE20">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AF20">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AG20">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>2.34</v>
+        <v>1.53</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,80 +3732,80 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.25</v>
+        <v>2.53</v>
       </c>
       <c r="O21">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="P21">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="Q21">
-        <v>2.63</v>
+        <v>2.85</v>
       </c>
       <c r="R21">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="S21">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T21">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="U21">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="V21">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="W21">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z21">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="AA21">
+        <v>1.3</v>
+      </c>
+      <c r="AB21">
+        <v>3.25</v>
+      </c>
+      <c r="AC21">
+        <v>1.75</v>
+      </c>
+      <c r="AD21">
+        <v>2.1</v>
+      </c>
+      <c r="AE21">
+        <v>1.38</v>
+      </c>
+      <c r="AF21">
+        <v>1.29</v>
+      </c>
+      <c r="AG21">
+        <v>3.25</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
         <v>1.25</v>
       </c>
-      <c r="AB21">
-        <v>3.42</v>
-      </c>
-      <c r="AC21">
-        <v>1.68</v>
-      </c>
-      <c r="AD21">
-        <v>2.09</v>
-      </c>
-      <c r="AE21">
-        <v>1.43</v>
-      </c>
-      <c r="AF21">
-        <v>1.25</v>
-      </c>
-      <c r="AG21">
-        <v>3.5</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.2</v>
-      </c>
       <c r="AK21">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O27">
         <v>2.95</v>
       </c>
       <c r="P27">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="Q27">
         <v>2.9</v>
@@ -4725,16 +4725,16 @@
         <v>1.85</v>
       </c>
       <c r="S27">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T27">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="U27">
         <v>3.5</v>
       </c>
       <c r="V27">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W27">
         <v>1.04</v>
@@ -4755,7 +4755,7 @@
         <v>1.53</v>
       </c>
       <c r="AC27">
-        <v>5.33</v>
+        <v>5.42</v>
       </c>
       <c r="AD27">
         <v>1.14</v>
@@ -4764,7 +4764,7 @@
         <v>1.01</v>
       </c>
       <c r="AF27">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AG27">
         <v>1.7</v>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
         <v>1.61</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="O29">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="P29">
-        <v>3.85</v>
+        <v>3.38</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="O30">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="P30">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q30">
         <v>2.31</v>
@@ -5365,13 +5365,13 @@
         <v>2.25</v>
       </c>
       <c r="O31">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="P31">
         <v>3.25</v>
       </c>
       <c r="Q31">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="R31">
         <v>1.86</v>
@@ -5380,7 +5380,7 @@
         <v>1.57</v>
       </c>
       <c r="T31">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="U31">
         <v>3.9</v>
@@ -5392,7 +5392,7 @@
         <v>1.03</v>
       </c>
       <c r="X31">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Y31">
         <v>1.62</v>
@@ -5410,7 +5410,7 @@
         <v>6</v>
       </c>
       <c r="AD31">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AE31">
         <v>1.03</v>
@@ -5419,7 +5419,7 @@
         <v>2.25</v>
       </c>
       <c r="AG31">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.26</v>
       </c>
       <c r="AK31">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P38">
-        <v>3.1</v>
+        <v>3.01</v>
       </c>
       <c r="Q38">
         <v>2.62</v>
@@ -6521,7 +6521,7 @@
         <v>1.32</v>
       </c>
       <c r="T38">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="U38">
         <v>2.7</v>
@@ -6530,37 +6530,37 @@
         <v>1.4</v>
       </c>
       <c r="W38">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z38">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA38">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB38">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC38">
         <v>3</v>
       </c>
       <c r="AD38">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE38">
         <v>1.09</v>
       </c>
       <c r="AF38">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG38">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6838,16 +6838,16 @@
         <v>0</v>
       </c>
       <c r="Q40">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="R40">
         <v>2.25</v>
       </c>
       <c r="S40">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T40">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="U40">
         <v>2.4</v>
@@ -6868,7 +6868,7 @@
         <v>4</v>
       </c>
       <c r="AA40">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB40">
         <v>2.12</v>
@@ -6877,7 +6877,7 @@
         <v>2.52</v>
       </c>
       <c r="AD40">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE40">
         <v>1.14</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="O42">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="P42">
-        <v>3.02</v>
+        <v>2.65</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="O43">
         <v>3.05</v>
@@ -7342,7 +7342,7 @@
         <v>3.18</v>
       </c>
       <c r="V43">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W43">
         <v>1.05</v>
@@ -7357,25 +7357,25 @@
         <v>2.8</v>
       </c>
       <c r="AA43">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB43">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AC43">
         <v>4.1</v>
       </c>
       <c r="AD43">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AE43">
         <v>1.01</v>
       </c>
       <c r="AF43">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AG43">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="O2">
         <v>3.17</v>
@@ -644,10 +644,10 @@
         <v>2.15</v>
       </c>
       <c r="Q2">
-        <v>3.82</v>
+        <v>3.92</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="S2">
         <v>1.45</v>
@@ -656,10 +656,10 @@
         <v>2.65</v>
       </c>
       <c r="U2">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W2">
         <v>1.01</v>
@@ -668,31 +668,31 @@
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z2">
-        <v>2.85</v>
+        <v>3.13</v>
       </c>
       <c r="AA2">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AB2">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC2">
-        <v>3.84</v>
+        <v>3.97</v>
       </c>
       <c r="AD2">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE2">
         <v>1.07</v>
       </c>
       <c r="AF2">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AG2">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="O3">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P3">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="Q3">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R3">
         <v>2.12</v>
@@ -816,13 +816,13 @@
         <v>1.43</v>
       </c>
       <c r="T3">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="U3">
         <v>3.13</v>
       </c>
       <c r="V3">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
         <v>1.04</v>
@@ -834,28 +834,28 @@
         <v>1.31</v>
       </c>
       <c r="Z3">
-        <v>2.94</v>
+        <v>3.17</v>
       </c>
       <c r="AA3">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AB3">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC3">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AD3">
         <v>1.22</v>
       </c>
       <c r="AE3">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF3">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AG3">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AK3">
         <v>2.45</v>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P4">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="Q4">
-        <v>2.79</v>
+        <v>2.57</v>
       </c>
       <c r="R4">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S4">
         <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="U4">
         <v>2.6</v>
@@ -994,16 +994,16 @@
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="Z4">
-        <v>3.5</v>
+        <v>4.48</v>
       </c>
       <c r="AA4">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AB4">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AC4">
         <v>2.61</v>
@@ -1012,13 +1012,13 @@
         <v>1.39</v>
       </c>
       <c r="AE4">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF4">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG4">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.27</v>
       </c>
       <c r="AK4">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>8</v>
+        <v>1.47</v>
       </c>
       <c r="O7">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="P7">
-        <v>1.28</v>
+        <v>5.3</v>
       </c>
       <c r="Q7">
-        <v>7.9</v>
+        <v>2</v>
       </c>
       <c r="R7">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T7">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U7">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z7">
-        <v>3.86</v>
+        <v>3.92</v>
       </c>
       <c r="AA7">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB7">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC7">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="AD7">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE7">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AG7">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK7">
-        <v>1.05</v>
+        <v>2.45</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.47</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="P8">
-        <v>5.3</v>
+        <v>1.28</v>
       </c>
       <c r="Q8">
+        <v>7.9</v>
+      </c>
+      <c r="R8">
+        <v>2.31</v>
+      </c>
+      <c r="S8">
+        <v>1.3</v>
+      </c>
+      <c r="T8">
+        <v>3</v>
+      </c>
+      <c r="U8">
+        <v>2.5</v>
+      </c>
+      <c r="V8">
+        <v>1.44</v>
+      </c>
+      <c r="W8">
+        <v>1.1</v>
+      </c>
+      <c r="X8">
+        <v>1.01</v>
+      </c>
+      <c r="Y8">
+        <v>1.19</v>
+      </c>
+      <c r="Z8">
+        <v>3.86</v>
+      </c>
+      <c r="AA8">
+        <v>1.72</v>
+      </c>
+      <c r="AB8">
+        <v>2.05</v>
+      </c>
+      <c r="AC8">
+        <v>2.93</v>
+      </c>
+      <c r="AD8">
+        <v>1.4</v>
+      </c>
+      <c r="AE8">
+        <v>1.14</v>
+      </c>
+      <c r="AF8">
         <v>2</v>
       </c>
-      <c r="R8">
-        <v>2.25</v>
-      </c>
-      <c r="S8">
-        <v>1.29</v>
-      </c>
-      <c r="T8">
-        <v>3.25</v>
-      </c>
-      <c r="U8">
-        <v>2.38</v>
-      </c>
-      <c r="V8">
-        <v>1.5</v>
-      </c>
-      <c r="W8">
-        <v>1.11</v>
-      </c>
-      <c r="X8">
-        <v>1</v>
-      </c>
-      <c r="Y8">
-        <v>1.18</v>
-      </c>
-      <c r="Z8">
-        <v>3.92</v>
-      </c>
-      <c r="AA8">
-        <v>1.7</v>
-      </c>
-      <c r="AB8">
-        <v>2.1</v>
-      </c>
-      <c r="AC8">
-        <v>2.7</v>
-      </c>
-      <c r="AD8">
-        <v>1.43</v>
-      </c>
-      <c r="AE8">
-        <v>1.13</v>
-      </c>
-      <c r="AF8">
-        <v>1.7</v>
-      </c>
       <c r="AG8">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK8">
-        <v>2.45</v>
+        <v>1.05</v>
       </c>
       <c r="AL8">
         <v>0</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1197,7 +1197,7 @@
         <v>0</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1453,61 +1453,61 @@
         <v>1.47</v>
       </c>
       <c r="O7">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P7">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="Q7">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R7">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S7">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T7">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="U7">
         <v>2.38</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
         <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z7">
-        <v>3.92</v>
+        <v>3.78</v>
       </c>
       <c r="AA7">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB7">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC7">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AD7">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AE7">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF7">
         <v>1.7</v>
       </c>
       <c r="AG7">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK7">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="O8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P8">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Q8">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="R8">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T8">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="U8">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="V8">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W8">
         <v>1.1</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z8">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="AA8">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AB8">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AC8">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="AD8">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE8">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AG8">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK8">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q10">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="R10">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S10">
         <v>1.4</v>
@@ -1960,37 +1960,37 @@
         <v>2.62</v>
       </c>
       <c r="U10">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="V10">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W10">
         <v>1.06</v>
       </c>
       <c r="X10">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z10">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="AA10">
         <v>2.1</v>
       </c>
       <c r="AB10">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC10">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="AD10">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE10">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF10">
         <v>1.85</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK10">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="O11">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="P11">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2594,22 +2594,22 @@
         <v>3</v>
       </c>
       <c r="O14">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P14">
         <v>2.25</v>
       </c>
       <c r="Q14">
-        <v>4.22</v>
+        <v>3.75</v>
       </c>
       <c r="R14">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="S14">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="T14">
-        <v>2.62</v>
+        <v>2.29</v>
       </c>
       <c r="U14">
         <v>3.25</v>
@@ -2618,16 +2618,16 @@
         <v>1.33</v>
       </c>
       <c r="W14">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
         <v>1.07</v>
       </c>
       <c r="Y14">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z14">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AA14">
         <v>2.2</v>
@@ -2639,7 +2639,7 @@
         <v>3.9</v>
       </c>
       <c r="AD14">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE14">
         <v>1.06</v>
@@ -2648,7 +2648,7 @@
         <v>1.89</v>
       </c>
       <c r="AG14">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AK14">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,61 +2754,61 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="O15">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="P15">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q15">
-        <v>4.05</v>
+        <v>4.61</v>
       </c>
       <c r="R15">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="S15">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="T15">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="U15">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="V15">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="W15">
         <v>1.01</v>
       </c>
       <c r="X15">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Y15">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z15">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="AA15">
         <v>2.35</v>
       </c>
       <c r="AB15">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AC15">
         <v>5</v>
       </c>
       <c r="AD15">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE15">
         <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AG15">
         <v>1.64</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AK15">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3895,34 +3895,34 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q22">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R22">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="S22">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="T22">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="U22">
         <v>3.5</v>
       </c>
       <c r="V22">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W22">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
         <v>1.08</v>
@@ -3934,22 +3934,22 @@
         <v>2.55</v>
       </c>
       <c r="AA22">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AB22">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AC22">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AD22">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AE22">
         <v>1.02</v>
       </c>
       <c r="AF22">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AG22">
         <v>1.62</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.22</v>
+        <v>2.05</v>
       </c>
       <c r="O23">
-        <v>5.25</v>
+        <v>2.84</v>
       </c>
       <c r="P23">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="Q23">
-        <v>1.67</v>
+        <v>2.88</v>
       </c>
       <c r="R23">
-        <v>2.45</v>
+        <v>1.93</v>
       </c>
       <c r="S23">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="T23">
-        <v>3.02</v>
+        <v>2.25</v>
       </c>
       <c r="U23">
-        <v>2.48</v>
+        <v>4.1</v>
       </c>
       <c r="V23">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
+        <v>1.1</v>
+      </c>
+      <c r="Y23">
+        <v>1.56</v>
+      </c>
+      <c r="Z23">
+        <v>2.15</v>
+      </c>
+      <c r="AA23">
+        <v>2.84</v>
+      </c>
+      <c r="AB23">
+        <v>1.37</v>
+      </c>
+      <c r="AC23">
+        <v>5.65</v>
+      </c>
+      <c r="AD23">
+        <v>1.12</v>
+      </c>
+      <c r="AE23">
         <v>1.01</v>
       </c>
-      <c r="Y23">
-        <v>1.22</v>
-      </c>
-      <c r="Z23">
-        <v>3.58</v>
-      </c>
-      <c r="AA23">
-        <v>1.75</v>
-      </c>
-      <c r="AB23">
-        <v>2</v>
-      </c>
-      <c r="AC23">
-        <v>2.7</v>
-      </c>
-      <c r="AD23">
-        <v>1.36</v>
-      </c>
-      <c r="AE23">
-        <v>1.14</v>
-      </c>
       <c r="AF23">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG23">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK23">
-        <v>3.8</v>
+        <v>1.66</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA24">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="AB24">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O25">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P25">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q25">
         <v>4.5</v>
       </c>
       <c r="R25">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="S25">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="T25">
         <v>2.18</v>
       </c>
       <c r="U25">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="V25">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="W25">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X25">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Y25">
         <v>1.57</v>
       </c>
       <c r="Z25">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AA25">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AB25">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AC25">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AD25">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF25">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AG25">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AK25">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O26">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P26">
         <v>4.2</v>
@@ -4559,10 +4559,10 @@
         <v>2.3</v>
       </c>
       <c r="R26">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T26">
         <v>3.1</v>
@@ -4571,13 +4571,13 @@
         <v>2.6</v>
       </c>
       <c r="V26">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W26">
         <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
         <v>1.25</v>
@@ -4589,7 +4589,7 @@
         <v>1.87</v>
       </c>
       <c r="AB26">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AC26">
         <v>3.1</v>
@@ -4598,7 +4598,7 @@
         <v>1.36</v>
       </c>
       <c r="AE26">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF26">
         <v>1.7</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK26">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AL26">
         <v>0</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O2">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="P2">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q2">
-        <v>3.92</v>
+        <v>3.45</v>
       </c>
       <c r="R2">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T2">
         <v>2.65</v>
       </c>
       <c r="U2">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="V2">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z2">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="AA2">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB2">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC2">
-        <v>3.97</v>
+        <v>3.85</v>
       </c>
       <c r="AD2">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE2">
         <v>1.07</v>
       </c>
       <c r="AF2">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AG2">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="O3">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="P3">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="Q3">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R3">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="S3">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T3">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="U3">
-        <v>3.13</v>
+        <v>3.06</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W3">
         <v>1.04</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y3">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z3">
-        <v>3.17</v>
+        <v>2.99</v>
       </c>
       <c r="AA3">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="AB3">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AC3">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AD3">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE3">
         <v>1.09</v>
       </c>
       <c r="AF3">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AG3">
         <v>1.54</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK3">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,31 +961,31 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="O4">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P4">
-        <v>2.61</v>
+        <v>2.95</v>
       </c>
       <c r="Q4">
-        <v>2.57</v>
+        <v>2.77</v>
       </c>
       <c r="R4">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="S4">
         <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="U4">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="V4">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W4">
         <v>1.07</v>
@@ -994,31 +994,31 @@
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>4.48</v>
+        <v>4.45</v>
       </c>
       <c r="AA4">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB4">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AC4">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="AD4">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AE4">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF4">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AG4">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.27</v>
       </c>
       <c r="AK4">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.47</v>
+        <v>6.8</v>
       </c>
       <c r="O7">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P7">
-        <v>5.7</v>
+        <v>1.31</v>
       </c>
       <c r="Q7">
-        <v>2.02</v>
+        <v>8.5</v>
       </c>
       <c r="R7">
-        <v>2.23</v>
+        <v>2.42</v>
       </c>
       <c r="S7">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T7">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="U7">
-        <v>2.38</v>
+        <v>2.76</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z7">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="AA7">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AB7">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AC7">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="AD7">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE7">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF7">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK7">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>6.8</v>
+        <v>1.47</v>
       </c>
       <c r="O8">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P8">
-        <v>1.31</v>
+        <v>5.7</v>
       </c>
       <c r="Q8">
-        <v>8.5</v>
+        <v>2.02</v>
       </c>
       <c r="R8">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="S8">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T8">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="U8">
-        <v>2.76</v>
+        <v>2.38</v>
       </c>
       <c r="V8">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z8">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="AA8">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB8">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC8">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="AD8">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AE8">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF8">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AG8">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK8">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="O11">
-        <v>3.09</v>
+        <v>3.5</v>
       </c>
       <c r="P11">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2268,16 +2268,16 @@
         <v>3.7</v>
       </c>
       <c r="O12">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P12">
         <v>1.7</v>
       </c>
       <c r="Q12">
-        <v>4.19</v>
+        <v>4.24</v>
       </c>
       <c r="R12">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S12">
         <v>1.21</v>
@@ -2295,28 +2295,28 @@
         <v>1.13</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z12">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="AA12">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AB12">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AC12">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AD12">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE12">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AF12">
         <v>1.44</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.94</v>
+        <v>1.18</v>
       </c>
       <c r="AK12">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2434,10 +2434,10 @@
         <v>4</v>
       </c>
       <c r="P13">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q13">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="R13">
         <v>2.29</v>
@@ -2446,10 +2446,10 @@
         <v>1.22</v>
       </c>
       <c r="T13">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="U13">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="V13">
         <v>1.63</v>
@@ -2470,7 +2470,7 @@
         <v>1.44</v>
       </c>
       <c r="AB13">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AC13">
         <v>2.3</v>
@@ -2479,7 +2479,7 @@
         <v>1.6</v>
       </c>
       <c r="AE13">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF13">
         <v>1.44</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK13">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,80 +2591,80 @@
         </is>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="O14">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P14">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q14">
-        <v>3.75</v>
+        <v>4.61</v>
       </c>
       <c r="R14">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="S14">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="T14">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="U14">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="V14">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="W14">
+        <v>1.01</v>
+      </c>
+      <c r="X14">
+        <v>1.09</v>
+      </c>
+      <c r="Y14">
+        <v>1.48</v>
+      </c>
+      <c r="Z14">
+        <v>2.49</v>
+      </c>
+      <c r="AA14">
+        <v>2.35</v>
+      </c>
+      <c r="AB14">
+        <v>1.5</v>
+      </c>
+      <c r="AC14">
+        <v>5</v>
+      </c>
+      <c r="AD14">
+        <v>1.15</v>
+      </c>
+      <c r="AE14">
         <v>1.02</v>
       </c>
-      <c r="X14">
-        <v>1.07</v>
-      </c>
-      <c r="Y14">
+      <c r="AF14">
+        <v>1.98</v>
+      </c>
+      <c r="AG14">
+        <v>1.64</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
         <v>1.38</v>
       </c>
-      <c r="Z14">
-        <v>2.7</v>
-      </c>
-      <c r="AA14">
-        <v>2.2</v>
-      </c>
-      <c r="AB14">
-        <v>1.62</v>
-      </c>
-      <c r="AC14">
-        <v>3.9</v>
-      </c>
-      <c r="AD14">
-        <v>1.18</v>
-      </c>
-      <c r="AE14">
-        <v>1.06</v>
-      </c>
-      <c r="AF14">
-        <v>1.89</v>
-      </c>
-      <c r="AG14">
-        <v>1.8</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.33</v>
-      </c>
       <c r="AK14">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.32</v>
+        <v>3</v>
       </c>
       <c r="O15">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P15">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q15">
-        <v>4.61</v>
+        <v>3.75</v>
       </c>
       <c r="R15">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="S15">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="T15">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="U15">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="V15">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X15">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y15">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="Z15">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AA15">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB15">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC15">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AD15">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE15">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AG15">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AK15">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2920,37 +2920,37 @@
         <v>1.18</v>
       </c>
       <c r="O16">
-        <v>6.05</v>
+        <v>6.25</v>
       </c>
       <c r="P16">
-        <v>6.9</v>
+        <v>7.14</v>
       </c>
       <c r="Q16">
         <v>1.61</v>
       </c>
       <c r="R16">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="S16">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="T16">
         <v>4.8</v>
       </c>
       <c r="U16">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="V16">
         <v>1.97</v>
       </c>
       <c r="W16">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z16">
         <v>8</v>
@@ -2959,22 +2959,22 @@
         <v>1.22</v>
       </c>
       <c r="AB16">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AC16">
         <v>1.62</v>
       </c>
       <c r="AD16">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AE16">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AF16">
         <v>1.5</v>
       </c>
       <c r="AG16">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AK16">
-        <v>3.78</v>
+        <v>3.42</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="O17">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="P17">
         <v>2.14</v>
@@ -3092,46 +3092,46 @@
         <v>3.1</v>
       </c>
       <c r="R17">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="S17">
         <v>1.17</v>
       </c>
       <c r="T17">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="U17">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="V17">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="W17">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z17">
-        <v>6.25</v>
+        <v>4.9</v>
       </c>
       <c r="AA17">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AB17">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="AC17">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AD17">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AE17">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AF17">
         <v>1.33</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AK17">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,22 +3243,22 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="O18">
         <v>5.35</v>
       </c>
       <c r="P18">
-        <v>5.82</v>
+        <v>4.65</v>
       </c>
       <c r="Q18">
         <v>1.8</v>
       </c>
       <c r="R18">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="S18">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="T18">
         <v>4.8</v>
@@ -3267,7 +3267,7 @@
         <v>1.77</v>
       </c>
       <c r="V18">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="W18">
         <v>1.3</v>
@@ -3282,13 +3282,13 @@
         <v>9</v>
       </c>
       <c r="AA18">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AB18">
         <v>3.77</v>
       </c>
       <c r="AC18">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AD18">
         <v>2.22</v>
@@ -3297,10 +3297,10 @@
         <v>1.57</v>
       </c>
       <c r="AF18">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG18">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK18">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,28 +3406,28 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="O19">
+        <v>4.4</v>
+      </c>
+      <c r="P19">
         <v>4.6</v>
       </c>
-      <c r="P19">
-        <v>4.29</v>
-      </c>
       <c r="Q19">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="R19">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="S19">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T19">
         <v>5</v>
       </c>
       <c r="U19">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="V19">
         <v>1.93</v>
@@ -3439,31 +3439,31 @@
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z19">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA19">
         <v>1.28</v>
       </c>
       <c r="AB19">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="AC19">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AD19">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AE19">
         <v>1.5</v>
       </c>
       <c r="AF19">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AG19">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.16</v>
       </c>
       <c r="AK19">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="O20">
         <v>3.8</v>
       </c>
       <c r="P20">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="Q20">
         <v>2.63</v>
       </c>
       <c r="R20">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="S20">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="U20">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V20">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="W20">
         <v>1.25</v>
@@ -3602,13 +3602,13 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z20">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="AA20">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB20">
         <v>3.42</v>
@@ -3617,16 +3617,16 @@
         <v>1.68</v>
       </c>
       <c r="AD20">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AE20">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AF20">
         <v>1.25</v>
       </c>
       <c r="AG20">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,43 +3732,43 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="O21">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="P21">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="Q21">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="R21">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="S21">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T21">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="U21">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="V21">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="W21">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z21">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AA21">
         <v>1.3</v>
@@ -3783,13 +3783,13 @@
         <v>2.1</v>
       </c>
       <c r="AE21">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AF21">
         <v>1.29</v>
       </c>
       <c r="AG21">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O22">
         <v>2.8</v>
       </c>
       <c r="P22">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="Q22">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R22">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="S22">
         <v>1.59</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O23">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="P23">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="Q23">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="R23">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="S23">
         <v>1.57</v>
@@ -4106,16 +4106,16 @@
         <v>5.65</v>
       </c>
       <c r="AD23">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE23">
         <v>1.01</v>
       </c>
       <c r="AF23">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG23">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>1.7</v>
       </c>
       <c r="R24">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="S24">
         <v>1.3</v>
@@ -4263,7 +4263,7 @@
         <v>1.75</v>
       </c>
       <c r="AB24">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC24">
         <v>2.7</v>
@@ -4272,7 +4272,7 @@
         <v>1.37</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF24">
         <v>2.2</v>
@@ -4384,25 +4384,25 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="O25">
         <v>2.9</v>
       </c>
       <c r="P25">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q25">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="R25">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="S25">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="T25">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="U25">
         <v>4</v>
@@ -4411,7 +4411,7 @@
         <v>1.19</v>
       </c>
       <c r="W25">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
         <v>1.08</v>
@@ -4420,28 +4420,28 @@
         <v>1.57</v>
       </c>
       <c r="Z25">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AA25">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="AB25">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AC25">
-        <v>5.3</v>
+        <v>5.55</v>
       </c>
       <c r="AD25">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF25">
         <v>2.28</v>
       </c>
       <c r="AG25">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AK25">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4556,7 +4556,7 @@
         <v>4.2</v>
       </c>
       <c r="Q26">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R26">
         <v>2.25</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,25 +4710,25 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="O27">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="P27">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q27">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="R27">
         <v>1.85</v>
       </c>
       <c r="S27">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="T27">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="U27">
         <v>3.5</v>
@@ -4737,10 +4737,10 @@
         <v>1.22</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y27">
         <v>1.53</v>
@@ -4749,22 +4749,22 @@
         <v>2.38</v>
       </c>
       <c r="AA27">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AB27">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AC27">
-        <v>5.42</v>
+        <v>5.5</v>
       </c>
       <c r="AD27">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE27">
         <v>1.01</v>
       </c>
       <c r="AF27">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AG27">
         <v>1.7</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK27">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G28">
@@ -4869,68 +4869,68 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N28">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="O28">
-        <v>2.55</v>
+        <v>2.91</v>
       </c>
       <c r="P28">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="Q28">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Z28">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="AA28">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="AB28">
         <v>1.36</v>
       </c>
       <c r="AC28">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK28">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.23</v>
+        <v>1.6</v>
       </c>
       <c r="O29">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="P29">
-        <v>3.38</v>
+        <v>21</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y29">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="Z29">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AA29">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="AB29">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G30">
@@ -5195,65 +5195,65 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30">
-        <v>1.17</v>
+        <v>2.25</v>
       </c>
       <c r="O30">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="P30">
-        <v>21</v>
+        <v>3.42</v>
       </c>
       <c r="Q30">
-        <v>2.31</v>
+        <v>3.14</v>
       </c>
       <c r="R30">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="S30">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="T30">
-        <v>2.37</v>
+        <v>2.08</v>
       </c>
       <c r="U30">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="V30">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="W30">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X30">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y30">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Z30">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AA30">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="AB30">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC30">
         <v>5.5</v>
       </c>
       <c r="AD30">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AE30">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="AG30">
         <v>1.55</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AK30">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,19 +5362,19 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="O31">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="P31">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q31">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R31">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="S31">
         <v>1.57</v>
@@ -5383,10 +5383,10 @@
         <v>2.17</v>
       </c>
       <c r="U31">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="V31">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W31">
         <v>1.03</v>
@@ -5395,7 +5395,7 @@
         <v>1.12</v>
       </c>
       <c r="Y31">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="Z31">
         <v>2.2</v>
@@ -5416,10 +5416,10 @@
         <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG31">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AK31">
         <v>1.53</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,65 +5525,65 @@
         </is>
       </c>
       <c r="N32">
+        <v>1.9</v>
+      </c>
+      <c r="O32">
+        <v>3.7</v>
+      </c>
+      <c r="P32">
+        <v>3.88</v>
+      </c>
+      <c r="Q32">
         <v>2.4</v>
       </c>
-      <c r="O32">
-        <v>3</v>
-      </c>
-      <c r="P32">
-        <v>2.68</v>
-      </c>
-      <c r="Q32">
-        <v>3</v>
-      </c>
       <c r="R32">
+        <v>2.25</v>
+      </c>
+      <c r="S32">
+        <v>1.3</v>
+      </c>
+      <c r="T32">
+        <v>3.2</v>
+      </c>
+      <c r="U32">
+        <v>2.5</v>
+      </c>
+      <c r="V32">
+        <v>1.5</v>
+      </c>
+      <c r="W32">
+        <v>1.07</v>
+      </c>
+      <c r="X32">
+        <v>1.05</v>
+      </c>
+      <c r="Y32">
+        <v>1.23</v>
+      </c>
+      <c r="Z32">
+        <v>3.8</v>
+      </c>
+      <c r="AA32">
+        <v>1.82</v>
+      </c>
+      <c r="AB32">
+        <v>2</v>
+      </c>
+      <c r="AC32">
+        <v>3.1</v>
+      </c>
+      <c r="AD32">
+        <v>1.39</v>
+      </c>
+      <c r="AE32">
+        <v>1.12</v>
+      </c>
+      <c r="AF32">
+        <v>1.65</v>
+      </c>
+      <c r="AG32">
         <v>2.15</v>
       </c>
-      <c r="S32">
-        <v>1.36</v>
-      </c>
-      <c r="T32">
-        <v>2.56</v>
-      </c>
-      <c r="U32">
-        <v>3</v>
-      </c>
-      <c r="V32">
-        <v>1.34</v>
-      </c>
-      <c r="W32">
-        <v>1.06</v>
-      </c>
-      <c r="X32">
-        <v>1.02</v>
-      </c>
-      <c r="Y32">
-        <v>1.33</v>
-      </c>
-      <c r="Z32">
-        <v>3.25</v>
-      </c>
-      <c r="AA32">
-        <v>1.99</v>
-      </c>
-      <c r="AB32">
-        <v>1.73</v>
-      </c>
-      <c r="AC32">
-        <v>3.8</v>
-      </c>
-      <c r="AD32">
-        <v>1.25</v>
-      </c>
-      <c r="AE32">
-        <v>1.07</v>
-      </c>
-      <c r="AF32">
-        <v>1.73</v>
-      </c>
-      <c r="AG32">
-        <v>2</v>
-      </c>
       <c r="AH32" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P33">
-        <v>3.28</v>
+        <v>6.75</v>
       </c>
       <c r="Q33">
-        <v>2.4</v>
+        <v>2.01</v>
       </c>
       <c r="R33">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T33">
-        <v>2.86</v>
+        <v>2.59</v>
       </c>
       <c r="U33">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="V33">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W33">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
+        <v>1.05</v>
+      </c>
+      <c r="Y33">
+        <v>1.33</v>
+      </c>
+      <c r="Z33">
+        <v>3.25</v>
+      </c>
+      <c r="AA33">
+        <v>2.05</v>
+      </c>
+      <c r="AB33">
+        <v>1.68</v>
+      </c>
+      <c r="AC33">
+        <v>3.5</v>
+      </c>
+      <c r="AD33">
+        <v>1.29</v>
+      </c>
+      <c r="AE33">
         <v>1.04</v>
       </c>
-      <c r="Y33">
-        <v>1.22</v>
-      </c>
-      <c r="Z33">
-        <v>3.7</v>
-      </c>
-      <c r="AA33">
-        <v>1.8</v>
-      </c>
-      <c r="AB33">
-        <v>1.95</v>
-      </c>
-      <c r="AC33">
-        <v>3.1</v>
-      </c>
-      <c r="AD33">
-        <v>1.36</v>
-      </c>
-      <c r="AE33">
-        <v>1.1</v>
-      </c>
       <c r="AF33">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AK33">
-        <v>1.75</v>
+        <v>2.56</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.51</v>
+        <v>2.37</v>
       </c>
       <c r="O34">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P34">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="Q34">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="R34">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T34">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="U34">
-        <v>2.8</v>
+        <v>2.27</v>
       </c>
       <c r="V34">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="W34">
+        <v>1.12</v>
+      </c>
+      <c r="X34">
         <v>1.03</v>
       </c>
-      <c r="X34">
-        <v>1.05</v>
-      </c>
       <c r="Y34">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="Z34">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="AA34">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AB34">
-        <v>1.74</v>
+        <v>2.43</v>
       </c>
       <c r="AC34">
-        <v>3.8</v>
+        <v>2.29</v>
       </c>
       <c r="AD34">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AE34">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AF34">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="AG34">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>2.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="O35">
-        <v>3.66</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="Q35">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="R35">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S35">
+        <v>1.36</v>
+      </c>
+      <c r="T35">
+        <v>2.58</v>
+      </c>
+      <c r="U35">
+        <v>3</v>
+      </c>
+      <c r="V35">
+        <v>1.34</v>
+      </c>
+      <c r="W35">
+        <v>1.05</v>
+      </c>
+      <c r="X35">
+        <v>1.06</v>
+      </c>
+      <c r="Y35">
+        <v>1.33</v>
+      </c>
+      <c r="Z35">
+        <v>3.25</v>
+      </c>
+      <c r="AA35">
+        <v>2.05</v>
+      </c>
+      <c r="AB35">
+        <v>1.75</v>
+      </c>
+      <c r="AC35">
+        <v>3.8</v>
+      </c>
+      <c r="AD35">
         <v>1.25</v>
       </c>
-      <c r="T35">
-        <v>3.5</v>
-      </c>
-      <c r="U35">
-        <v>2.29</v>
-      </c>
-      <c r="V35">
-        <v>1.58</v>
-      </c>
-      <c r="W35">
-        <v>1.12</v>
-      </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
-        <v>1.18</v>
-      </c>
-      <c r="Z35">
-        <v>4.55</v>
-      </c>
-      <c r="AA35">
-        <v>1.55</v>
-      </c>
-      <c r="AB35">
-        <v>2.41</v>
-      </c>
-      <c r="AC35">
-        <v>2.32</v>
-      </c>
-      <c r="AD35">
+      <c r="AE35">
+        <v>1.07</v>
+      </c>
+      <c r="AF35">
+        <v>1.8</v>
+      </c>
+      <c r="AG35">
+        <v>1.95</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>1.29</v>
+      </c>
+      <c r="AK35">
         <v>1.49</v>
-      </c>
-      <c r="AE35">
-        <v>1.21</v>
-      </c>
-      <c r="AF35">
-        <v>1.5</v>
-      </c>
-      <c r="AG35">
-        <v>2.55</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.3</v>
-      </c>
-      <c r="AK35">
-        <v>1.53</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O36">
         <v>3.5</v>
@@ -6186,7 +6186,7 @@
         <v>2.05</v>
       </c>
       <c r="Q36">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="R36">
         <v>2.27</v>
@@ -6195,7 +6195,7 @@
         <v>1.25</v>
       </c>
       <c r="T36">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U36">
         <v>2.2</v>
@@ -6204,7 +6204,7 @@
         <v>1.62</v>
       </c>
       <c r="W36">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X36">
         <v>1.02</v>
@@ -6213,10 +6213,10 @@
         <v>1.12</v>
       </c>
       <c r="Z36">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="AA36">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB36">
         <v>2.35</v>
@@ -6225,16 +6225,16 @@
         <v>2.2</v>
       </c>
       <c r="AD36">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AE36">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF36">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AG36">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="O37">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="P37">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="Q37">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="R37">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="S37">
         <v>1.22</v>
@@ -6364,40 +6364,40 @@
         <v>2.03</v>
       </c>
       <c r="V37">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="W37">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
         <v>1.13</v>
       </c>
       <c r="Z37">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="AA37">
         <v>1.4</v>
       </c>
       <c r="AB37">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AC37">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AD37">
         <v>1.76</v>
       </c>
       <c r="AE37">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF37">
         <v>1.67</v>
       </c>
       <c r="AG37">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.08</v>
       </c>
       <c r="AK37">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,25 +6503,25 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="O38">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P38">
-        <v>3.01</v>
+        <v>3.1</v>
       </c>
       <c r="Q38">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="R38">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S38">
         <v>1.32</v>
       </c>
       <c r="T38">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="U38">
         <v>2.7</v>
@@ -6536,31 +6536,31 @@
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA38">
         <v>1.85</v>
       </c>
       <c r="AB38">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AC38">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD38">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE38">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF38">
         <v>1.68</v>
       </c>
       <c r="AG38">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK38">
         <v>1.52</v>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="O39">
         <v>4.7</v>
@@ -6675,10 +6675,10 @@
         <v>6.88</v>
       </c>
       <c r="Q39">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="R39">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="S39">
         <v>1.2</v>
@@ -6687,10 +6687,10 @@
         <v>4</v>
       </c>
       <c r="U39">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V39">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W39">
         <v>1.18</v>
@@ -6702,10 +6702,10 @@
         <v>1.09</v>
       </c>
       <c r="Z39">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="AA39">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB39">
         <v>2.56</v>
@@ -6720,10 +6720,10 @@
         <v>1.25</v>
       </c>
       <c r="AF39">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG39">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AK39">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q40">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R40">
         <v>2.25</v>
       </c>
       <c r="S40">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T40">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="U40">
         <v>2.4</v>
@@ -6868,25 +6868,25 @@
         <v>4</v>
       </c>
       <c r="AA40">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB40">
         <v>2.12</v>
       </c>
       <c r="AC40">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="AD40">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE40">
         <v>1.14</v>
       </c>
       <c r="AF40">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG40">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="O41">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="P41">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="Q41">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="R41">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="S41">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T41">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="U41">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="V41">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="W41">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z41">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA41">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB41">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AC41">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AD41">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AE41">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AF41">
         <v>1.53</v>
       </c>
       <c r="AG41">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AK41">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>2.45</v>
       </c>
       <c r="O42">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="P42">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7318,22 +7318,22 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="O43">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P43">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q43">
         <v>2.8</v>
       </c>
       <c r="R43">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="S43">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T43">
         <v>2.44</v>
@@ -7351,31 +7351,31 @@
         <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z43">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AA43">
         <v>2.25</v>
       </c>
       <c r="AB43">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC43">
         <v>4.1</v>
       </c>
       <c r="AD43">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF43">
         <v>1.91</v>
       </c>
       <c r="AG43">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK43">
         <v>1.62</v>
@@ -7481,28 +7481,28 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q44">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="R44">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="S44">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T44">
         <v>2.82</v>
       </c>
       <c r="U44">
-        <v>2.28</v>
+        <v>2.53</v>
       </c>
       <c r="V44">
         <v>1.43</v>
@@ -7514,31 +7514,31 @@
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z44">
         <v>3.5</v>
       </c>
       <c r="AA44">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB44">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AC44">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="AD44">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE44">
         <v>1.1</v>
       </c>
       <c r="AF44">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AG44">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AK44">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AL44">
         <v>0</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>6.8</v>
+        <v>1.47</v>
       </c>
       <c r="O7">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P7">
-        <v>1.31</v>
+        <v>5.7</v>
       </c>
       <c r="Q7">
-        <v>8.5</v>
+        <v>2.02</v>
       </c>
       <c r="R7">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="S7">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T7">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="U7">
-        <v>2.76</v>
+        <v>2.38</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z7">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="AA7">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB7">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC7">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="AD7">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AE7">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF7">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AG7">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK7">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.47</v>
+        <v>6.8</v>
       </c>
       <c r="O8">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P8">
-        <v>5.7</v>
+        <v>1.31</v>
       </c>
       <c r="Q8">
-        <v>2.02</v>
+        <v>8.5</v>
       </c>
       <c r="R8">
-        <v>2.23</v>
+        <v>2.42</v>
       </c>
       <c r="S8">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T8">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="U8">
-        <v>2.38</v>
+        <v>2.76</v>
       </c>
       <c r="V8">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z8">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="AA8">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AB8">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AC8">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="AD8">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE8">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AG8">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK8">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.32</v>
+        <v>3</v>
       </c>
       <c r="O14">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P14">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q14">
-        <v>4.61</v>
+        <v>3.75</v>
       </c>
       <c r="R14">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="S14">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="T14">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="U14">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="V14">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y14">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="Z14">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AA14">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB14">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC14">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AD14">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE14">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AG14">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AK14">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,80 +2754,80 @@
         </is>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="O15">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P15">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q15">
-        <v>3.75</v>
+        <v>4.61</v>
       </c>
       <c r="R15">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="S15">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="T15">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="U15">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="V15">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="W15">
+        <v>1.01</v>
+      </c>
+      <c r="X15">
+        <v>1.09</v>
+      </c>
+      <c r="Y15">
+        <v>1.48</v>
+      </c>
+      <c r="Z15">
+        <v>2.49</v>
+      </c>
+      <c r="AA15">
+        <v>2.35</v>
+      </c>
+      <c r="AB15">
+        <v>1.5</v>
+      </c>
+      <c r="AC15">
+        <v>5</v>
+      </c>
+      <c r="AD15">
+        <v>1.15</v>
+      </c>
+      <c r="AE15">
         <v>1.02</v>
       </c>
-      <c r="X15">
-        <v>1.07</v>
-      </c>
-      <c r="Y15">
+      <c r="AF15">
+        <v>1.98</v>
+      </c>
+      <c r="AG15">
+        <v>1.64</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
         <v>1.38</v>
       </c>
-      <c r="Z15">
-        <v>2.7</v>
-      </c>
-      <c r="AA15">
-        <v>2.2</v>
-      </c>
-      <c r="AB15">
-        <v>1.62</v>
-      </c>
-      <c r="AC15">
-        <v>3.9</v>
-      </c>
-      <c r="AD15">
-        <v>1.18</v>
-      </c>
-      <c r="AE15">
-        <v>1.06</v>
-      </c>
-      <c r="AF15">
-        <v>1.89</v>
-      </c>
-      <c r="AG15">
-        <v>1.8</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.33</v>
-      </c>
       <c r="AK15">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="O20">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P20">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q20">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="R20">
         <v>2.63</v>
       </c>
       <c r="S20">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T20">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="U20">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="V20">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W20">
         <v>1.25</v>
@@ -3602,47 +3602,47 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z20">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AA20">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AB20">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="AC20">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AD20">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AE20">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AF20">
+        <v>1.29</v>
+      </c>
+      <c r="AG20">
+        <v>3.4</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
         <v>1.25</v>
       </c>
-      <c r="AG20">
-        <v>3.7</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.2</v>
-      </c>
       <c r="AK20">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,31 +3732,31 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="O21">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P21">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q21">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="R21">
         <v>2.63</v>
       </c>
       <c r="S21">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T21">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="U21">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="V21">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="W21">
         <v>1.25</v>
@@ -3765,31 +3765,31 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Z21">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AA21">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AB21">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="AC21">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AD21">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AE21">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AF21">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AG21">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2</v>
+        <v>3.74</v>
       </c>
       <c r="O23">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="P23">
-        <v>3.7</v>
+        <v>1.95</v>
       </c>
       <c r="Q23">
-        <v>2.78</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="S23">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="T23">
         <v>2.25</v>
       </c>
       <c r="U23">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="V23">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W23">
         <v>1.03</v>
       </c>
       <c r="X23">
+        <v>1.08</v>
+      </c>
+      <c r="Y23">
+        <v>1.57</v>
+      </c>
+      <c r="Z23">
+        <v>2.27</v>
+      </c>
+      <c r="AA23">
+        <v>2.62</v>
+      </c>
+      <c r="AB23">
+        <v>1.36</v>
+      </c>
+      <c r="AC23">
+        <v>5.55</v>
+      </c>
+      <c r="AD23">
         <v>1.1</v>
-      </c>
-      <c r="Y23">
-        <v>1.56</v>
-      </c>
-      <c r="Z23">
-        <v>2.15</v>
-      </c>
-      <c r="AA23">
-        <v>2.84</v>
-      </c>
-      <c r="AB23">
-        <v>1.37</v>
-      </c>
-      <c r="AC23">
-        <v>5.65</v>
-      </c>
-      <c r="AD23">
-        <v>1.13</v>
       </c>
       <c r="AE23">
         <v>1.01</v>
       </c>
       <c r="AF23">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AG23">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
+        <v>1.32</v>
+      </c>
+      <c r="AK23">
         <v>1.16</v>
-      </c>
-      <c r="AK23">
-        <v>1.66</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.74</v>
+        <v>2</v>
       </c>
       <c r="O25">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="P25">
-        <v>1.95</v>
+        <v>3.7</v>
       </c>
       <c r="Q25">
-        <v>5</v>
+        <v>2.78</v>
       </c>
       <c r="R25">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="S25">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="T25">
         <v>2.25</v>
       </c>
       <c r="U25">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="V25">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W25">
         <v>1.03</v>
       </c>
       <c r="X25">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y25">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Z25">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AA25">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="AB25">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AC25">
-        <v>5.55</v>
+        <v>5.65</v>
       </c>
       <c r="AD25">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE25">
         <v>1.01</v>
       </c>
       <c r="AF25">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AG25">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AK25">
-        <v>1.16</v>
+        <v>1.66</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G29">
@@ -5032,65 +5032,65 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="O29">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="P29">
-        <v>21</v>
+        <v>3.42</v>
       </c>
       <c r="Q29">
-        <v>2.31</v>
+        <v>3.14</v>
       </c>
       <c r="R29">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="S29">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="T29">
-        <v>2.37</v>
+        <v>2.08</v>
       </c>
       <c r="U29">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="V29">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="W29">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y29">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Z29">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AA29">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="AB29">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC29">
         <v>5.5</v>
       </c>
       <c r="AD29">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AE29">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF29">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="AG29">
         <v>1.55</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AK29">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G30">
@@ -5195,65 +5195,65 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="O30">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="P30">
-        <v>3.42</v>
+        <v>21</v>
       </c>
       <c r="Q30">
-        <v>3.14</v>
+        <v>2.31</v>
       </c>
       <c r="R30">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="S30">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="T30">
-        <v>2.08</v>
+        <v>2.37</v>
       </c>
       <c r="U30">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="V30">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="W30">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X30">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y30">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="Z30">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AA30">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="AB30">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC30">
         <v>5.5</v>
       </c>
       <c r="AD30">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AE30">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF30">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="AG30">
         <v>1.55</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AK30">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6189,7 +6189,7 @@
         <v>3.3</v>
       </c>
       <c r="R36">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="S36">
         <v>1.25</v>
@@ -6219,7 +6219,7 @@
         <v>1.53</v>
       </c>
       <c r="AB36">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC36">
         <v>2.2</v>
@@ -6231,10 +6231,10 @@
         <v>1.22</v>
       </c>
       <c r="AF36">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG36">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>6.88</v>
       </c>
       <c r="Q39">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R39">
         <v>2.7</v>
@@ -6699,7 +6699,7 @@
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z39">
         <v>5.75</v>
@@ -6708,22 +6708,22 @@
         <v>1.4</v>
       </c>
       <c r="AB39">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="AC39">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AD39">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AE39">
         <v>1.25</v>
       </c>
       <c r="AF39">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG39">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="O41">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="P41">
         <v>5.7</v>
@@ -7031,16 +7031,16 @@
         <v>6.5</v>
       </c>
       <c r="AA41">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB41">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="AC41">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AD41">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE41">
         <v>1.27</v>
@@ -7049,7 +7049,7 @@
         <v>1.53</v>
       </c>
       <c r="AG41">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -2271,22 +2271,22 @@
         <v>3.85</v>
       </c>
       <c r="P12">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q12">
-        <v>4.24</v>
+        <v>4.3</v>
       </c>
       <c r="R12">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S12">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T12">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="U12">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V12">
         <v>1.64</v>
@@ -2301,10 +2301,10 @@
         <v>1.09</v>
       </c>
       <c r="Z12">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AA12">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AB12">
         <v>2.5</v>
@@ -2316,13 +2316,13 @@
         <v>1.65</v>
       </c>
       <c r="AE12">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF12">
         <v>1.44</v>
       </c>
       <c r="AG12">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.18</v>
+        <v>1.94</v>
       </c>
       <c r="AK12">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,80 +2591,80 @@
         </is>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="O14">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P14">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q14">
-        <v>3.75</v>
+        <v>4.61</v>
       </c>
       <c r="R14">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="S14">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="T14">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="U14">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="V14">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="W14">
+        <v>1.01</v>
+      </c>
+      <c r="X14">
+        <v>1.09</v>
+      </c>
+      <c r="Y14">
+        <v>1.48</v>
+      </c>
+      <c r="Z14">
+        <v>2.49</v>
+      </c>
+      <c r="AA14">
+        <v>2.35</v>
+      </c>
+      <c r="AB14">
+        <v>1.5</v>
+      </c>
+      <c r="AC14">
+        <v>5</v>
+      </c>
+      <c r="AD14">
+        <v>1.15</v>
+      </c>
+      <c r="AE14">
         <v>1.02</v>
       </c>
-      <c r="X14">
-        <v>1.07</v>
-      </c>
-      <c r="Y14">
+      <c r="AF14">
+        <v>1.98</v>
+      </c>
+      <c r="AG14">
+        <v>1.64</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
         <v>1.38</v>
       </c>
-      <c r="Z14">
-        <v>2.7</v>
-      </c>
-      <c r="AA14">
-        <v>2.2</v>
-      </c>
-      <c r="AB14">
-        <v>1.62</v>
-      </c>
-      <c r="AC14">
-        <v>3.9</v>
-      </c>
-      <c r="AD14">
-        <v>1.18</v>
-      </c>
-      <c r="AE14">
-        <v>1.06</v>
-      </c>
-      <c r="AF14">
-        <v>1.89</v>
-      </c>
-      <c r="AG14">
-        <v>1.8</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.33</v>
-      </c>
       <c r="AK14">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.32</v>
+        <v>3</v>
       </c>
       <c r="O15">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P15">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q15">
-        <v>4.61</v>
+        <v>3.75</v>
       </c>
       <c r="R15">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="S15">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="T15">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="U15">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="V15">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X15">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y15">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="Z15">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AA15">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB15">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC15">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AD15">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE15">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AG15">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AK15">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.22</v>
+        <v>2</v>
       </c>
       <c r="O24">
-        <v>5.25</v>
+        <v>2.75</v>
       </c>
       <c r="P24">
-        <v>9.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q24">
-        <v>1.7</v>
+        <v>2.78</v>
       </c>
       <c r="R24">
-        <v>2.55</v>
+        <v>1.77</v>
       </c>
       <c r="S24">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="T24">
-        <v>2.96</v>
+        <v>2.25</v>
       </c>
       <c r="U24">
-        <v>2.48</v>
+        <v>4.1</v>
       </c>
       <c r="V24">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X24">
+        <v>1.1</v>
+      </c>
+      <c r="Y24">
+        <v>1.56</v>
+      </c>
+      <c r="Z24">
+        <v>2.15</v>
+      </c>
+      <c r="AA24">
+        <v>2.84</v>
+      </c>
+      <c r="AB24">
+        <v>1.37</v>
+      </c>
+      <c r="AC24">
+        <v>5.65</v>
+      </c>
+      <c r="AD24">
+        <v>1.13</v>
+      </c>
+      <c r="AE24">
         <v>1.01</v>
       </c>
-      <c r="Y24">
-        <v>1.2</v>
-      </c>
-      <c r="Z24">
-        <v>4.1</v>
-      </c>
-      <c r="AA24">
-        <v>1.75</v>
-      </c>
-      <c r="AB24">
-        <v>2</v>
-      </c>
-      <c r="AC24">
-        <v>2.7</v>
-      </c>
-      <c r="AD24">
-        <v>1.37</v>
-      </c>
-      <c r="AE24">
-        <v>1.11</v>
-      </c>
       <c r="AF24">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG24">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AK24">
-        <v>3.45</v>
+        <v>1.66</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,80 +4384,80 @@
         </is>
       </c>
       <c r="N25">
+        <v>1.22</v>
+      </c>
+      <c r="O25">
+        <v>5.25</v>
+      </c>
+      <c r="P25">
+        <v>9.5</v>
+      </c>
+      <c r="Q25">
+        <v>1.7</v>
+      </c>
+      <c r="R25">
+        <v>2.55</v>
+      </c>
+      <c r="S25">
+        <v>1.3</v>
+      </c>
+      <c r="T25">
+        <v>2.96</v>
+      </c>
+      <c r="U25">
+        <v>2.48</v>
+      </c>
+      <c r="V25">
+        <v>1.44</v>
+      </c>
+      <c r="W25">
+        <v>1.08</v>
+      </c>
+      <c r="X25">
+        <v>1.01</v>
+      </c>
+      <c r="Y25">
+        <v>1.2</v>
+      </c>
+      <c r="Z25">
+        <v>4.1</v>
+      </c>
+      <c r="AA25">
+        <v>1.75</v>
+      </c>
+      <c r="AB25">
         <v>2</v>
       </c>
-      <c r="O25">
-        <v>2.75</v>
-      </c>
-      <c r="P25">
-        <v>3.7</v>
-      </c>
-      <c r="Q25">
-        <v>2.78</v>
-      </c>
-      <c r="R25">
-        <v>1.77</v>
-      </c>
-      <c r="S25">
+      <c r="AC25">
+        <v>2.7</v>
+      </c>
+      <c r="AD25">
+        <v>1.37</v>
+      </c>
+      <c r="AE25">
+        <v>1.11</v>
+      </c>
+      <c r="AF25">
+        <v>2.2</v>
+      </c>
+      <c r="AG25">
         <v>1.57</v>
       </c>
-      <c r="T25">
-        <v>2.25</v>
-      </c>
-      <c r="U25">
-        <v>4.1</v>
-      </c>
-      <c r="V25">
-        <v>1.2</v>
-      </c>
-      <c r="W25">
-        <v>1.03</v>
-      </c>
-      <c r="X25">
-        <v>1.1</v>
-      </c>
-      <c r="Y25">
-        <v>1.56</v>
-      </c>
-      <c r="Z25">
-        <v>2.15</v>
-      </c>
-      <c r="AA25">
-        <v>2.84</v>
-      </c>
-      <c r="AB25">
-        <v>1.37</v>
-      </c>
-      <c r="AC25">
-        <v>5.65</v>
-      </c>
-      <c r="AD25">
-        <v>1.13</v>
-      </c>
-      <c r="AE25">
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
         <v>1.01</v>
       </c>
-      <c r="AF25">
-        <v>2.3</v>
-      </c>
-      <c r="AG25">
-        <v>1.5</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.16</v>
-      </c>
       <c r="AK25">
-        <v>1.66</v>
+        <v>3.45</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="O27">
         <v>2.96</v>
       </c>
       <c r="P27">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="Q27">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="R27">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="S27">
         <v>1.59</v>
@@ -4743,10 +4743,10 @@
         <v>1.07</v>
       </c>
       <c r="Y27">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Z27">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AA27">
         <v>2.49</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O28">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="P28">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>2.1</v>
       </c>
       <c r="AA28">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="AB28">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -5365,7 +5365,7 @@
         <v>2.28</v>
       </c>
       <c r="O31">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="P31">
         <v>3.1</v>
@@ -5380,10 +5380,10 @@
         <v>1.57</v>
       </c>
       <c r="T31">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="U31">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="V31">
         <v>1.22</v>
@@ -5392,7 +5392,7 @@
         <v>1.03</v>
       </c>
       <c r="X31">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Y31">
         <v>1.49</v>
@@ -5401,13 +5401,13 @@
         <v>2.2</v>
       </c>
       <c r="AA31">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AB31">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AC31">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AD31">
         <v>1.08</v>
@@ -5435,7 +5435,7 @@
         <v>1.4</v>
       </c>
       <c r="AK31">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="O36">
         <v>3.5</v>
@@ -6189,7 +6189,7 @@
         <v>3.3</v>
       </c>
       <c r="R36">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S36">
         <v>1.25</v>
@@ -6204,37 +6204,37 @@
         <v>1.62</v>
       </c>
       <c r="W36">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X36">
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z36">
-        <v>5.25</v>
+        <v>4.95</v>
       </c>
       <c r="AA36">
         <v>1.53</v>
       </c>
       <c r="AB36">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="AC36">
         <v>2.2</v>
       </c>
       <c r="AD36">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AE36">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF36">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AG36">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6509,19 +6509,19 @@
         <v>3.25</v>
       </c>
       <c r="P38">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="Q38">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="R38">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S38">
         <v>1.32</v>
       </c>
       <c r="T38">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="U38">
         <v>2.7</v>
@@ -6533,34 +6533,34 @@
         <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z38">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA38">
         <v>1.85</v>
       </c>
       <c r="AB38">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AC38">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD38">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE38">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF38">
         <v>1.68</v>
       </c>
       <c r="AG38">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK38">
         <v>1.52</v>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="O39">
         <v>4.7</v>
@@ -6687,10 +6687,10 @@
         <v>4</v>
       </c>
       <c r="U39">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V39">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="W39">
         <v>1.18</v>
@@ -6702,16 +6702,16 @@
         <v>1.11</v>
       </c>
       <c r="Z39">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AA39">
         <v>1.4</v>
       </c>
       <c r="AB39">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="AC39">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AD39">
         <v>1.63</v>
@@ -6998,13 +6998,13 @@
         <v>4.6</v>
       </c>
       <c r="P41">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="Q41">
         <v>1.73</v>
       </c>
       <c r="R41">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="S41">
         <v>1.19</v>
@@ -7019,7 +7019,7 @@
         <v>1.68</v>
       </c>
       <c r="W41">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X41">
         <v>1.02</v>
@@ -7028,16 +7028,16 @@
         <v>1.08</v>
       </c>
       <c r="Z41">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="AA41">
         <v>1.4</v>
       </c>
       <c r="AB41">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AC41">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AD41">
         <v>1.71</v>
@@ -7049,7 +7049,7 @@
         <v>1.53</v>
       </c>
       <c r="AG41">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7158,10 +7158,10 @@
         <v>2.45</v>
       </c>
       <c r="O42">
-        <v>2.78</v>
+        <v>2.55</v>
       </c>
       <c r="P42">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="O43">
         <v>3.1</v>
@@ -7333,19 +7333,19 @@
         <v>2.02</v>
       </c>
       <c r="S43">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="T43">
         <v>2.44</v>
       </c>
       <c r="U43">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="V43">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W43">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X43">
         <v>1.03</v>
@@ -7357,22 +7357,22 @@
         <v>2.83</v>
       </c>
       <c r="AA43">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AB43">
         <v>1.6</v>
       </c>
       <c r="AC43">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AD43">
         <v>1.2</v>
       </c>
       <c r="AE43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF43">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AG43">
         <v>1.8</v>
@@ -7391,7 +7391,7 @@
         <v>1.29</v>
       </c>
       <c r="AK43">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O44">
         <v>3.15</v>
@@ -7505,7 +7505,7 @@
         <v>2.53</v>
       </c>
       <c r="V44">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W44">
         <v>1.1</v>
@@ -7523,13 +7523,13 @@
         <v>1.88</v>
       </c>
       <c r="AB44">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="AC44">
         <v>3.08</v>
       </c>
       <c r="AD44">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE44">
         <v>1.1</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -1124,34 +1124,34 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="X5">
         <v>0</v>
@@ -1163,25 +1163,25 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AB5">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.04</v>
+        <v>4.06</v>
       </c>
       <c r="O6">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P6">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="Q6">
         <v>4.2</v>
       </c>
       <c r="R6">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T6">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="U6">
-        <v>2.59</v>
+        <v>2.28</v>
       </c>
       <c r="V6">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z6">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AA6">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AB6">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="AC6">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="AD6">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="AE6">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AF6">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AG6">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK6">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.47</v>
+        <v>6.8</v>
       </c>
       <c r="O7">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P7">
-        <v>5.7</v>
+        <v>1.31</v>
       </c>
       <c r="Q7">
-        <v>2.02</v>
+        <v>8.5</v>
       </c>
       <c r="R7">
-        <v>2.23</v>
+        <v>2.42</v>
       </c>
       <c r="S7">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T7">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="U7">
-        <v>2.38</v>
+        <v>2.76</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z7">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="AA7">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AB7">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AC7">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="AD7">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE7">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF7">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK7">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>6.8</v>
+        <v>1.47</v>
       </c>
       <c r="O8">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P8">
-        <v>1.31</v>
+        <v>5.7</v>
       </c>
       <c r="Q8">
-        <v>8.5</v>
+        <v>2.02</v>
       </c>
       <c r="R8">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="S8">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T8">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="U8">
-        <v>2.76</v>
+        <v>2.38</v>
       </c>
       <c r="V8">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z8">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="AA8">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB8">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC8">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="AD8">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AE8">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF8">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AG8">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK8">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="O9">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P9">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q9">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="R9">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="S9">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="T9">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="U9">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="V9">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
         <v>1.06</v>
       </c>
       <c r="Y9">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="Z9">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="AA9">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AB9">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AC9">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="AD9">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AE9">
         <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="AG9">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AK9">
         <v>2.2</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O11">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.32</v>
+        <v>2.87</v>
       </c>
       <c r="O14">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P14">
         <v>2.3</v>
       </c>
       <c r="Q14">
-        <v>4.61</v>
+        <v>4.5</v>
       </c>
       <c r="R14">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="S14">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="T14">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U14">
         <v>3.34</v>
       </c>
       <c r="V14">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
         <v>1.09</v>
       </c>
       <c r="Y14">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Z14">
         <v>2.49</v>
       </c>
       <c r="AA14">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AB14">
         <v>1.5</v>
       </c>
       <c r="AC14">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="AD14">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE14">
         <v>1.02</v>
       </c>
       <c r="AF14">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AG14">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AK14">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>3.27</v>
       </c>
       <c r="O15">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="P15">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Q15">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="R15">
         <v>1.95</v>
@@ -2775,22 +2775,22 @@
         <v>2.29</v>
       </c>
       <c r="U15">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V15">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W15">
         <v>1.02</v>
       </c>
       <c r="X15">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y15">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z15">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AA15">
         <v>2.2</v>
@@ -2799,19 +2799,19 @@
         <v>1.62</v>
       </c>
       <c r="AC15">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="AD15">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE15">
         <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AG15">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="O20">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P20">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q20">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="R20">
         <v>2.63</v>
       </c>
       <c r="S20">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T20">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="U20">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="V20">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="W20">
         <v>1.25</v>
@@ -3602,31 +3602,31 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Z20">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AA20">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AB20">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="AC20">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AD20">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AE20">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AF20">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AG20">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,31 +3732,31 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="O21">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P21">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q21">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="R21">
         <v>2.63</v>
       </c>
       <c r="S21">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T21">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="U21">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="V21">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W21">
         <v>1.25</v>
@@ -3765,47 +3765,47 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z21">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AA21">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AB21">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="AC21">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AD21">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AE21">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AF21">
+        <v>1.29</v>
+      </c>
+      <c r="AG21">
+        <v>3.4</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
         <v>1.25</v>
       </c>
-      <c r="AG21">
-        <v>3.7</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.2</v>
-      </c>
       <c r="AK21">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,16 +3895,16 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O22">
         <v>2.8</v>
       </c>
       <c r="P22">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q22">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="R22">
         <v>1.91</v>
@@ -3913,10 +3913,10 @@
         <v>1.59</v>
       </c>
       <c r="T22">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="U22">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="V22">
         <v>1.25</v>
@@ -3943,13 +3943,13 @@
         <v>5.5</v>
       </c>
       <c r="AD22">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE22">
         <v>1.02</v>
       </c>
       <c r="AF22">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="AG22">
         <v>1.62</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.74</v>
+        <v>2.15</v>
       </c>
       <c r="O23">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="P23">
-        <v>1.95</v>
+        <v>4</v>
       </c>
       <c r="Q23">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="R23">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="S23">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="T23">
         <v>2.25</v>
       </c>
       <c r="U23">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="V23">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W23">
         <v>1.03</v>
       </c>
       <c r="X23">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y23">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Z23">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="AA23">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AB23">
         <v>1.36</v>
       </c>
       <c r="AC23">
-        <v>5.55</v>
+        <v>6</v>
       </c>
       <c r="AD23">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF23">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AG23">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AK23">
-        <v>1.16</v>
+        <v>1.67</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,80 +4221,80 @@
         </is>
       </c>
       <c r="N24">
-        <v>2</v>
+        <v>1.22</v>
       </c>
       <c r="O24">
-        <v>2.75</v>
+        <v>5.3</v>
       </c>
       <c r="P24">
-        <v>3.7</v>
+        <v>11</v>
       </c>
       <c r="Q24">
-        <v>2.78</v>
+        <v>1.73</v>
       </c>
       <c r="R24">
-        <v>1.77</v>
+        <v>2.44</v>
       </c>
       <c r="S24">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="T24">
+        <v>2.96</v>
+      </c>
+      <c r="U24">
+        <v>2.47</v>
+      </c>
+      <c r="V24">
+        <v>1.45</v>
+      </c>
+      <c r="W24">
+        <v>1.08</v>
+      </c>
+      <c r="X24">
+        <v>1.05</v>
+      </c>
+      <c r="Y24">
+        <v>1.2</v>
+      </c>
+      <c r="Z24">
+        <v>4.2</v>
+      </c>
+      <c r="AA24">
+        <v>1.72</v>
+      </c>
+      <c r="AB24">
+        <v>2.07</v>
+      </c>
+      <c r="AC24">
+        <v>2.85</v>
+      </c>
+      <c r="AD24">
+        <v>1.39</v>
+      </c>
+      <c r="AE24">
+        <v>1.11</v>
+      </c>
+      <c r="AF24">
         <v>2.25</v>
       </c>
-      <c r="U24">
-        <v>4.1</v>
-      </c>
-      <c r="V24">
-        <v>1.2</v>
-      </c>
-      <c r="W24">
-        <v>1.03</v>
-      </c>
-      <c r="X24">
-        <v>1.1</v>
-      </c>
-      <c r="Y24">
-        <v>1.56</v>
-      </c>
-      <c r="Z24">
-        <v>2.15</v>
-      </c>
-      <c r="AA24">
-        <v>2.84</v>
-      </c>
-      <c r="AB24">
-        <v>1.37</v>
-      </c>
-      <c r="AC24">
-        <v>5.65</v>
-      </c>
-      <c r="AD24">
-        <v>1.13</v>
-      </c>
-      <c r="AE24">
+      <c r="AG24">
+        <v>1.53</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
         <v>1.01</v>
       </c>
-      <c r="AF24">
-        <v>2.3</v>
-      </c>
-      <c r="AG24">
-        <v>1.5</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.16</v>
-      </c>
       <c r="AK24">
-        <v>1.66</v>
+        <v>3.25</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.22</v>
+        <v>3.74</v>
       </c>
       <c r="O25">
-        <v>5.25</v>
+        <v>2.75</v>
       </c>
       <c r="P25">
-        <v>9.5</v>
+        <v>1.95</v>
       </c>
       <c r="Q25">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="R25">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="S25">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="T25">
-        <v>2.96</v>
+        <v>2.18</v>
       </c>
       <c r="U25">
-        <v>2.48</v>
+        <v>4</v>
       </c>
       <c r="V25">
+        <v>1.19</v>
+      </c>
+      <c r="W25">
+        <v>1.03</v>
+      </c>
+      <c r="X25">
+        <v>1.08</v>
+      </c>
+      <c r="Y25">
+        <v>1.62</v>
+      </c>
+      <c r="Z25">
+        <v>2.21</v>
+      </c>
+      <c r="AA25">
+        <v>2.62</v>
+      </c>
+      <c r="AB25">
         <v>1.44</v>
       </c>
-      <c r="W25">
-        <v>1.08</v>
-      </c>
-      <c r="X25">
+      <c r="AC25">
+        <v>6</v>
+      </c>
+      <c r="AD25">
+        <v>1.13</v>
+      </c>
+      <c r="AE25">
         <v>1.01</v>
       </c>
-      <c r="Y25">
-        <v>1.2</v>
-      </c>
-      <c r="Z25">
-        <v>4.1</v>
-      </c>
-      <c r="AA25">
-        <v>1.75</v>
-      </c>
-      <c r="AB25">
-        <v>2</v>
-      </c>
-      <c r="AC25">
-        <v>2.7</v>
-      </c>
-      <c r="AD25">
-        <v>1.37</v>
-      </c>
-      <c r="AE25">
-        <v>1.11</v>
-      </c>
       <c r="AF25">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AG25">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="AK25">
-        <v>3.45</v>
+        <v>1.16</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4550,19 +4550,19 @@
         <v>1.8</v>
       </c>
       <c r="O26">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="P26">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q26">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="R26">
         <v>2.25</v>
       </c>
       <c r="S26">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T26">
         <v>3.1</v>
@@ -4577,25 +4577,25 @@
         <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y26">
         <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA26">
         <v>1.87</v>
       </c>
       <c r="AB26">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC26">
         <v>3.1</v>
       </c>
       <c r="AD26">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE26">
         <v>1.12</v>
@@ -4604,7 +4604,7 @@
         <v>1.7</v>
       </c>
       <c r="AG26">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK26">
         <v>1.95</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -635,40 +635,40 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O2">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="P2">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q2">
-        <v>3.45</v>
+        <v>4.08</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S2">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T2">
         <v>2.65</v>
       </c>
       <c r="U2">
-        <v>3.22</v>
+        <v>2.87</v>
       </c>
       <c r="V2">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z2">
         <v>3</v>
@@ -683,7 +683,7 @@
         <v>3.85</v>
       </c>
       <c r="AD2">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE2">
         <v>1.07</v>
@@ -692,7 +692,7 @@
         <v>1.78</v>
       </c>
       <c r="AG2">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.33</v>
       </c>
       <c r="AK2">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,28 +798,28 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="O3">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="P3">
-        <v>5.9</v>
+        <v>5.74</v>
       </c>
       <c r="Q3">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="R3">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="S3">
         <v>1.42</v>
       </c>
       <c r="T3">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="U3">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="V3">
         <v>1.37</v>
@@ -831,19 +831,19 @@
         <v>1.05</v>
       </c>
       <c r="Y3">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z3">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="AA3">
         <v>2.01</v>
       </c>
       <c r="AB3">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AC3">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="AD3">
         <v>1.24</v>
@@ -852,10 +852,10 @@
         <v>1.09</v>
       </c>
       <c r="AF3">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AG3">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,34 +961,34 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="O4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>2.95</v>
+        <v>2.58</v>
       </c>
       <c r="Q4">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="R4">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="S4">
         <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U4">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="V4">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
         <v>1.02</v>
@@ -997,13 +997,13 @@
         <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="AA4">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB4">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AC4">
         <v>2.7</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>4.5</v>
       </c>
       <c r="P7">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Q7">
         <v>8.5</v>
       </c>
       <c r="R7">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="S7">
         <v>1.34</v>
       </c>
       <c r="T7">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="U7">
-        <v>2.76</v>
+        <v>2.67</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W7">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z7">
         <v>3.5</v>
       </c>
       <c r="AA7">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AB7">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AC7">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="AD7">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE7">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AG7">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK7">
         <v>1.04</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="O8">
         <v>4</v>
       </c>
       <c r="P8">
-        <v>5.7</v>
+        <v>5.25</v>
       </c>
       <c r="Q8">
         <v>2.02</v>
@@ -1634,31 +1634,31 @@
         <v>2.92</v>
       </c>
       <c r="U8">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="V8">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W8">
         <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
         <v>1.2</v>
       </c>
       <c r="Z8">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AA8">
         <v>1.72</v>
       </c>
       <c r="AB8">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC8">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AD8">
         <v>1.41</v>
@@ -1667,10 +1667,10 @@
         <v>1.14</v>
       </c>
       <c r="AF8">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AG8">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK8">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1939,28 +1939,28 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="O10">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P10">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q10">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="R10">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S10">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T10">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U10">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="V10">
         <v>1.32</v>
@@ -1969,13 +1969,13 @@
         <v>1.06</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y10">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="Z10">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="AA10">
         <v>2.1</v>
@@ -1984,7 +1984,7 @@
         <v>1.67</v>
       </c>
       <c r="AC10">
-        <v>4.1</v>
+        <v>3.62</v>
       </c>
       <c r="AD10">
         <v>1.22</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.26</v>
+        <v>1.75</v>
       </c>
       <c r="AK10">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="O12">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="P12">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="Q12">
-        <v>4.3</v>
+        <v>4.55</v>
       </c>
       <c r="R12">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="S12">
         <v>1.22</v>
@@ -2286,13 +2286,13 @@
         <v>3.5</v>
       </c>
       <c r="U12">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="V12">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="W12">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X12">
         <v>1.02</v>
@@ -2304,7 +2304,7 @@
         <v>5.25</v>
       </c>
       <c r="AA12">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AB12">
         <v>2.5</v>
@@ -2316,13 +2316,13 @@
         <v>1.65</v>
       </c>
       <c r="AE12">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF12">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AG12">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="AK12">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2431,16 +2431,16 @@
         <v>1.84</v>
       </c>
       <c r="O13">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="P13">
-        <v>3.2</v>
+        <v>3.03</v>
       </c>
       <c r="Q13">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="R13">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="S13">
         <v>1.22</v>
@@ -2467,10 +2467,10 @@
         <v>5.5</v>
       </c>
       <c r="AA13">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB13">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AC13">
         <v>2.3</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2920,16 +2920,16 @@
         <v>1.18</v>
       </c>
       <c r="O16">
-        <v>6.25</v>
+        <v>5.45</v>
       </c>
       <c r="P16">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="Q16">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="R16">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="S16">
         <v>1.12</v>
@@ -2938,10 +2938,10 @@
         <v>4.8</v>
       </c>
       <c r="U16">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="V16">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="W16">
         <v>1.29</v>
@@ -2953,7 +2953,7 @@
         <v>1.03</v>
       </c>
       <c r="Z16">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AA16">
         <v>1.22</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK16">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,58 +3080,58 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.45</v>
+        <v>3.15</v>
       </c>
       <c r="O17">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="P17">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="Q17">
         <v>3.1</v>
       </c>
       <c r="R17">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="S17">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T17">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U17">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="V17">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="W17">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z17">
-        <v>4.9</v>
+        <v>6.55</v>
       </c>
       <c r="AA17">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AB17">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="AC17">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AD17">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="AE17">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AF17">
         <v>1.33</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AK17">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,37 +3243,37 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="O18">
-        <v>5.35</v>
+        <v>4.8</v>
       </c>
       <c r="P18">
         <v>4.65</v>
       </c>
       <c r="Q18">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R18">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="S18">
         <v>1.13</v>
       </c>
       <c r="T18">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="U18">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="V18">
         <v>1.98</v>
       </c>
       <c r="W18">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y18">
         <v>1.05</v>
@@ -3285,13 +3285,13 @@
         <v>1.23</v>
       </c>
       <c r="AB18">
-        <v>3.77</v>
+        <v>3.85</v>
       </c>
       <c r="AC18">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AD18">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AE18">
         <v>1.57</v>
@@ -3300,7 +3300,7 @@
         <v>1.36</v>
       </c>
       <c r="AG18">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.11</v>
       </c>
       <c r="AK18">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,25 +3409,25 @@
         <v>1.53</v>
       </c>
       <c r="O19">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="P19">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="Q19">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="R19">
         <v>2.9</v>
       </c>
       <c r="S19">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T19">
         <v>5</v>
       </c>
       <c r="U19">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="V19">
         <v>1.93</v>
@@ -3439,7 +3439,7 @@
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z19">
         <v>7.5</v>
@@ -3451,19 +3451,19 @@
         <v>3.5</v>
       </c>
       <c r="AC19">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AD19">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="AE19">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AF19">
         <v>1.3</v>
       </c>
       <c r="AG19">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK19">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,34 +3569,34 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="O20">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P20">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="Q20">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="R20">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="S20">
         <v>1.14</v>
       </c>
       <c r="T20">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="U20">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V20">
         <v>1.83</v>
       </c>
       <c r="W20">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3605,22 +3605,22 @@
         <v>1.03</v>
       </c>
       <c r="Z20">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="AA20">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AB20">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AC20">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AD20">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AE20">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AF20">
         <v>1.25</v>
@@ -3642,7 +3642,7 @@
         <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="O21">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P21">
         <v>2.25</v>
@@ -3747,16 +3747,16 @@
         <v>2.63</v>
       </c>
       <c r="S21">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T21">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="U21">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V21">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="W21">
         <v>1.25</v>
@@ -3765,7 +3765,7 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Z21">
         <v>8</v>
@@ -3783,7 +3783,7 @@
         <v>2.1</v>
       </c>
       <c r="AE21">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AF21">
         <v>1.29</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AK21">
         <v>1.44</v>
@@ -3895,37 +3895,37 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O22">
         <v>2.8</v>
       </c>
       <c r="P22">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q22">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="R22">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="S22">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="T22">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="U22">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="V22">
         <v>1.25</v>
       </c>
       <c r="W22">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X22">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y22">
         <v>1.5</v>
@@ -3934,25 +3934,25 @@
         <v>2.55</v>
       </c>
       <c r="AA22">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AB22">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AC22">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="AD22">
         <v>1.11</v>
       </c>
       <c r="AE22">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF22">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AG22">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK22">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.15</v>
+        <v>1.22</v>
       </c>
       <c r="O23">
-        <v>2.75</v>
+        <v>5.3</v>
       </c>
       <c r="P23">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Q23">
-        <v>2.88</v>
+        <v>1.74</v>
       </c>
       <c r="R23">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="S23">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="T23">
+        <v>2.96</v>
+      </c>
+      <c r="U23">
+        <v>2.48</v>
+      </c>
+      <c r="V23">
+        <v>1.44</v>
+      </c>
+      <c r="W23">
+        <v>1.08</v>
+      </c>
+      <c r="X23">
+        <v>1.02</v>
+      </c>
+      <c r="Y23">
+        <v>1.21</v>
+      </c>
+      <c r="Z23">
+        <v>4.2</v>
+      </c>
+      <c r="AA23">
+        <v>1.75</v>
+      </c>
+      <c r="AB23">
+        <v>2.05</v>
+      </c>
+      <c r="AC23">
+        <v>2.8</v>
+      </c>
+      <c r="AD23">
+        <v>1.42</v>
+      </c>
+      <c r="AE23">
+        <v>1.11</v>
+      </c>
+      <c r="AF23">
         <v>2.25</v>
       </c>
-      <c r="U23">
-        <v>4.1</v>
-      </c>
-      <c r="V23">
-        <v>1.2</v>
-      </c>
-      <c r="W23">
-        <v>1.03</v>
-      </c>
-      <c r="X23">
-        <v>1.1</v>
-      </c>
-      <c r="Y23">
-        <v>1.6</v>
-      </c>
-      <c r="Z23">
-        <v>2.45</v>
-      </c>
-      <c r="AA23">
-        <v>2.75</v>
-      </c>
-      <c r="AB23">
-        <v>1.36</v>
-      </c>
-      <c r="AC23">
-        <v>6</v>
-      </c>
-      <c r="AD23">
-        <v>1.13</v>
-      </c>
-      <c r="AE23">
+      <c r="AG23">
+        <v>1.54</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
         <v>1.02</v>
       </c>
-      <c r="AF23">
-        <v>2.3</v>
-      </c>
-      <c r="AG23">
-        <v>1.5</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.34</v>
-      </c>
       <c r="AK23">
-        <v>1.67</v>
+        <v>3.2</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
+        <v>1.97</v>
+      </c>
+      <c r="O24">
+        <v>2.87</v>
+      </c>
+      <c r="P24">
+        <v>3.8</v>
+      </c>
+      <c r="Q24">
+        <v>2.88</v>
+      </c>
+      <c r="R24">
+        <v>1.93</v>
+      </c>
+      <c r="S24">
+        <v>1.57</v>
+      </c>
+      <c r="T24">
+        <v>2.25</v>
+      </c>
+      <c r="U24">
+        <v>4.1</v>
+      </c>
+      <c r="V24">
         <v>1.22</v>
       </c>
-      <c r="O24">
-        <v>5.3</v>
-      </c>
-      <c r="P24">
-        <v>11</v>
-      </c>
-      <c r="Q24">
-        <v>1.73</v>
-      </c>
-      <c r="R24">
-        <v>2.44</v>
-      </c>
-      <c r="S24">
-        <v>1.32</v>
-      </c>
-      <c r="T24">
-        <v>2.96</v>
-      </c>
-      <c r="U24">
-        <v>2.47</v>
-      </c>
-      <c r="V24">
-        <v>1.45</v>
-      </c>
       <c r="W24">
+        <v>1.03</v>
+      </c>
+      <c r="X24">
+        <v>1.1</v>
+      </c>
+      <c r="Y24">
+        <v>1.53</v>
+      </c>
+      <c r="Z24">
+        <v>2.15</v>
+      </c>
+      <c r="AA24">
+        <v>2.8</v>
+      </c>
+      <c r="AB24">
+        <v>1.41</v>
+      </c>
+      <c r="AC24">
+        <v>6.5</v>
+      </c>
+      <c r="AD24">
         <v>1.08</v>
       </c>
-      <c r="X24">
-        <v>1.05</v>
-      </c>
-      <c r="Y24">
-        <v>1.2</v>
-      </c>
-      <c r="Z24">
-        <v>4.2</v>
-      </c>
-      <c r="AA24">
-        <v>1.72</v>
-      </c>
-      <c r="AB24">
-        <v>2.07</v>
-      </c>
-      <c r="AC24">
-        <v>2.85</v>
-      </c>
-      <c r="AD24">
-        <v>1.39</v>
-      </c>
       <c r="AE24">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF24">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AG24">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.74</v>
+        <v>4.05</v>
       </c>
       <c r="O25">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P25">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q25">
-        <v>5.3</v>
+        <v>5.31</v>
       </c>
       <c r="R25">
         <v>1.91</v>
@@ -4405,28 +4405,28 @@
         <v>2.18</v>
       </c>
       <c r="U25">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="V25">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="W25">
         <v>1.03</v>
       </c>
       <c r="X25">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y25">
         <v>1.62</v>
       </c>
       <c r="Z25">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="AA25">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="AB25">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AC25">
         <v>6</v>
@@ -4438,7 +4438,7 @@
         <v>1.01</v>
       </c>
       <c r="AF25">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AG25">
         <v>1.55</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AK25">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O27">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="P27">
-        <v>3.56</v>
+        <v>3.13</v>
       </c>
       <c r="Q27">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="R27">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="S27">
         <v>1.59</v>
@@ -4743,10 +4743,10 @@
         <v>1.07</v>
       </c>
       <c r="Y27">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Z27">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="AA27">
         <v>2.49</v>
@@ -4755,10 +4755,10 @@
         <v>1.42</v>
       </c>
       <c r="AC27">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="AD27">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AE27">
         <v>1.01</v>
@@ -4767,7 +4767,7 @@
         <v>2.15</v>
       </c>
       <c r="AG27">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK27">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="O30">
-        <v>2.8</v>
+        <v>5.35</v>
       </c>
       <c r="P30">
         <v>21</v>
@@ -5365,22 +5365,22 @@
         <v>2.28</v>
       </c>
       <c r="O31">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="P31">
+        <v>3.05</v>
+      </c>
+      <c r="Q31">
         <v>3.1</v>
       </c>
-      <c r="Q31">
-        <v>3</v>
-      </c>
       <c r="R31">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="S31">
         <v>1.57</v>
       </c>
       <c r="T31">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="U31">
         <v>3.75</v>
@@ -5401,22 +5401,22 @@
         <v>2.2</v>
       </c>
       <c r="AA31">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="AB31">
         <v>1.44</v>
       </c>
       <c r="AC31">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AD31">
         <v>1.08</v>
       </c>
       <c r="AE31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF31">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG31">
         <v>1.6</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AK31">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O32">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="P32">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="Q32">
         <v>2.4</v>
@@ -5543,10 +5543,10 @@
         <v>1.3</v>
       </c>
       <c r="T32">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="U32">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V32">
         <v>1.5</v>
@@ -5561,10 +5561,10 @@
         <v>1.23</v>
       </c>
       <c r="Z32">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA32">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AB32">
         <v>2</v>
@@ -5573,16 +5573,16 @@
         <v>3.1</v>
       </c>
       <c r="AD32">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE32">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF32">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG32">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5691,22 +5691,22 @@
         <v>1.4</v>
       </c>
       <c r="O33">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P33">
         <v>6.75</v>
       </c>
       <c r="Q33">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="R33">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="S33">
         <v>1.38</v>
       </c>
       <c r="T33">
-        <v>2.59</v>
+        <v>2.87</v>
       </c>
       <c r="U33">
         <v>2.75</v>
@@ -5715,7 +5715,7 @@
         <v>1.4</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X33">
         <v>1.05</v>
@@ -5727,16 +5727,16 @@
         <v>3.25</v>
       </c>
       <c r="AA33">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AB33">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AC33">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD33">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE33">
         <v>1.04</v>
@@ -5745,7 +5745,7 @@
         <v>2.2</v>
       </c>
       <c r="AG33">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.08</v>
       </c>
       <c r="AK33">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="O34">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="P34">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="Q34">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R34">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S34">
+        <v>1.36</v>
+      </c>
+      <c r="T34">
+        <v>2.57</v>
+      </c>
+      <c r="U34">
+        <v>3</v>
+      </c>
+      <c r="V34">
+        <v>1.35</v>
+      </c>
+      <c r="W34">
+        <v>1.05</v>
+      </c>
+      <c r="X34">
+        <v>1.07</v>
+      </c>
+      <c r="Y34">
+        <v>1.33</v>
+      </c>
+      <c r="Z34">
+        <v>3.25</v>
+      </c>
+      <c r="AA34">
+        <v>2.07</v>
+      </c>
+      <c r="AB34">
+        <v>1.72</v>
+      </c>
+      <c r="AC34">
+        <v>3.8</v>
+      </c>
+      <c r="AD34">
         <v>1.25</v>
       </c>
-      <c r="T34">
-        <v>3.6</v>
-      </c>
-      <c r="U34">
-        <v>2.27</v>
-      </c>
-      <c r="V34">
-        <v>1.59</v>
-      </c>
-      <c r="W34">
-        <v>1.12</v>
-      </c>
-      <c r="X34">
-        <v>1.03</v>
-      </c>
-      <c r="Y34">
-        <v>1.17</v>
-      </c>
-      <c r="Z34">
-        <v>5</v>
-      </c>
-      <c r="AA34">
-        <v>1.6</v>
-      </c>
-      <c r="AB34">
-        <v>2.43</v>
-      </c>
-      <c r="AC34">
-        <v>2.29</v>
-      </c>
-      <c r="AD34">
-        <v>1.5</v>
-      </c>
       <c r="AE34">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AF34">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="AG34">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK34">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O35">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P35">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q35">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="R35">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S35">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
-        <v>2.58</v>
+        <v>3.25</v>
       </c>
       <c r="U35">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="V35">
-        <v>1.34</v>
+        <v>1.6</v>
       </c>
       <c r="W35">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X35">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="Z35">
-        <v>3.25</v>
+        <v>4.35</v>
       </c>
       <c r="AA35">
-        <v>2.05</v>
+        <v>1.54</v>
       </c>
       <c r="AB35">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AC35">
-        <v>3.8</v>
+        <v>2.38</v>
       </c>
       <c r="AD35">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AE35">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AF35">
-        <v>1.8</v>
+        <v>1.46</v>
       </c>
       <c r="AG35">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="O36">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P36">
         <v>2.05</v>
@@ -6192,7 +6192,7 @@
         <v>2.3</v>
       </c>
       <c r="S36">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T36">
         <v>3.6</v>
@@ -6201,7 +6201,7 @@
         <v>2.2</v>
       </c>
       <c r="V36">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W36">
         <v>1.14</v>
@@ -6213,7 +6213,7 @@
         <v>1.11</v>
       </c>
       <c r="Z36">
-        <v>4.95</v>
+        <v>5.75</v>
       </c>
       <c r="AA36">
         <v>1.53</v>
@@ -6225,7 +6225,7 @@
         <v>2.2</v>
       </c>
       <c r="AD36">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="AE36">
         <v>1.2</v>
@@ -6343,25 +6343,25 @@
         <v>1.3</v>
       </c>
       <c r="O37">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="P37">
-        <v>8.25</v>
+        <v>6.4</v>
       </c>
       <c r="Q37">
         <v>1.7</v>
       </c>
       <c r="R37">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="S37">
         <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
       <c r="U37">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="V37">
         <v>1.7</v>
@@ -6373,10 +6373,10 @@
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z37">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AA37">
         <v>1.4</v>
@@ -6385,19 +6385,19 @@
         <v>2.7</v>
       </c>
       <c r="AC37">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AD37">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AE37">
         <v>1.28</v>
       </c>
       <c r="AF37">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AG37">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.08</v>
       </c>
       <c r="AK37">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,19 +6503,19 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="O38">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="P38">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="Q38">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R38">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="S38">
         <v>1.32</v>
@@ -6533,25 +6533,25 @@
         <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
         <v>1.24</v>
       </c>
       <c r="Z38">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA38">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB38">
         <v>1.82</v>
       </c>
       <c r="AC38">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD38">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE38">
         <v>1.08</v>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="O39">
         <v>4.7</v>
@@ -6675,10 +6675,10 @@
         <v>6.88</v>
       </c>
       <c r="Q39">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="R39">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="S39">
         <v>1.2</v>
@@ -6690,25 +6690,25 @@
         <v>2.05</v>
       </c>
       <c r="V39">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W39">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X39">
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z39">
         <v>5</v>
       </c>
       <c r="AA39">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB39">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AC39">
         <v>2.05</v>
@@ -6720,10 +6720,10 @@
         <v>1.25</v>
       </c>
       <c r="AF39">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK39">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6832,10 +6832,10 @@
         <v>1.97</v>
       </c>
       <c r="O40">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P40">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
@@ -6844,10 +6844,10 @@
         <v>2.25</v>
       </c>
       <c r="S40">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T40">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="U40">
         <v>2.4</v>
@@ -6856,7 +6856,7 @@
         <v>1.49</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
         <v>1.03</v>
@@ -6874,7 +6874,7 @@
         <v>2.12</v>
       </c>
       <c r="AC40">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="AD40">
         <v>1.43</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="O41">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P41">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q41">
         <v>1.73</v>
       </c>
       <c r="R41">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="S41">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T41">
         <v>4.2</v>
       </c>
       <c r="U41">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="V41">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="W41">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z41">
-        <v>5.6</v>
+        <v>6.05</v>
       </c>
       <c r="AA41">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB41">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AC41">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="AD41">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="AE41">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AF41">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG41">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK41">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="O42">
         <v>2.55</v>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="O43">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="P43">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="Q43">
         <v>2.8</v>
       </c>
       <c r="R43">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="S43">
         <v>1.46</v>
@@ -7339,13 +7339,13 @@
         <v>2.44</v>
       </c>
       <c r="U43">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="V43">
         <v>1.28</v>
       </c>
       <c r="W43">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
         <v>1.03</v>
@@ -7354,25 +7354,25 @@
         <v>1.41</v>
       </c>
       <c r="Z43">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AA43">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AB43">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC43">
-        <v>3.7</v>
+        <v>4.34</v>
       </c>
       <c r="AD43">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE43">
         <v>1.01</v>
       </c>
       <c r="AF43">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG43">
         <v>1.8</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK43">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7484,31 +7484,31 @@
         <v>2.6</v>
       </c>
       <c r="O44">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P44">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q44">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="R44">
         <v>2.25</v>
       </c>
       <c r="S44">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T44">
         <v>2.82</v>
       </c>
       <c r="U44">
-        <v>2.53</v>
+        <v>2.77</v>
       </c>
       <c r="V44">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W44">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X44">
         <v>1.01</v>
@@ -7526,10 +7526,10 @@
         <v>1.88</v>
       </c>
       <c r="AC44">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="AD44">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE44">
         <v>1.1</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -635,40 +635,40 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="O2">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="P2">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q2">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
       <c r="R2">
         <v>2.05</v>
       </c>
       <c r="S2">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
         <v>2.65</v>
       </c>
       <c r="U2">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="V2">
         <v>1.35</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="Z2">
         <v>3</v>
@@ -683,7 +683,7 @@
         <v>3.85</v>
       </c>
       <c r="AD2">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AE2">
         <v>1.07</v>
@@ -692,7 +692,7 @@
         <v>1.78</v>
       </c>
       <c r="AG2">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.33</v>
       </c>
       <c r="AK2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.48</v>
+        <v>2.29</v>
       </c>
       <c r="O3">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="P3">
-        <v>5.74</v>
+        <v>2.8</v>
       </c>
       <c r="Q3">
-        <v>2.07</v>
+        <v>2.84</v>
       </c>
       <c r="R3">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="S3">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
-        <v>2.73</v>
+        <v>3.3</v>
       </c>
       <c r="U3">
-        <v>3.12</v>
+        <v>2.65</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="W3">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z3">
-        <v>3.05</v>
+        <v>4.33</v>
       </c>
       <c r="AA3">
-        <v>2.01</v>
+        <v>1.66</v>
       </c>
       <c r="AB3">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="AC3">
-        <v>3.78</v>
+        <v>2.9</v>
       </c>
       <c r="AD3">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AE3">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AF3">
-        <v>2.1</v>
+        <v>1.56</v>
       </c>
       <c r="AG3">
-        <v>1.66</v>
+        <v>2.28</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK3">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.2</v>
+        <v>1.51</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P4">
-        <v>2.58</v>
+        <v>6.85</v>
       </c>
       <c r="Q4">
-        <v>2.8</v>
+        <v>2.16</v>
       </c>
       <c r="R4">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="S4">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="T4">
-        <v>3.3</v>
+        <v>2.59</v>
       </c>
       <c r="U4">
-        <v>2.65</v>
+        <v>3.35</v>
       </c>
       <c r="V4">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y4">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z4">
+        <v>2.83</v>
+      </c>
+      <c r="AA4">
+        <v>2.17</v>
+      </c>
+      <c r="AB4">
+        <v>1.67</v>
+      </c>
+      <c r="AC4">
         <v>4.2</v>
       </c>
-      <c r="AA4">
-        <v>1.7</v>
-      </c>
-      <c r="AB4">
-        <v>2.05</v>
-      </c>
-      <c r="AC4">
-        <v>2.7</v>
-      </c>
       <c r="AD4">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="AE4">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>1.56</v>
+        <v>2.25</v>
       </c>
       <c r="AG4">
-        <v>2.28</v>
+        <v>1.59</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK4">
-        <v>1.62</v>
+        <v>2.47</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
+        <v>1.97</v>
+      </c>
+      <c r="O23">
+        <v>2.87</v>
+      </c>
+      <c r="P23">
+        <v>3.8</v>
+      </c>
+      <c r="Q23">
+        <v>2.88</v>
+      </c>
+      <c r="R23">
+        <v>1.93</v>
+      </c>
+      <c r="S23">
+        <v>1.57</v>
+      </c>
+      <c r="T23">
+        <v>2.25</v>
+      </c>
+      <c r="U23">
+        <v>4.1</v>
+      </c>
+      <c r="V23">
         <v>1.22</v>
       </c>
-      <c r="O23">
-        <v>5.3</v>
-      </c>
-      <c r="P23">
-        <v>11</v>
-      </c>
-      <c r="Q23">
-        <v>1.74</v>
-      </c>
-      <c r="R23">
-        <v>2.55</v>
-      </c>
-      <c r="S23">
-        <v>1.32</v>
-      </c>
-      <c r="T23">
-        <v>2.96</v>
-      </c>
-      <c r="U23">
-        <v>2.48</v>
-      </c>
-      <c r="V23">
-        <v>1.44</v>
-      </c>
       <c r="W23">
+        <v>1.03</v>
+      </c>
+      <c r="X23">
+        <v>1.1</v>
+      </c>
+      <c r="Y23">
+        <v>1.53</v>
+      </c>
+      <c r="Z23">
+        <v>2.15</v>
+      </c>
+      <c r="AA23">
+        <v>2.8</v>
+      </c>
+      <c r="AB23">
+        <v>1.41</v>
+      </c>
+      <c r="AC23">
+        <v>6.5</v>
+      </c>
+      <c r="AD23">
         <v>1.08</v>
       </c>
-      <c r="X23">
-        <v>1.02</v>
-      </c>
-      <c r="Y23">
-        <v>1.21</v>
-      </c>
-      <c r="Z23">
-        <v>4.2</v>
-      </c>
-      <c r="AA23">
-        <v>1.75</v>
-      </c>
-      <c r="AB23">
-        <v>2.05</v>
-      </c>
-      <c r="AC23">
-        <v>2.8</v>
-      </c>
-      <c r="AD23">
-        <v>1.42</v>
-      </c>
       <c r="AE23">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF23">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AG23">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>3.2</v>
+        <v>1.67</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.97</v>
+        <v>1.22</v>
       </c>
       <c r="O24">
-        <v>2.87</v>
+        <v>5.3</v>
       </c>
       <c r="P24">
-        <v>3.8</v>
+        <v>11</v>
       </c>
       <c r="Q24">
-        <v>2.88</v>
+        <v>1.74</v>
       </c>
       <c r="R24">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="S24">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="T24">
+        <v>2.96</v>
+      </c>
+      <c r="U24">
+        <v>2.48</v>
+      </c>
+      <c r="V24">
+        <v>1.44</v>
+      </c>
+      <c r="W24">
+        <v>1.08</v>
+      </c>
+      <c r="X24">
+        <v>1.02</v>
+      </c>
+      <c r="Y24">
+        <v>1.21</v>
+      </c>
+      <c r="Z24">
+        <v>4.2</v>
+      </c>
+      <c r="AA24">
+        <v>1.75</v>
+      </c>
+      <c r="AB24">
+        <v>2.05</v>
+      </c>
+      <c r="AC24">
+        <v>2.8</v>
+      </c>
+      <c r="AD24">
+        <v>1.42</v>
+      </c>
+      <c r="AE24">
+        <v>1.11</v>
+      </c>
+      <c r="AF24">
         <v>2.25</v>
       </c>
-      <c r="U24">
-        <v>4.1</v>
-      </c>
-      <c r="V24">
-        <v>1.22</v>
-      </c>
-      <c r="W24">
-        <v>1.03</v>
-      </c>
-      <c r="X24">
-        <v>1.1</v>
-      </c>
-      <c r="Y24">
-        <v>1.53</v>
-      </c>
-      <c r="Z24">
-        <v>2.15</v>
-      </c>
-      <c r="AA24">
-        <v>2.8</v>
-      </c>
-      <c r="AB24">
-        <v>1.41</v>
-      </c>
-      <c r="AC24">
-        <v>6.5</v>
-      </c>
-      <c r="AD24">
-        <v>1.08</v>
-      </c>
-      <c r="AE24">
-        <v>1.03</v>
-      </c>
-      <c r="AF24">
-        <v>2.18</v>
-      </c>
       <c r="AG24">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="AK24">
-        <v>1.67</v>
+        <v>3.2</v>
       </c>
       <c r="AL24">
         <v>0</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -612,26 +612,26 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -696,12 +696,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+1", "84"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -766,139 +766,139 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>2.29</v>
+        <v>1.51</v>
       </c>
       <c r="O3">
+        <v>3.7</v>
+      </c>
+      <c r="P3">
+        <v>6.85</v>
+      </c>
+      <c r="Q3">
+        <v>2.16</v>
+      </c>
+      <c r="R3">
+        <v>2.12</v>
+      </c>
+      <c r="S3">
+        <v>1.45</v>
+      </c>
+      <c r="T3">
+        <v>2.59</v>
+      </c>
+      <c r="U3">
         <v>3.35</v>
       </c>
-      <c r="P3">
-        <v>2.8</v>
-      </c>
-      <c r="Q3">
-        <v>2.84</v>
-      </c>
-      <c r="R3">
-        <v>2.22</v>
-      </c>
-      <c r="S3">
-        <v>1.3</v>
-      </c>
-      <c r="T3">
-        <v>3.3</v>
-      </c>
-      <c r="U3">
-        <v>2.65</v>
-      </c>
       <c r="V3">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y3">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z3">
-        <v>4.33</v>
+        <v>2.83</v>
       </c>
       <c r="AA3">
-        <v>1.66</v>
+        <v>2.17</v>
       </c>
       <c r="AB3">
-        <v>2.04</v>
+        <v>1.67</v>
       </c>
       <c r="AC3">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD3">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AE3">
+        <v>1.07</v>
+      </c>
+      <c r="AF3">
+        <v>2.25</v>
+      </c>
+      <c r="AG3">
+        <v>1.59</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>["88", "89"]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>["5", "45"]</t>
+        </is>
+      </c>
+      <c r="AJ3">
+        <v>1.23</v>
+      </c>
+      <c r="AK3">
+        <v>2.47</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>12</v>
+      </c>
+      <c r="AN3">
+        <v>6</v>
+      </c>
+      <c r="AO3">
+        <v>29</v>
+      </c>
+      <c r="AP3">
+        <v>9</v>
+      </c>
+      <c r="AQ3">
+        <v>3.32</v>
+      </c>
+      <c r="AR3">
         <v>1.18</v>
       </c>
-      <c r="AF3">
-        <v>1.56</v>
-      </c>
-      <c r="AG3">
-        <v>2.28</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.27</v>
-      </c>
-      <c r="AK3">
-        <v>1.62</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>-1</v>
-      </c>
-      <c r="AN3">
-        <v>-1</v>
-      </c>
-      <c r="AO3">
-        <v>-1</v>
-      </c>
-      <c r="AP3">
-        <v>-1</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
       <c r="AS3">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -929,19 +929,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -950,118 +950,118 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>1.51</v>
+        <v>2.29</v>
       </c>
       <c r="O4">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P4">
-        <v>6.85</v>
+        <v>2.8</v>
       </c>
       <c r="Q4">
-        <v>2.16</v>
+        <v>2.84</v>
       </c>
       <c r="R4">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="S4">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>2.59</v>
+        <v>3.3</v>
       </c>
       <c r="U4">
-        <v>3.35</v>
+        <v>2.65</v>
       </c>
       <c r="V4">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="W4">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>2.83</v>
+        <v>4.33</v>
       </c>
       <c r="AA4">
-        <v>2.17</v>
+        <v>1.66</v>
       </c>
       <c r="AB4">
-        <v>1.67</v>
+        <v>2.04</v>
       </c>
       <c r="AC4">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD4">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AE4">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AF4">
-        <v>2.25</v>
+        <v>1.56</v>
       </c>
       <c r="AG4">
-        <v>1.59</v>
+        <v>2.28</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+4", "90+7"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["49"]</t>
         </is>
       </c>
       <c r="AJ4">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK4">
-        <v>2.47</v>
+        <v>1.62</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,91 +1101,91 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
         <v>1.01</v>
       </c>
       <c r="O5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q5">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="R5">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="S5">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="T5">
+        <v>17</v>
+      </c>
+      <c r="U5">
+        <v>1.12</v>
+      </c>
+      <c r="V5">
+        <v>3.55</v>
+      </c>
+      <c r="W5">
+        <v>2.2</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>1.01</v>
+      </c>
+      <c r="Z5">
+        <v>29</v>
+      </c>
+      <c r="AA5">
+        <v>1.02</v>
+      </c>
+      <c r="AB5">
+        <v>11</v>
+      </c>
+      <c r="AC5">
+        <v>1.13</v>
+      </c>
+      <c r="AD5">
         <v>8</v>
       </c>
-      <c r="U5">
-        <v>1.3</v>
-      </c>
-      <c r="V5">
-        <v>3.25</v>
-      </c>
-      <c r="W5">
-        <v>1.74</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>1.03</v>
-      </c>
-      <c r="AB5">
-        <v>8.5</v>
-      </c>
-      <c r="AC5">
-        <v>1.12</v>
-      </c>
-      <c r="AD5">
+      <c r="AE5">
         <v>4.65</v>
       </c>
-      <c r="AE5">
-        <v>2.74</v>
-      </c>
       <c r="AF5">
-        <v>3.04</v>
+        <v>2.3</v>
       </c>
       <c r="AG5">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2", "37", "45+2", "49", "50", "61", "78", "82", "90"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>33</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1267,84 +1267,84 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>4.06</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>3.75</v>
+        <v>5.55</v>
       </c>
       <c r="P6">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q6">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="R6">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="S6">
         <v>1.22</v>
       </c>
       <c r="T6">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U6">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="V6">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W6">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z6">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA6">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB6">
-        <v>2.28</v>
+        <v>2.51</v>
       </c>
       <c r="AC6">
-        <v>2.36</v>
+        <v>1.82</v>
       </c>
       <c r="AD6">
         <v>1.54</v>
       </c>
       <c r="AE6">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AF6">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AG6">
-        <v>2.25</v>
+        <v>1.79</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1353,41 +1353,41 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "25", "48", "54", "59", "90+3"]</t>
         </is>
       </c>
       <c r="AJ6">
-        <v>1.16</v>
+        <v>3.45</v>
       </c>
       <c r="AK6">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P7">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Q7">
         <v>8.5</v>
       </c>
       <c r="R7">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="S7">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T7">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="U7">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="V7">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z7">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="AA7">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AB7">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AC7">
-        <v>2.97</v>
+        <v>2.63</v>
       </c>
       <c r="AD7">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE7">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AG7">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AK7">
         <v>1.04</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="O8">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P8">
-        <v>5.25</v>
+        <v>4.85</v>
       </c>
       <c r="Q8">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="R8">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S8">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T8">
-        <v>2.92</v>
+        <v>3.12</v>
       </c>
       <c r="U8">
+        <v>2.31</v>
+      </c>
+      <c r="V8">
+        <v>1.53</v>
+      </c>
+      <c r="W8">
+        <v>1.12</v>
+      </c>
+      <c r="X8">
+        <v>1.02</v>
+      </c>
+      <c r="Y8">
+        <v>1.17</v>
+      </c>
+      <c r="Z8">
+        <v>4.3</v>
+      </c>
+      <c r="AA8">
+        <v>1.57</v>
+      </c>
+      <c r="AB8">
+        <v>2.25</v>
+      </c>
+      <c r="AC8">
         <v>2.46</v>
       </c>
-      <c r="V8">
-        <v>1.45</v>
-      </c>
-      <c r="W8">
-        <v>1.11</v>
-      </c>
-      <c r="X8">
-        <v>1.01</v>
-      </c>
-      <c r="Y8">
-        <v>1.2</v>
-      </c>
-      <c r="Z8">
-        <v>3.8</v>
-      </c>
-      <c r="AA8">
-        <v>1.72</v>
-      </c>
-      <c r="AB8">
-        <v>2.07</v>
-      </c>
-      <c r="AC8">
-        <v>2.63</v>
-      </c>
       <c r="AD8">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE8">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF8">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AG8">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK8">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1939,31 +1939,31 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="O10">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="P10">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Q10">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="R10">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S10">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T10">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U10">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="V10">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W10">
         <v>1.06</v>
@@ -1972,31 +1972,31 @@
         <v>1.06</v>
       </c>
       <c r="Y10">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z10">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="AA10">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB10">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AC10">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="AD10">
         <v>1.22</v>
       </c>
       <c r="AE10">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG10">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AK10">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.87</v>
+        <v>3.27</v>
       </c>
       <c r="O14">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="P14">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q14">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="R14">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="S14">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="T14">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="U14">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="V14">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="W14">
         <v>1.02</v>
       </c>
       <c r="X14">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="Z14">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="AA14">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB14">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC14">
-        <v>4.96</v>
+        <v>3.94</v>
       </c>
       <c r="AD14">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE14">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AG14">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK14">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.27</v>
+        <v>2.87</v>
       </c>
       <c r="O15">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="P15">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q15">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="R15">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="S15">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="T15">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="U15">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="V15">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="W15">
         <v>1.02</v>
       </c>
       <c r="X15">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y15">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="Z15">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="AA15">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB15">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AC15">
-        <v>3.94</v>
+        <v>4.96</v>
       </c>
       <c r="AD15">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE15">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AG15">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK15">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="O20">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P20">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="Q20">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="R20">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="S20">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T20">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="U20">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="V20">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="W20">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z20">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="AA20">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AB20">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AC20">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AD20">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AE20">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AF20">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AG20">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AK20">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
+        <v>2.05</v>
+      </c>
+      <c r="O21">
+        <v>3.9</v>
+      </c>
+      <c r="P21">
+        <v>2.34</v>
+      </c>
+      <c r="Q21">
         <v>2.55</v>
       </c>
-      <c r="O21">
-        <v>3.8</v>
-      </c>
-      <c r="P21">
-        <v>2.25</v>
-      </c>
-      <c r="Q21">
-        <v>2.9</v>
-      </c>
       <c r="R21">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="S21">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T21">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="U21">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="V21">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="W21">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z21">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="AA21">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AB21">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AC21">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AD21">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AE21">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AF21">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AG21">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.97</v>
+        <v>1.22</v>
       </c>
       <c r="O23">
-        <v>2.87</v>
+        <v>5.3</v>
       </c>
       <c r="P23">
-        <v>3.8</v>
+        <v>11</v>
       </c>
       <c r="Q23">
-        <v>2.88</v>
+        <v>1.74</v>
       </c>
       <c r="R23">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="S23">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="T23">
+        <v>2.96</v>
+      </c>
+      <c r="U23">
+        <v>2.48</v>
+      </c>
+      <c r="V23">
+        <v>1.44</v>
+      </c>
+      <c r="W23">
+        <v>1.08</v>
+      </c>
+      <c r="X23">
+        <v>1.02</v>
+      </c>
+      <c r="Y23">
+        <v>1.21</v>
+      </c>
+      <c r="Z23">
+        <v>4.2</v>
+      </c>
+      <c r="AA23">
+        <v>1.75</v>
+      </c>
+      <c r="AB23">
+        <v>2.05</v>
+      </c>
+      <c r="AC23">
+        <v>2.8</v>
+      </c>
+      <c r="AD23">
+        <v>1.42</v>
+      </c>
+      <c r="AE23">
+        <v>1.11</v>
+      </c>
+      <c r="AF23">
         <v>2.25</v>
       </c>
-      <c r="U23">
-        <v>4.1</v>
-      </c>
-      <c r="V23">
-        <v>1.22</v>
-      </c>
-      <c r="W23">
-        <v>1.03</v>
-      </c>
-      <c r="X23">
-        <v>1.1</v>
-      </c>
-      <c r="Y23">
-        <v>1.53</v>
-      </c>
-      <c r="Z23">
-        <v>2.15</v>
-      </c>
-      <c r="AA23">
-        <v>2.8</v>
-      </c>
-      <c r="AB23">
-        <v>1.41</v>
-      </c>
-      <c r="AC23">
-        <v>6.5</v>
-      </c>
-      <c r="AD23">
-        <v>1.08</v>
-      </c>
-      <c r="AE23">
-        <v>1.03</v>
-      </c>
-      <c r="AF23">
-        <v>2.18</v>
-      </c>
       <c r="AG23">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="AK23">
-        <v>1.67</v>
+        <v>3.2</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.22</v>
+        <v>4.05</v>
       </c>
       <c r="O24">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="P24">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Q24">
-        <v>1.74</v>
+        <v>5.31</v>
       </c>
       <c r="R24">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="S24">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="T24">
-        <v>2.96</v>
+        <v>2.18</v>
       </c>
       <c r="U24">
-        <v>2.48</v>
+        <v>4.1</v>
       </c>
       <c r="V24">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y24">
-        <v>1.21</v>
+        <v>1.62</v>
       </c>
       <c r="Z24">
-        <v>4.2</v>
+        <v>2.38</v>
       </c>
       <c r="AA24">
-        <v>1.75</v>
+        <v>2.85</v>
       </c>
       <c r="AB24">
-        <v>2.05</v>
+        <v>1.42</v>
       </c>
       <c r="AC24">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="AD24">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="AE24">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AF24">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AG24">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.02</v>
+        <v>1.67</v>
       </c>
       <c r="AK24">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,31 +4384,31 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.05</v>
+        <v>1.97</v>
       </c>
       <c r="O25">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P25">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="Q25">
-        <v>5.31</v>
+        <v>2.88</v>
       </c>
       <c r="R25">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="S25">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="T25">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="U25">
         <v>4.1</v>
       </c>
       <c r="V25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W25">
         <v>1.03</v>
@@ -4417,31 +4417,31 @@
         <v>1.1</v>
       </c>
       <c r="Y25">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="Z25">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AA25">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AB25">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AC25">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AD25">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AE25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF25">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="AG25">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
+        <v>1.33</v>
+      </c>
+      <c r="AK25">
         <v>1.67</v>
-      </c>
-      <c r="AK25">
-        <v>1.2</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4716,25 +4716,25 @@
         <v>2.9</v>
       </c>
       <c r="P27">
-        <v>3.13</v>
+        <v>3.6</v>
       </c>
       <c r="Q27">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="R27">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="S27">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="T27">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="U27">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="V27">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W27">
         <v>1</v>
@@ -4746,19 +4746,19 @@
         <v>1.53</v>
       </c>
       <c r="Z27">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="AA27">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="AB27">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AC27">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AD27">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE27">
         <v>1.01</v>
@@ -4767,23 +4767,23 @@
         <v>2.15</v>
       </c>
       <c r="AG27">
+        <v>1.65</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>1.22</v>
+      </c>
+      <c r="AK27">
         <v>1.61</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.36</v>
-      </c>
-      <c r="AK27">
-        <v>1.54</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O28">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="P28">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>2.1</v>
       </c>
       <c r="AA28">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="AB28">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.64</v>
+        <v>1.17</v>
       </c>
       <c r="O30">
-        <v>5.35</v>
+        <v>3.2</v>
       </c>
       <c r="P30">
         <v>21</v>
@@ -5368,22 +5368,22 @@
         <v>2.95</v>
       </c>
       <c r="P31">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="Q31">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R31">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="S31">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="T31">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="U31">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="V31">
         <v>1.22</v>
@@ -5395,25 +5395,25 @@
         <v>1.13</v>
       </c>
       <c r="Y31">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="Z31">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AA31">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="AB31">
         <v>1.44</v>
       </c>
       <c r="AC31">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AD31">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF31">
         <v>2.25</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK31">
         <v>1.53</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O34">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P34">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q34">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="R34">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T34">
-        <v>2.57</v>
+        <v>3.25</v>
       </c>
       <c r="U34">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="V34">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="W34">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X34">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="Z34">
-        <v>3.25</v>
+        <v>4.35</v>
       </c>
       <c r="AA34">
-        <v>2.07</v>
+        <v>1.54</v>
       </c>
       <c r="AB34">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="AC34">
-        <v>3.8</v>
+        <v>2.38</v>
       </c>
       <c r="AD34">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AE34">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AF34">
-        <v>1.78</v>
+        <v>1.46</v>
       </c>
       <c r="AG34">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O35">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="Q35">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="R35">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S35">
+        <v>1.36</v>
+      </c>
+      <c r="T35">
+        <v>2.57</v>
+      </c>
+      <c r="U35">
+        <v>3</v>
+      </c>
+      <c r="V35">
+        <v>1.35</v>
+      </c>
+      <c r="W35">
+        <v>1.05</v>
+      </c>
+      <c r="X35">
+        <v>1.07</v>
+      </c>
+      <c r="Y35">
+        <v>1.33</v>
+      </c>
+      <c r="Z35">
+        <v>3.25</v>
+      </c>
+      <c r="AA35">
+        <v>2.07</v>
+      </c>
+      <c r="AB35">
+        <v>1.72</v>
+      </c>
+      <c r="AC35">
+        <v>3.8</v>
+      </c>
+      <c r="AD35">
         <v>1.25</v>
       </c>
-      <c r="T35">
-        <v>3.25</v>
-      </c>
-      <c r="U35">
-        <v>2.25</v>
-      </c>
-      <c r="V35">
-        <v>1.6</v>
-      </c>
-      <c r="W35">
-        <v>1.12</v>
-      </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
-        <v>1.16</v>
-      </c>
-      <c r="Z35">
-        <v>4.35</v>
-      </c>
-      <c r="AA35">
-        <v>1.54</v>
-      </c>
-      <c r="AB35">
-        <v>2.3</v>
-      </c>
-      <c r="AC35">
-        <v>2.38</v>
-      </c>
-      <c r="AD35">
-        <v>1.53</v>
-      </c>
       <c r="AE35">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AF35">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="AG35">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK35">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -7151,17 +7151,17 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N42">
         <v>2.44</v>
       </c>
       <c r="O42">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="P42">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="Q42">
         <v>0</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -1430,23 +1430,23 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "69"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,26 +1590,26 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "39", "44", "71"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61"]</t>
         </is>
       </c>
       <c r="AJ8">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1772,20 +1772,20 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="O9">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
-        <v>5.5</v>
+        <v>6.56</v>
       </c>
       <c r="Q9">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="R9">
         <v>1.91</v>
@@ -1794,7 +1794,7 @@
         <v>1.57</v>
       </c>
       <c r="T9">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="U9">
         <v>3.68</v>
@@ -1809,13 +1809,13 @@
         <v>1.06</v>
       </c>
       <c r="Y9">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="Z9">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
       <c r="AA9">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AB9">
         <v>1.42</v>
@@ -1824,16 +1824,16 @@
         <v>5.4</v>
       </c>
       <c r="AD9">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AE9">
         <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="AG9">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AK9">
         <v>2.2</v>
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2079,16 +2079,16 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -2098,111 +2098,111 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
+        <v>2.75</v>
+      </c>
+      <c r="O11">
+        <v>3.45</v>
+      </c>
+      <c r="P11">
         <v>2.6</v>
       </c>
-      <c r="O11">
-        <v>3.4</v>
-      </c>
-      <c r="P11">
-        <v>2.61</v>
-      </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA11">
         <v>1.8</v>
       </c>
       <c r="AB11">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29"]</t>
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2242,42 +2242,42 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O12">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="P12">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="Q12">
-        <v>4.55</v>
+        <v>4</v>
       </c>
       <c r="R12">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
         <v>1.22</v>
@@ -2286,28 +2286,28 @@
         <v>3.5</v>
       </c>
       <c r="U12">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V12">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W12">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z12">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="AA12">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AB12">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AC12">
         <v>2.11</v>
@@ -2316,26 +2316,26 @@
         <v>1.65</v>
       </c>
       <c r="AE12">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF12">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AG12">
         <v>2.15</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "49", "77"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33"]</t>
         </is>
       </c>
       <c r="AJ12">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AK12">
         <v>1.13</v>
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,57 +2405,57 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="O13">
-        <v>3.48</v>
+        <v>3.9</v>
       </c>
       <c r="P13">
-        <v>3.03</v>
+        <v>3.5</v>
       </c>
       <c r="Q13">
+        <v>2.45</v>
+      </c>
+      <c r="R13">
         <v>2.3</v>
       </c>
-      <c r="R13">
-        <v>2.4</v>
-      </c>
       <c r="S13">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T13">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="U13">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="V13">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="W13">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X13">
         <v>1.01</v>
@@ -2464,71 +2464,71 @@
         <v>1.14</v>
       </c>
       <c r="Z13">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA13">
+        <v>1.65</v>
+      </c>
+      <c r="AB13">
+        <v>2.2</v>
+      </c>
+      <c r="AC13">
+        <v>2.56</v>
+      </c>
+      <c r="AD13">
         <v>1.48</v>
       </c>
-      <c r="AB13">
-        <v>2.33</v>
-      </c>
-      <c r="AC13">
-        <v>2.3</v>
-      </c>
-      <c r="AD13">
-        <v>1.6</v>
-      </c>
       <c r="AE13">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AF13">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG13">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "32", "68"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87"]</t>
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK13">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.27</v>
+        <v>2.65</v>
       </c>
       <c r="O14">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="P14">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="Q14">
-        <v>3.7</v>
+        <v>3.86</v>
       </c>
       <c r="R14">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="S14">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="T14">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="U14">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="V14">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="W14">
         <v>1.02</v>
       </c>
       <c r="X14">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y14">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="Z14">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="AA14">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB14">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AC14">
-        <v>3.94</v>
+        <v>5.5</v>
       </c>
       <c r="AD14">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AE14">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF14">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AG14">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AK14">
         <v>1.36</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.87</v>
+        <v>2.65</v>
       </c>
       <c r="O15">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P15">
-        <v>2.3</v>
+        <v>2.61</v>
       </c>
       <c r="Q15">
-        <v>4.5</v>
+        <v>3.24</v>
       </c>
       <c r="R15">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="S15">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T15">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="U15">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="V15">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="W15">
         <v>1.02</v>
       </c>
       <c r="X15">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y15">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="Z15">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="AA15">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AB15">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AC15">
-        <v>4.96</v>
+        <v>3.94</v>
       </c>
       <c r="AD15">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE15">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG15">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AK15">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="O16">
-        <v>5.45</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>6.9</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="R16">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="S16">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="T16">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="U16">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="V16">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="W16">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z16">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA16">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AB16">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AC16">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AD16">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AE16">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AF16">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AG16">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AK16">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3057,39 +3057,39 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O17">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="P17">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="Q17">
-        <v>3.1</v>
+        <v>3.71</v>
       </c>
       <c r="R17">
         <v>2.51</v>
@@ -3101,10 +3101,10 @@
         <v>4.2</v>
       </c>
       <c r="U17">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V17">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="W17">
         <v>1.2</v>
@@ -3116,22 +3116,22 @@
         <v>1.05</v>
       </c>
       <c r="Z17">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="AA17">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AB17">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="AC17">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AD17">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AE17">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AF17">
         <v>1.33</v>
@@ -3141,46 +3141,46 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["89"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "39"]</t>
         </is>
       </c>
       <c r="AJ17">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AK17">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3220,130 +3220,130 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
         <v>1.42</v>
       </c>
       <c r="O18">
-        <v>4.8</v>
+        <v>5.35</v>
       </c>
       <c r="P18">
         <v>4.65</v>
       </c>
       <c r="Q18">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="R18">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="S18">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="T18">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="U18">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="V18">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="W18">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X18">
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Z18">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AA18">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AB18">
-        <v>3.85</v>
+        <v>4.57</v>
       </c>
       <c r="AC18">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AD18">
-        <v>2.25</v>
+        <v>2.58</v>
       </c>
       <c r="AE18">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AF18">
         <v>1.36</v>
       </c>
       <c r="AG18">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "35", "58", "82"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "33"]</t>
         </is>
       </c>
       <c r="AJ18">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK18">
-        <v>2.72</v>
+        <v>2.97</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3383,13 +3383,13 @@
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3402,111 +3402,111 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O19">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="P19">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="Q19">
         <v>1.95</v>
       </c>
       <c r="R19">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="S19">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="U19">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="V19">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="W19">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z19">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA19">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AB19">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="AC19">
-        <v>1.64</v>
+        <v>2.03</v>
       </c>
       <c r="AD19">
-        <v>2.22</v>
+        <v>1.77</v>
       </c>
       <c r="AE19">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AF19">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AG19">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
+          <t>["28", "42", "43"]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ19">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK19">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3549,13 +3549,13 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -3565,68 +3565,68 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="O20">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="P20">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q20">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R20">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="S20">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T20">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="U20">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="V20">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="W20">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA20">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AB20">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="AC20">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AD20">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AE20">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AF20">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AG20">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3635,41 +3635,41 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33"]</t>
         </is>
       </c>
       <c r="AJ20">
         <v>1.57</v>
       </c>
       <c r="AK20">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3709,130 +3709,130 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="O21">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="Q21">
         <v>2.55</v>
       </c>
       <c r="R21">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S21">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T21">
-        <v>4.7</v>
+        <v>4.15</v>
       </c>
       <c r="U21">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="V21">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="W21">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z21">
-        <v>7.7</v>
+        <v>6.25</v>
       </c>
       <c r="AA21">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AB21">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="AC21">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AD21">
-        <v>2.04</v>
+        <v>1.79</v>
       </c>
       <c r="AE21">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AF21">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AG21">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "46"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44", "84"]</t>
         </is>
       </c>
       <c r="AJ21">
         <v>1.2</v>
       </c>
       <c r="AK21">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O22">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P22">
         <v>2.78</v>
       </c>
       <c r="Q22">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="R22">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="S22">
         <v>1.5</v>
@@ -3916,37 +3916,37 @@
         <v>2.35</v>
       </c>
       <c r="U22">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="V22">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W22">
         <v>1.02</v>
       </c>
       <c r="X22">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y22">
+        <v>1.47</v>
+      </c>
+      <c r="Z22">
+        <v>2.63</v>
+      </c>
+      <c r="AA22">
+        <v>2.49</v>
+      </c>
+      <c r="AB22">
         <v>1.5</v>
       </c>
-      <c r="Z22">
-        <v>2.55</v>
-      </c>
-      <c r="AA22">
-        <v>2.73</v>
-      </c>
-      <c r="AB22">
-        <v>1.42</v>
-      </c>
       <c r="AC22">
-        <v>4.9</v>
+        <v>4.45</v>
       </c>
       <c r="AD22">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AE22">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF22">
         <v>2.1</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK22">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
+        <v>1.97</v>
+      </c>
+      <c r="O23">
+        <v>2.7</v>
+      </c>
+      <c r="P23">
+        <v>3.4</v>
+      </c>
+      <c r="Q23">
+        <v>2.88</v>
+      </c>
+      <c r="R23">
+        <v>1.85</v>
+      </c>
+      <c r="S23">
+        <v>1.57</v>
+      </c>
+      <c r="T23">
+        <v>2.25</v>
+      </c>
+      <c r="U23">
+        <v>3.75</v>
+      </c>
+      <c r="V23">
         <v>1.22</v>
       </c>
-      <c r="O23">
-        <v>5.3</v>
-      </c>
-      <c r="P23">
-        <v>11</v>
-      </c>
-      <c r="Q23">
-        <v>1.74</v>
-      </c>
-      <c r="R23">
-        <v>2.55</v>
-      </c>
-      <c r="S23">
-        <v>1.32</v>
-      </c>
-      <c r="T23">
-        <v>2.96</v>
-      </c>
-      <c r="U23">
-        <v>2.48</v>
-      </c>
-      <c r="V23">
-        <v>1.44</v>
-      </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y23">
-        <v>1.21</v>
+        <v>1.62</v>
       </c>
       <c r="Z23">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="AA23">
-        <v>1.75</v>
+        <v>2.89</v>
       </c>
       <c r="AB23">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="AC23">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="AD23">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="AE23">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF23">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG23">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="AK23">
-        <v>3.2</v>
+        <v>1.57</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,65 +4221,65 @@
         </is>
       </c>
       <c r="N24">
-        <v>4.05</v>
+        <v>1.32</v>
       </c>
       <c r="O24">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="P24">
-        <v>2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q24">
-        <v>5.31</v>
+        <v>1.74</v>
       </c>
       <c r="R24">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="S24">
-        <v>1.6</v>
+        <v>1.34</v>
       </c>
       <c r="T24">
-        <v>2.18</v>
+        <v>2.88</v>
       </c>
       <c r="U24">
-        <v>4.1</v>
+        <v>2.59</v>
       </c>
       <c r="V24">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="W24">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
+        <v>1.23</v>
+      </c>
+      <c r="Z24">
+        <v>3.8</v>
+      </c>
+      <c r="AA24">
+        <v>1.85</v>
+      </c>
+      <c r="AB24">
+        <v>1.94</v>
+      </c>
+      <c r="AC24">
+        <v>3</v>
+      </c>
+      <c r="AD24">
+        <v>1.38</v>
+      </c>
+      <c r="AE24">
+        <v>1.09</v>
+      </c>
+      <c r="AF24">
+        <v>2.1</v>
+      </c>
+      <c r="AG24">
         <v>1.62</v>
       </c>
-      <c r="Z24">
-        <v>2.38</v>
-      </c>
-      <c r="AA24">
-        <v>2.85</v>
-      </c>
-      <c r="AB24">
-        <v>1.42</v>
-      </c>
-      <c r="AC24">
-        <v>6</v>
-      </c>
-      <c r="AD24">
-        <v>1.13</v>
-      </c>
-      <c r="AE24">
-        <v>1.01</v>
-      </c>
-      <c r="AF24">
-        <v>2.32</v>
-      </c>
-      <c r="AG24">
-        <v>1.55</v>
-      </c>
       <c r="AH24" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.67</v>
+        <v>1.12</v>
       </c>
       <c r="AK24">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,31 +4384,31 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.97</v>
+        <v>4.05</v>
       </c>
       <c r="O25">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="P25">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="Q25">
-        <v>2.88</v>
+        <v>5.31</v>
       </c>
       <c r="R25">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="S25">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="T25">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="U25">
         <v>4.1</v>
       </c>
       <c r="V25">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W25">
         <v>1.03</v>
@@ -4417,31 +4417,31 @@
         <v>1.1</v>
       </c>
       <c r="Y25">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="Z25">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AA25">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AB25">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AC25">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AD25">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF25">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="AG25">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AK25">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="O26">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
-        <v>4.33</v>
+        <v>3.62</v>
       </c>
       <c r="Q26">
         <v>2.25</v>
@@ -4562,49 +4562,49 @@
         <v>2.25</v>
       </c>
       <c r="S26">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U26">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="V26">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W26">
         <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z26">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA26">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB26">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC26">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="AD26">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE26">
         <v>1.12</v>
       </c>
       <c r="AF26">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG26">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G29">
@@ -5032,65 +5032,65 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29">
-        <v>2.25</v>
+        <v>1.17</v>
       </c>
       <c r="O29">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="P29">
-        <v>3.42</v>
+        <v>21</v>
       </c>
       <c r="Q29">
-        <v>3.14</v>
+        <v>2.31</v>
       </c>
       <c r="R29">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="S29">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="T29">
-        <v>2.08</v>
+        <v>2.37</v>
       </c>
       <c r="U29">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="V29">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="W29">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X29">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y29">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="Z29">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AA29">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="AB29">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC29">
         <v>5.5</v>
       </c>
       <c r="AD29">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AE29">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="AG29">
         <v>1.55</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AK29">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G30">
@@ -5195,65 +5195,65 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30">
-        <v>1.17</v>
+        <v>2.25</v>
       </c>
       <c r="O30">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="P30">
-        <v>21</v>
+        <v>3.42</v>
       </c>
       <c r="Q30">
-        <v>2.31</v>
+        <v>3.14</v>
       </c>
       <c r="R30">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="S30">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="T30">
-        <v>2.37</v>
+        <v>2.08</v>
       </c>
       <c r="U30">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="V30">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="W30">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X30">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y30">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Z30">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AA30">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="AB30">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC30">
         <v>5.5</v>
       </c>
       <c r="AD30">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AE30">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="AG30">
         <v>1.55</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AK30">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5528,10 +5528,10 @@
         <v>1.91</v>
       </c>
       <c r="O32">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="P32">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="Q32">
         <v>2.4</v>
@@ -5540,43 +5540,43 @@
         <v>2.25</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="U32">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="V32">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W32">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z32">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA32">
         <v>1.8</v>
       </c>
       <c r="AB32">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AC32">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="AD32">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE32">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF32">
         <v>1.6</v>
@@ -5598,7 +5598,7 @@
         <v>1.29</v>
       </c>
       <c r="AK32">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="O33">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P33">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="Q33">
         <v>2.05</v>
@@ -5706,46 +5706,46 @@
         <v>1.38</v>
       </c>
       <c r="T33">
-        <v>2.87</v>
+        <v>2.59</v>
       </c>
       <c r="U33">
         <v>2.75</v>
       </c>
       <c r="V33">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W33">
         <v>1.05</v>
       </c>
       <c r="X33">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y33">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z33">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA33">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AB33">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AC33">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AD33">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE33">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF33">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AG33">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O34">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
+        <v>2.84</v>
+      </c>
+      <c r="Q34">
         <v>2.9</v>
       </c>
-      <c r="Q34">
-        <v>2.7</v>
-      </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S34">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T34">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="U34">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="V34">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="Z34">
-        <v>4.35</v>
+        <v>3.4</v>
       </c>
       <c r="AA34">
-        <v>1.54</v>
+        <v>2</v>
       </c>
       <c r="AB34">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AC34">
-        <v>2.38</v>
+        <v>3.3</v>
       </c>
       <c r="AD34">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AE34">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF34">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="AG34">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK34">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="O35">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="P35">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="Q35">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="R35">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="S35">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
-        <v>2.57</v>
+        <v>3.6</v>
       </c>
       <c r="U35">
-        <v>3</v>
+        <v>2.27</v>
       </c>
       <c r="V35">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="W35">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X35">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="Z35">
-        <v>3.25</v>
+        <v>4.45</v>
       </c>
       <c r="AA35">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="AB35">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="AC35">
-        <v>3.8</v>
+        <v>2.21</v>
       </c>
       <c r="AD35">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AE35">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AF35">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="AG35">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="O36">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P36">
         <v>2.05</v>
       </c>
       <c r="Q36">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="R36">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S36">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T36">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U36">
         <v>2.2</v>
       </c>
       <c r="V36">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="W36">
         <v>1.14</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z36">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA36">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB36">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="AC36">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AD36">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AE36">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AF36">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AG36">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="O37">
-        <v>5.75</v>
+        <v>6.35</v>
       </c>
       <c r="P37">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="Q37">
+        <v>1.62</v>
+      </c>
+      <c r="R37">
+        <v>2.9</v>
+      </c>
+      <c r="S37">
+        <v>1.18</v>
+      </c>
+      <c r="T37">
+        <v>4.33</v>
+      </c>
+      <c r="U37">
+        <v>1.93</v>
+      </c>
+      <c r="V37">
+        <v>1.81</v>
+      </c>
+      <c r="W37">
+        <v>1.21</v>
+      </c>
+      <c r="X37">
+        <v>1.01</v>
+      </c>
+      <c r="Y37">
+        <v>1.11</v>
+      </c>
+      <c r="Z37">
+        <v>7.5</v>
+      </c>
+      <c r="AA37">
+        <v>1.36</v>
+      </c>
+      <c r="AB37">
+        <v>3</v>
+      </c>
+      <c r="AC37">
+        <v>2</v>
+      </c>
+      <c r="AD37">
+        <v>1.8</v>
+      </c>
+      <c r="AE37">
+        <v>1.33</v>
+      </c>
+      <c r="AF37">
         <v>1.7</v>
       </c>
-      <c r="R37">
-        <v>2.75</v>
-      </c>
-      <c r="S37">
-        <v>1.22</v>
-      </c>
-      <c r="T37">
-        <v>4.1</v>
-      </c>
-      <c r="U37">
-        <v>2</v>
-      </c>
-      <c r="V37">
-        <v>1.7</v>
-      </c>
-      <c r="W37">
-        <v>1.18</v>
-      </c>
-      <c r="X37">
-        <v>1.02</v>
-      </c>
-      <c r="Y37">
-        <v>1.08</v>
-      </c>
-      <c r="Z37">
-        <v>6.5</v>
-      </c>
-      <c r="AA37">
-        <v>1.4</v>
-      </c>
-      <c r="AB37">
-        <v>2.7</v>
-      </c>
-      <c r="AC37">
-        <v>2.1</v>
-      </c>
-      <c r="AD37">
-        <v>1.77</v>
-      </c>
-      <c r="AE37">
-        <v>1.28</v>
-      </c>
-      <c r="AF37">
-        <v>1.74</v>
-      </c>
       <c r="AG37">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AK37">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O38">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="P38">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="Q38">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="R38">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="S38">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T38">
-        <v>2.77</v>
+        <v>2.53</v>
       </c>
       <c r="U38">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V38">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y38">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="AA38">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AB38">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AC38">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="AD38">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE38">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF38">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AG38">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="O39">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="P39">
-        <v>6.88</v>
+        <v>6.25</v>
       </c>
       <c r="Q39">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="R39">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="S39">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="U39">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="V39">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W39">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z39">
-        <v>5</v>
+        <v>4.45</v>
       </c>
       <c r="AA39">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AB39">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AC39">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AD39">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AE39">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF39">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG39">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AK39">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="O41">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P41">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q41">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R41">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="S41">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T41">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="U41">
-        <v>1.99</v>
+        <v>1.65</v>
       </c>
       <c r="V41">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="W41">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X41">
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z41">
-        <v>6.05</v>
+        <v>7.1</v>
       </c>
       <c r="AA41">
+        <v>1.28</v>
+      </c>
+      <c r="AB41">
+        <v>3.2</v>
+      </c>
+      <c r="AC41">
+        <v>1.72</v>
+      </c>
+      <c r="AD41">
+        <v>1.93</v>
+      </c>
+      <c r="AE41">
         <v>1.44</v>
       </c>
-      <c r="AB41">
-        <v>2.83</v>
-      </c>
-      <c r="AC41">
-        <v>1.92</v>
-      </c>
-      <c r="AD41">
-        <v>1.84</v>
-      </c>
-      <c r="AE41">
-        <v>1.31</v>
-      </c>
       <c r="AF41">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG41">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK41">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AL41">
         <v>0</v>

--- a/jogos_2026-08-26.xlsx
+++ b/jogos_2026-08-26.xlsx
@@ -2559,19 +2559,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -2583,72 +2583,72 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
         <v>2.65</v>
       </c>
       <c r="O14">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="P14">
-        <v>2.26</v>
+        <v>2.61</v>
       </c>
       <c r="Q14">
-        <v>3.86</v>
+        <v>3.24</v>
       </c>
       <c r="R14">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="S14">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T14">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="U14">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="V14">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="W14">
         <v>1.02</v>
       </c>
       <c r="X14">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y14">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="Z14">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AA14">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AB14">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AC14">
-        <v>5.5</v>
+        <v>3.94</v>
       </c>
       <c r="AD14">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AE14">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AG14">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2657,41 +2657,41 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51", "86", "90+5"]</t>
         </is>
       </c>
       <c r="AJ14">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AK14">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2722,139 +2722,139 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
         <v>2.65</v>
       </c>
       <c r="O15">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="P15">
-        <v>2.61</v>
+        <v>2.26</v>
       </c>
       <c r="Q15">
-        <v>3.24</v>
+        <v>3.86</v>
       </c>
       <c r="R15">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="S15">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T15">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="U15">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="V15">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="W15">
         <v>1.02</v>
       </c>
       <c r="X15">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y15">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="Z15">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AA15">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AB15">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AC15">
-        <v>3.94</v>
+        <v>5.5</v>
       </c>
       <c r="AD15">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AE15">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF15">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AG15">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65", "81"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "43", "48"]</t>
         </is>
       </c>
       <c r="AJ15">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AK15">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -2906,14 +2906,14 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2978,12 +2978,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["75", "90+1", "90+7"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67"]</t>
         </is>
       </c>
       <c r="AJ16">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -3884,14 +3884,14 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["69"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
@@ -3974,28 +3974,28 @@
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
@@ -4137,28 +4137,28 @@
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4198,26 +4198,26 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "33", "52", "66", "90+1"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["46", "70"]</t>
         </is>
       </c>
       <c r="AJ24">
@@ -4300,28 +4300,28 @@
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4361,26 +4361,26 @@
         </is>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "39"]</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "76"]</t>
         </is>
       </c>
       <c r="AJ25">
@@ -4463,28 +4463,28 @@
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -4536,14 +4536,14 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["83"]</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["71"]</t>
         </is>
       </c>
       <c r="AJ26">
@@ -4626,28 +4626,28 @@
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4687,10 +4687,10 @@
         </is>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -4699,39 +4699,39 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="O27">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="P27">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="Q27">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="R27">
         <v>1.94</v>
       </c>
       <c r="S27">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="T27">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="U27">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="V27">
         <v>1.21</v>
@@ -4746,37 +4746,37 @@
         <v>1.53</v>
       </c>
       <c r="Z27">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="AA27">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="AB27">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AC27">
         <v>4.95</v>
       </c>
       <c r="AD27">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE27">
         <v>1.01</v>
       </c>
       <c r="AF27">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG27">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65"]</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["82", "86"]</t>
         </is>
       </c>
       <c r="AJ27">
@@ -4789,28 +4789,28 @@
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -4862,14 +4862,14 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
@@ -4934,14 +4934,14 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
+          <t>["59", "67", "89"]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ28">
         <v>0</v>
       </c>
@@ -4952,28 +4952,28 @@
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G29">
@@ -5032,65 +5032,65 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29">
-        <v>1.17</v>
+        <v>2.25</v>
       </c>
       <c r="O29">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="P29">
-        <v>21</v>
+        <v>3.42</v>
       </c>
       <c r="Q29">
-        <v>2.31</v>
+        <v>3.14</v>
       </c>
       <c r="R29">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="S29">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="T29">
-        <v>2.37</v>
+        <v>2.08</v>
       </c>
       <c r="U29">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="V29">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="W29">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y29">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Z29">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AA29">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="AB29">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC29">
         <v>5.5</v>
       </c>
       <c r="AD29">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AE29">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF29">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="AG29">
         <v>1.55</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AK29">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,22 +5167,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30">
         <v>0</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -5195,111 +5195,111 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
-        <v>2.25</v>
+        <v>1.17</v>
       </c>
       <c r="O30">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="P30">
-        <v>3.42</v>
+        <v>21</v>
       </c>
       <c r="Q30">
-        <v>3.14</v>
+        <v>2.31</v>
       </c>
       <c r="R30">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="S30">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="T30">
-        <v>2.08</v>
+        <v>2.37</v>
       </c>
       <c r="U30">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="V30">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="W30">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X30">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y30">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="Z30">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AA30">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="AB30">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC30">
         <v>5.5</v>
       </c>
       <c r="AD30">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AE30">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF30">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="AG30">
         <v>1.55</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
+          <t>["36"]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ30">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AK30">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="AL30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
@@ -5339,36 +5339,36 @@
         </is>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31">
         <v>0</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
         <v>2.28</v>
       </c>
       <c r="O31">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P31">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -5377,10 +5377,10 @@
         <v>1.8</v>
       </c>
       <c r="S31">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="T31">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="U31">
         <v>3.9</v>
@@ -5404,7 +5404,7 @@
         <v>2.9</v>
       </c>
       <c r="AB31">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AC31">
         <v>5.7</v>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "82"]</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
@@ -5441,28 +5441,28 @@
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN31">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO31">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
@@ -5502,26 +5502,26 @@
         </is>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32">
         <v>0</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N32">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61"]</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "28"]</t>
         </is>
       </c>
       <c r="AJ32">
@@ -5604,28 +5604,28 @@
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP32">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
@@ -5665,26 +5665,26 @@
         </is>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H33">
         <v>0</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N33">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "12", "29", "55"]</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
@@ -5767,28 +5767,28 @@
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN33">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO33">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP33">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
@@ -5991,26 +5991,26 @@
         </is>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35">
         <v>0</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N35">
@@ -6075,12 +6075,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "48", "50"]</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10"]</t>
         </is>
       </c>
       <c r="AJ35">
@@ -6093,28 +6093,28 @@
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN35">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO35">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP35">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
@@ -6317,26 +6317,26 @@
         </is>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L37">
         <v>0</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N37">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40", "60", "68", "80"]</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44"]</t>
         </is>
       </c>
       <c r="AJ37">
@@ -6419,28 +6419,28 @@
         <v>0</v>
       </c>
       <c r="AM37">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN37">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO37">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
@@ -6666,43 +6666,43 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="O39">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="P39">
-        <v>6.25</v>
+        <v>7.55</v>
       </c>
       <c r="Q39">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="R39">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="S39">
         <v>1.25</v>
       </c>
       <c r="T39">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U39">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="V39">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W39">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z39">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AA39">
         <v>1.55</v>
@@ -6711,19 +6711,19 @@
         <v>2.35</v>
       </c>
       <c r="AC39">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AD39">
         <v>1.53</v>
       </c>
       <c r="AE39">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AF39">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AG39">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK39">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="O40">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P40">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q40">
         <v>2.5</v>
       </c>
       <c r="R40">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S40">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T40">
         <v>3.14</v>
       </c>
       <c r="U40">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V40">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W40">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
         <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z40">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA40">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB40">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AC40">
-        <v>2.68</v>
+        <v>2.2</v>
       </c>
       <c r="AD40">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE40">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF40">
         <v>1.44</v>
       </c>
       <c r="AG40">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK40">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6998,25 +6998,25 @@
         <v>5</v>
       </c>
       <c r="P41">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="Q41">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="R41">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="S41">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T41">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="U41">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="V41">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="W41">
         <v>1.25</v>
@@ -7025,31 +7025,31 @@
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Z41">
-        <v>7.1</v>
+        <v>9.5</v>
       </c>
       <c r="AA41">
         <v>1.28</v>
       </c>
       <c r="AB41">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="AC41">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AD41">
-        <v>1.93</v>
+        <v>2.31</v>
       </c>
       <c r="AE41">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF41">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG41">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK41">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>2.44</v>
       </c>
       <c r="O42">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="P42">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="O43">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="P43">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="Q43">
         <v>2.8</v>
       </c>
       <c r="R43">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="S43">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="T43">
         <v>2.44</v>
       </c>
       <c r="U43">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="V43">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W43">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y43">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z43">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AA43">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AB43">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC43">
-        <v>4.34</v>
+        <v>4.2</v>
       </c>
       <c r="AD43">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE43">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF43">
         <v>1.91</v>
       </c>
       <c r="AG43">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK43">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,65 +7481,65 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O44">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P44">
         <v>2.4</v>
       </c>
       <c r="Q44">
-        <v>3.26</v>
+        <v>3.18</v>
       </c>
       <c r="R44">
+        <v>2.11</v>
+      </c>
+      <c r="S44">
+        <v>1.33</v>
+      </c>
+      <c r="T44">
+        <v>2.91</v>
+      </c>
+      <c r="U44">
+        <v>2.63</v>
+      </c>
+      <c r="V44">
+        <v>1.44</v>
+      </c>
+      <c r="W44">
+        <v>1.08</v>
+      </c>
+      <c r="X44">
+        <v>1.02</v>
+      </c>
+      <c r="Y44">
+        <v>1.23</v>
+      </c>
+      <c r="Z44">
+        <v>3.9</v>
+      </c>
+      <c r="AA44">
+        <v>1.72</v>
+      </c>
+      <c r="AB44">
+        <v>2.07</v>
+      </c>
+      <c r="AC44">
+        <v>2.9</v>
+      </c>
+      <c r="AD44">
+        <v>1.41</v>
+      </c>
+      <c r="AE44">
+        <v>1.12</v>
+      </c>
+      <c r="AF44">
+        <v>1.57</v>
+      </c>
+      <c r="AG44">
         <v>2.25</v>
       </c>
-      <c r="S44">
-        <v>1.35</v>
-      </c>
-      <c r="T44">
-        <v>2.82</v>
-      </c>
-      <c r="U44">
-        <v>2.77</v>
-      </c>
-      <c r="V44">
-        <v>1.43</v>
-      </c>
-      <c r="W44">
-        <v>1.06</v>
-      </c>
-      <c r="X44">
-        <v>1.01</v>
-      </c>
-      <c r="Y44">
-        <v>1.22</v>
-      </c>
-      <c r="Z44">
-        <v>3.5</v>
-      </c>
-      <c r="AA44">
-        <v>1.88</v>
-      </c>
-      <c r="AB44">
-        <v>1.88</v>
-      </c>
-      <c r="AC44">
-        <v>2.83</v>
-      </c>
-      <c r="AD44">
-        <v>1.36</v>
-      </c>
-      <c r="AE44">
-        <v>1.1</v>
-      </c>
-      <c r="AF44">
-        <v>1.52</v>
-      </c>
-      <c r="AG44">
-        <v>2.12</v>
-      </c>
       <c r="AH44" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK44">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AL44">
         <v>0</v>
